--- a/spreadsheet/CardLedger-Google-Sheets.xlsx
+++ b/spreadsheet/CardLedger-Google-Sheets.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sales" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clients" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands &amp; Makes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventory'!$A$1:$P$501</definedName>
@@ -20,6 +21,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sales'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clients'!$A$1:$H$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Clients'!$1:$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Brands &amp; Makes'!$A$1:$D$231</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -31,7 +33,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +48,14 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="0017243B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
       <color rgb="0017243B"/>
       <sz val="11"/>
     </font>
@@ -127,32 +137,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -17288,7 +17305,10 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations count="4">
+    <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Custom brand" error="This brand is not in the reference list. You may keep it or add it to Brands &amp; Makes." promptTitle="Brand or product line" prompt="Choose a listed brand, or enter a custom release." type="list" errorStyle="warning">
+      <formula1>INDIRECT("'Brands &amp; Makes'!$A$2:$A$1001")</formula1>
+    </dataValidation>
     <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a valid non-negative amount or whole-number quantity." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
@@ -47026,7 +47046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47145,7 +47165,5124 @@
         </is>
       </c>
     </row>
+    <row r="18" ht="45" customHeight="1">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>15. Brands &amp; Makes lists major brands, product lines, and historical labels; it is not an exhaustive release checklist or a current ownership/licensing directory. Inventory column E includes a dropdown. Add missing names in column A of Brands &amp; Makes (up to row 1001) or enter a custom name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>16. In Google Sheets, if the brand dropdown does not convert, select Inventory E2:E501 → Data → Data validation → Dropdown from a range → Brands &amp; Makes!A2:A1001. Use a warning rather than rejecting custom brands.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D231"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="85" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="21" t="inlineStr">
+        <is>
+          <t>Brand / product name</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t>Brand family / make</t>
+        </is>
+      </c>
+      <c r="C1" s="21" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="21" t="inlineStr">
+        <is>
+          <t>Reference notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="22" t="inlineStr">
+        <is>
+          <t>A&amp;BC</t>
+        </is>
+      </c>
+      <c r="B2" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C2" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D2" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Action Packed</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>Arena Club</t>
+        </is>
+      </c>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Best</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Bowman Chrome</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>Bowman Draft</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Bowman Heritage</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Bowman Inception</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Bowman Platinum</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="inlineStr">
+        <is>
+          <t>Bowman Sterling</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Bowman University</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Bowman University Best</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Bowman University Chrome</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Bowman's Best</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>Bowman</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Broders</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Classic Best</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Classic Draft Picks</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Classic Four Sport</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>Classic</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Cracker Jack</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Custom / other</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>Use this or enter a custom name for releases not listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Donruss Americana</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Donruss Classics</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Donruss Diamond Kings</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Donruss Elite</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Donruss Elite Extra Edition</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C29" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D29" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Donruss Leaf</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Donruss Optic</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C31" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D31" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Donruss Signature Series</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>Donruss Studio</t>
+        </is>
+      </c>
+      <c r="B33" s="23" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C33" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D33" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Donruss Threads</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Donruss</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D34" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>Dover</t>
+        </is>
+      </c>
+      <c r="B35" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Fleer E-X</t>
+        </is>
+      </c>
+      <c r="B37" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C37" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D37" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Flair</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D38" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Fleer Flair Showcase</t>
+        </is>
+      </c>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C39" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D39" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Focus</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C40" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D40" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>Fleer Greats of the Game</t>
+        </is>
+      </c>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C41" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D41" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Hot Prospects</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C42" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D42" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="inlineStr">
+        <is>
+          <t>Fleer Metal</t>
+        </is>
+      </c>
+      <c r="B43" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C43" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D43" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Metal Universe</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="inlineStr">
+        <is>
+          <t>Fleer Mystique</t>
+        </is>
+      </c>
+      <c r="B45" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C45" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D45" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Showcase</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C46" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D46" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Fleer Tradition</t>
+        </is>
+      </c>
+      <c r="B47" s="23" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C47" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D47" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>Fleer Ultra</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Fleer</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
+        <is>
+          <t>Goodwin &amp; Company</t>
+        </is>
+      </c>
+      <c r="B49" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C49" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D49" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>Goudey</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="inlineStr">
+        <is>
+          <t>Gum Inc.</t>
+        </is>
+      </c>
+      <c r="B51" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C51" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D51" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>Honus Bonus</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="B53" s="23" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="C53" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D53" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>In The Game Between the Pipes</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>In The Game Heroes and Prospects</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>In The Game Superlative</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="inlineStr">
+        <is>
+          <t>In The Game Ultimate Memorabilia</t>
+        </is>
+      </c>
+      <c r="B57" s="23" t="inlineStr">
+        <is>
+          <t>In The Game</t>
+        </is>
+      </c>
+      <c r="C57" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D57" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Kellogg's</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="B59" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C59" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D59" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Decadence</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C60" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D60" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>Leaf In The Game Used</t>
+        </is>
+      </c>
+      <c r="B61" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C61" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D61" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Lumber</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C62" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D62" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="inlineStr">
+        <is>
+          <t>Leaf Metal</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C63" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Pop Century</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C64" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D64" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="23" t="inlineStr">
+        <is>
+          <t>Leaf Pro Set</t>
+        </is>
+      </c>
+      <c r="B65" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C65" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D65" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Signature Series</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C66" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D66" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="23" t="inlineStr">
+        <is>
+          <t>Leaf Trinity</t>
+        </is>
+      </c>
+      <c r="B67" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C67" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D67" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Ultimate</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C68" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D68" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="23" t="inlineStr">
+        <is>
+          <t>Leaf Ultimate Draft</t>
+        </is>
+      </c>
+      <c r="B69" s="23" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C69" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D69" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="22" t="inlineStr">
+        <is>
+          <t>Leaf Valiant</t>
+        </is>
+      </c>
+      <c r="B70" s="22" t="inlineStr">
+        <is>
+          <t>Leaf</t>
+        </is>
+      </c>
+      <c r="C70" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D70" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="23" t="inlineStr">
+        <is>
+          <t>Lone Star</t>
+        </is>
+      </c>
+      <c r="B71" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C71" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D71" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="22" t="inlineStr">
+        <is>
+          <t>Mother's Cookies</t>
+        </is>
+      </c>
+      <c r="B72" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C72" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D72" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="23" t="inlineStr">
+        <is>
+          <t>O-Pee-Chee</t>
+        </is>
+      </c>
+      <c r="B73" s="23" t="inlineStr">
+        <is>
+          <t>O-Pee-Chee</t>
+        </is>
+      </c>
+      <c r="C73" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D73" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="22" t="inlineStr">
+        <is>
+          <t>O-Pee-Chee Premier</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>O-Pee-Chee</t>
+        </is>
+      </c>
+      <c r="C74" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D74" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="23" t="inlineStr">
+        <is>
+          <t>Onyx</t>
+        </is>
+      </c>
+      <c r="B75" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C75" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D75" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C76" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D76" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="23" t="inlineStr">
+        <is>
+          <t>Pacific Cramer</t>
+        </is>
+      </c>
+      <c r="B77" s="23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C77" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D77" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="22" t="inlineStr">
+        <is>
+          <t>Pacific Crown Royale</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C78" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D78" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="23" t="inlineStr">
+        <is>
+          <t>Pacific Invincible</t>
+        </is>
+      </c>
+      <c r="B79" s="23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C79" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D79" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="22" t="inlineStr">
+        <is>
+          <t>Pacific Prism</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C80" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D80" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="23" t="inlineStr">
+        <is>
+          <t>Pacific Private Stock</t>
+        </is>
+      </c>
+      <c r="B81" s="23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C81" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D81" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="22" t="inlineStr">
+        <is>
+          <t>Pacific Prizm</t>
+        </is>
+      </c>
+      <c r="B82" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C82" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D82" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="23" t="inlineStr">
+        <is>
+          <t>Pacific Revolution</t>
+        </is>
+      </c>
+      <c r="B83" s="23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C83" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D83" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="22" t="inlineStr">
+        <is>
+          <t>Pacific Titanium</t>
+        </is>
+      </c>
+      <c r="B84" s="22" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C84" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D84" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="23" t="inlineStr">
+        <is>
+          <t>Pacific Vanguard</t>
+        </is>
+      </c>
+      <c r="B85" s="23" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="C85" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D85" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C86" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D86" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="23" t="inlineStr">
+        <is>
+          <t>Panini Absolute</t>
+        </is>
+      </c>
+      <c r="B87" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C87" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D87" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="22" t="inlineStr">
+        <is>
+          <t>Panini Adrenalyn XL</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D88" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="inlineStr">
+        <is>
+          <t>Panini Black</t>
+        </is>
+      </c>
+      <c r="B89" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C89" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D89" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="22" t="inlineStr">
+        <is>
+          <t>Panini Certified</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C90" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="23" t="inlineStr">
+        <is>
+          <t>Panini Chronicles</t>
+        </is>
+      </c>
+      <c r="B91" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C91" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D91" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="22" t="inlineStr">
+        <is>
+          <t>Panini Contenders</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C92" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="23" t="inlineStr">
+        <is>
+          <t>Panini Contenders Optic</t>
+        </is>
+      </c>
+      <c r="B93" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C93" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="22" t="inlineStr">
+        <is>
+          <t>Panini Court Kings</t>
+        </is>
+      </c>
+      <c r="B94" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D94" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="23" t="inlineStr">
+        <is>
+          <t>Panini Crown Royale</t>
+        </is>
+      </c>
+      <c r="B95" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C95" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="22" t="inlineStr">
+        <is>
+          <t>Panini Elite</t>
+        </is>
+      </c>
+      <c r="B96" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C96" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D96" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="23" t="inlineStr">
+        <is>
+          <t>Panini Encased</t>
+        </is>
+      </c>
+      <c r="B97" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C97" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D97" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="22" t="inlineStr">
+        <is>
+          <t>Panini Flawless</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C98" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="23" t="inlineStr">
+        <is>
+          <t>Panini Gold Standard</t>
+        </is>
+      </c>
+      <c r="B99" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C99" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="22" t="inlineStr">
+        <is>
+          <t>Panini Hoops</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C100" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D100" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="23" t="inlineStr">
+        <is>
+          <t>Panini Illusions</t>
+        </is>
+      </c>
+      <c r="B101" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C101" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="22" t="inlineStr">
+        <is>
+          <t>Panini Immaculate Collection</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C102" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D102" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="23" t="inlineStr">
+        <is>
+          <t>Panini Impeccable</t>
+        </is>
+      </c>
+      <c r="B103" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C103" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D103" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="22" t="inlineStr">
+        <is>
+          <t>Panini Instant</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C104" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D104" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="23" t="inlineStr">
+        <is>
+          <t>Panini Limited</t>
+        </is>
+      </c>
+      <c r="B105" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C105" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D105" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="22" t="inlineStr">
+        <is>
+          <t>Panini Luminance</t>
+        </is>
+      </c>
+      <c r="B106" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D106" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="inlineStr">
+        <is>
+          <t>Panini Mosaic</t>
+        </is>
+      </c>
+      <c r="B107" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C107" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="22" t="inlineStr">
+        <is>
+          <t>Panini National Treasures</t>
+        </is>
+      </c>
+      <c r="B108" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C108" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D108" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="23" t="inlineStr">
+        <is>
+          <t>Panini NBA Hoops</t>
+        </is>
+      </c>
+      <c r="B109" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C109" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="22" t="inlineStr">
+        <is>
+          <t>Panini Noir</t>
+        </is>
+      </c>
+      <c r="B110" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D110" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="23" t="inlineStr">
+        <is>
+          <t>Panini Obsidian</t>
+        </is>
+      </c>
+      <c r="B111" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C111" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="22" t="inlineStr">
+        <is>
+          <t>Panini One</t>
+        </is>
+      </c>
+      <c r="B112" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D112" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="23" t="inlineStr">
+        <is>
+          <t>Panini One and One</t>
+        </is>
+      </c>
+      <c r="B113" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C113" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="22" t="inlineStr">
+        <is>
+          <t>Panini Origins</t>
+        </is>
+      </c>
+      <c r="B114" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C114" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D114" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="23" t="inlineStr">
+        <is>
+          <t>Panini Phoenix</t>
+        </is>
+      </c>
+      <c r="B115" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C115" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="22" t="inlineStr">
+        <is>
+          <t>Panini Playbook</t>
+        </is>
+      </c>
+      <c r="B116" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C116" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D116" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="23" t="inlineStr">
+        <is>
+          <t>Panini Prestige</t>
+        </is>
+      </c>
+      <c r="B117" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C117" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D117" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="22" t="inlineStr">
+        <is>
+          <t>Panini Prizm</t>
+        </is>
+      </c>
+      <c r="B118" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C118" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D118" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="23" t="inlineStr">
+        <is>
+          <t>Panini Revolution</t>
+        </is>
+      </c>
+      <c r="B119" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C119" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D119" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="22" t="inlineStr">
+        <is>
+          <t>Panini Select</t>
+        </is>
+      </c>
+      <c r="B120" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C120" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D120" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="23" t="inlineStr">
+        <is>
+          <t>Panini Spectra</t>
+        </is>
+      </c>
+      <c r="B121" s="23" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C121" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D121" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="22" t="inlineStr">
+        <is>
+          <t>Panini XR</t>
+        </is>
+      </c>
+      <c r="B122" s="22" t="inlineStr">
+        <is>
+          <t>Panini</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D122" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="23" t="inlineStr">
+        <is>
+          <t>Parkhurst</t>
+        </is>
+      </c>
+      <c r="B123" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C123" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D123" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="B124" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="C124" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D124" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="23" t="inlineStr">
+        <is>
+          <t>Pinnacle Aficionado</t>
+        </is>
+      </c>
+      <c r="B125" s="23" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="C125" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D125" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle Certified</t>
+        </is>
+      </c>
+      <c r="B126" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="C126" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D126" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="23" t="inlineStr">
+        <is>
+          <t>Pinnacle Inside</t>
+        </is>
+      </c>
+      <c r="B127" s="23" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="C127" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D127" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle Zenith</t>
+        </is>
+      </c>
+      <c r="B128" s="22" t="inlineStr">
+        <is>
+          <t>Pinnacle</t>
+        </is>
+      </c>
+      <c r="C128" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D128" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="23" t="inlineStr">
+        <is>
+          <t>Post</t>
+        </is>
+      </c>
+      <c r="B129" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C129" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D129" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="B130" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C130" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D130" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass Eclipse</t>
+        </is>
+      </c>
+      <c r="B131" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C131" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass Legends</t>
+        </is>
+      </c>
+      <c r="B132" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C132" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D132" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass Premium</t>
+        </is>
+      </c>
+      <c r="B133" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C133" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D133" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass SE</t>
+        </is>
+      </c>
+      <c r="B134" s="22" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C134" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D134" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass Showcase</t>
+        </is>
+      </c>
+      <c r="B135" s="23" t="inlineStr">
+        <is>
+          <t>Press Pass</t>
+        </is>
+      </c>
+      <c r="C135" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D135" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="22" t="inlineStr">
+        <is>
+          <t>Pro Set</t>
+        </is>
+      </c>
+      <c r="B136" s="22" t="inlineStr">
+        <is>
+          <t>Pro Set</t>
+        </is>
+      </c>
+      <c r="C136" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D136" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="23" t="inlineStr">
+        <is>
+          <t>Pro Set Platinum</t>
+        </is>
+      </c>
+      <c r="B137" s="23" t="inlineStr">
+        <is>
+          <t>Pro Set</t>
+        </is>
+      </c>
+      <c r="C137" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D137" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="22" t="inlineStr">
+        <is>
+          <t>Pro Set Power</t>
+        </is>
+      </c>
+      <c r="B138" s="22" t="inlineStr">
+        <is>
+          <t>Pro Set</t>
+        </is>
+      </c>
+      <c r="C138" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D138" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="23" t="inlineStr">
+        <is>
+          <t>Rittenhouse</t>
+        </is>
+      </c>
+      <c r="B139" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C139" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D139" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="22" t="inlineStr">
+        <is>
+          <t>Royal Rookies</t>
+        </is>
+      </c>
+      <c r="B140" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C140" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D140" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="23" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="B141" s="23" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="C141" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D141" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="22" t="inlineStr">
+        <is>
+          <t>SAGE Aspire</t>
+        </is>
+      </c>
+      <c r="B142" s="22" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="C142" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D142" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="23" t="inlineStr">
+        <is>
+          <t>SAGE Autographed</t>
+        </is>
+      </c>
+      <c r="B143" s="23" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="C143" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="22" t="inlineStr">
+        <is>
+          <t>SAGE HIT</t>
+        </is>
+      </c>
+      <c r="B144" s="22" t="inlineStr">
+        <is>
+          <t>SAGE</t>
+        </is>
+      </c>
+      <c r="C144" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D144" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B145" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C145" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D145" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="22" t="inlineStr">
+        <is>
+          <t>Score Pinnacle</t>
+        </is>
+      </c>
+      <c r="B146" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C146" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D146" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="23" t="inlineStr">
+        <is>
+          <t>Score Select</t>
+        </is>
+      </c>
+      <c r="B147" s="23" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C147" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D147" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="22" t="inlineStr">
+        <is>
+          <t>Score Summit</t>
+        </is>
+      </c>
+      <c r="B148" s="22" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="C148" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D148" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="B149" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C149" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D149" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox Autographics</t>
+        </is>
+      </c>
+      <c r="B150" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D150" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox Dominion</t>
+        </is>
+      </c>
+      <c r="B151" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C151" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D151" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox E-X</t>
+        </is>
+      </c>
+      <c r="B152" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D152" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox E-X2000</t>
+        </is>
+      </c>
+      <c r="B153" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C153" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D153" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox E-X2001</t>
+        </is>
+      </c>
+      <c r="B154" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D154" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox Metal Universe</t>
+        </is>
+      </c>
+      <c r="B155" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C155" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D155" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox Premium</t>
+        </is>
+      </c>
+      <c r="B156" s="22" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C156" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D156" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox Z-Force</t>
+        </is>
+      </c>
+      <c r="B157" s="23" t="inlineStr">
+        <is>
+          <t>SkyBox</t>
+        </is>
+      </c>
+      <c r="C157" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D157" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="22" t="inlineStr">
+        <is>
+          <t>Sport Kings</t>
+        </is>
+      </c>
+      <c r="B158" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C158" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D158" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="23" t="inlineStr">
+        <is>
+          <t>TCMA</t>
+        </is>
+      </c>
+      <c r="B159" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C159" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D159" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="22" t="inlineStr">
+        <is>
+          <t>Tobacco cards (T-series)</t>
+        </is>
+      </c>
+      <c r="B160" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C160" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D160" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="B161" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C161" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D161" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="22" t="inlineStr">
+        <is>
+          <t>Topps Allen &amp; Ginter</t>
+        </is>
+      </c>
+      <c r="B162" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C162" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D162" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="23" t="inlineStr">
+        <is>
+          <t>Topps Archives</t>
+        </is>
+      </c>
+      <c r="B163" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C163" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D163" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="22" t="inlineStr">
+        <is>
+          <t>Topps Archives Signature Series</t>
+        </is>
+      </c>
+      <c r="B164" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C164" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D164" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="23" t="inlineStr">
+        <is>
+          <t>Topps Big League</t>
+        </is>
+      </c>
+      <c r="B165" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C165" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D165" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="22" t="inlineStr">
+        <is>
+          <t>Topps Bundesliga</t>
+        </is>
+      </c>
+      <c r="B166" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C166" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D166" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="23" t="inlineStr">
+        <is>
+          <t>Topps Chrome</t>
+        </is>
+      </c>
+      <c r="B167" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C167" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D167" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="22" t="inlineStr">
+        <is>
+          <t>Topps Chrome Black</t>
+        </is>
+      </c>
+      <c r="B168" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C168" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D168" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="23" t="inlineStr">
+        <is>
+          <t>Topps Chrome Platinum Anniversary</t>
+        </is>
+      </c>
+      <c r="B169" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C169" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D169" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="22" t="inlineStr">
+        <is>
+          <t>Topps Chrome Sapphire</t>
+        </is>
+      </c>
+      <c r="B170" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C170" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D170" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="23" t="inlineStr">
+        <is>
+          <t>Topps Chrome Update</t>
+        </is>
+      </c>
+      <c r="B171" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C171" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D171" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="22" t="inlineStr">
+        <is>
+          <t>Topps Cosmic Chrome</t>
+        </is>
+      </c>
+      <c r="B172" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C172" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D172" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="23" t="inlineStr">
+        <is>
+          <t>Topps Definitive</t>
+        </is>
+      </c>
+      <c r="B173" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C173" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D173" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="22" t="inlineStr">
+        <is>
+          <t>Topps Dynasty</t>
+        </is>
+      </c>
+      <c r="B174" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C174" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D174" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="23" t="inlineStr">
+        <is>
+          <t>Topps Finest</t>
+        </is>
+      </c>
+      <c r="B175" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C175" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D175" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="22" t="inlineStr">
+        <is>
+          <t>Topps Fire</t>
+        </is>
+      </c>
+      <c r="B176" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C176" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D176" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="23" t="inlineStr">
+        <is>
+          <t>Topps Five Star</t>
+        </is>
+      </c>
+      <c r="B177" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C177" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D177" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="22" t="inlineStr">
+        <is>
+          <t>Topps Gallery</t>
+        </is>
+      </c>
+      <c r="B178" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C178" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D178" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="23" t="inlineStr">
+        <is>
+          <t>Topps Gold Label</t>
+        </is>
+      </c>
+      <c r="B179" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C179" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D179" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="22" t="inlineStr">
+        <is>
+          <t>Topps Gypsy Queen</t>
+        </is>
+      </c>
+      <c r="B180" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C180" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D180" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="23" t="inlineStr">
+        <is>
+          <t>Topps Heritage</t>
+        </is>
+      </c>
+      <c r="B181" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C181" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D181" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="22" t="inlineStr">
+        <is>
+          <t>Topps Inception</t>
+        </is>
+      </c>
+      <c r="B182" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C182" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D182" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="23" t="inlineStr">
+        <is>
+          <t>Topps Living Set</t>
+        </is>
+      </c>
+      <c r="B183" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C183" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D183" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="22" t="inlineStr">
+        <is>
+          <t>Topps Match Attax</t>
+        </is>
+      </c>
+      <c r="B184" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C184" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D184" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="23" t="inlineStr">
+        <is>
+          <t>Topps Museum Collection</t>
+        </is>
+      </c>
+      <c r="B185" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C185" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D185" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="22" t="inlineStr">
+        <is>
+          <t>Topps NOW</t>
+        </is>
+      </c>
+      <c r="B186" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C186" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D186" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="23" t="inlineStr">
+        <is>
+          <t>Topps Opening Day</t>
+        </is>
+      </c>
+      <c r="B187" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C187" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D187" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="22" t="inlineStr">
+        <is>
+          <t>Topps Pro Debut</t>
+        </is>
+      </c>
+      <c r="B188" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C188" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D188" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="23" t="inlineStr">
+        <is>
+          <t>Topps Stadium Club</t>
+        </is>
+      </c>
+      <c r="B189" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C189" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D189" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="22" t="inlineStr">
+        <is>
+          <t>Topps Stadium Club Chrome</t>
+        </is>
+      </c>
+      <c r="B190" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C190" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D190" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="23" t="inlineStr">
+        <is>
+          <t>Topps T206</t>
+        </is>
+      </c>
+      <c r="B191" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C191" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D191" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="22" t="inlineStr">
+        <is>
+          <t>Topps Tier One</t>
+        </is>
+      </c>
+      <c r="B192" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C192" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D192" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="23" t="inlineStr">
+        <is>
+          <t>Topps Transcendent</t>
+        </is>
+      </c>
+      <c r="B193" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C193" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D193" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="22" t="inlineStr">
+        <is>
+          <t>Topps Tribute</t>
+        </is>
+      </c>
+      <c r="B194" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C194" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D194" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="23" t="inlineStr">
+        <is>
+          <t>Topps Triple Threads</t>
+        </is>
+      </c>
+      <c r="B195" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C195" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D195" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="22" t="inlineStr">
+        <is>
+          <t>Topps UEFA Club Competitions</t>
+        </is>
+      </c>
+      <c r="B196" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C196" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D196" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="23" t="inlineStr">
+        <is>
+          <t>Topps Update</t>
+        </is>
+      </c>
+      <c r="B197" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C197" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D197" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="22" t="inlineStr">
+        <is>
+          <t>Tristar</t>
+        </is>
+      </c>
+      <c r="B198" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C198" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D198" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="23" t="inlineStr">
+        <is>
+          <t>Tristar Hidden Treasures</t>
+        </is>
+      </c>
+      <c r="B199" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C199" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D199" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="22" t="inlineStr">
+        <is>
+          <t>Tristar Obak</t>
+        </is>
+      </c>
+      <c r="B200" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C200" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D200" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="B201" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C201" s="23" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D201" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Allure</t>
+        </is>
+      </c>
+      <c r="B202" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C202" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D202" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Artifacts</t>
+        </is>
+      </c>
+      <c r="B203" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C203" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D203" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Black Diamond</t>
+        </is>
+      </c>
+      <c r="B204" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C204" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D204" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck CHL</t>
+        </is>
+      </c>
+      <c r="B205" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C205" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D205" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Clear Cut</t>
+        </is>
+      </c>
+      <c r="B206" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C206" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D206" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Credentials</t>
+        </is>
+      </c>
+      <c r="B207" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C207" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D207" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Exquisite Collection</t>
+        </is>
+      </c>
+      <c r="B208" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C208" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D208" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Extended Series</t>
+        </is>
+      </c>
+      <c r="B209" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C209" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D209" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Goodwin Champions</t>
+        </is>
+      </c>
+      <c r="B210" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C210" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D210" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Ice</t>
+        </is>
+      </c>
+      <c r="B211" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C211" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D211" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck MVP</t>
+        </is>
+      </c>
+      <c r="B212" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C212" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D212" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck O-Pee-Chee</t>
+        </is>
+      </c>
+      <c r="B213" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C213" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D213" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck O-Pee-Chee Platinum</t>
+        </is>
+      </c>
+      <c r="B214" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C214" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D214" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Parkhurst</t>
+        </is>
+      </c>
+      <c r="B215" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C215" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D215" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Parkhurst Champions</t>
+        </is>
+      </c>
+      <c r="B216" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C216" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D216" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Premier</t>
+        </is>
+      </c>
+      <c r="B217" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C217" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D217" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Series 1</t>
+        </is>
+      </c>
+      <c r="B218" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C218" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D218" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Series 2</t>
+        </is>
+      </c>
+      <c r="B219" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C219" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D219" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Authentic</t>
+        </is>
+      </c>
+      <c r="B220" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C220" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D220" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Game Used</t>
+        </is>
+      </c>
+      <c r="B221" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C221" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D221" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Signature</t>
+        </is>
+      </c>
+      <c r="B222" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C222" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D222" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck SPx</t>
+        </is>
+      </c>
+      <c r="B223" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C223" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D223" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Synergy</t>
+        </is>
+      </c>
+      <c r="B224" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C224" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D224" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck The Cup</t>
+        </is>
+      </c>
+      <c r="B225" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C225" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D225" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Trilogy</t>
+        </is>
+      </c>
+      <c r="B226" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C226" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D226" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Ultimate Collection</t>
+        </is>
+      </c>
+      <c r="B227" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C227" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D227" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Young Guns</t>
+        </is>
+      </c>
+      <c r="B228" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C228" s="22" t="inlineStr">
+        <is>
+          <t>Insert / rookie subset</t>
+        </is>
+      </c>
+      <c r="D228" s="22" t="inlineStr">
+        <is>
+          <t>Young Guns is a subset, not a separate manufacturer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="23" t="inlineStr">
+        <is>
+          <t>Wild Card</t>
+        </is>
+      </c>
+      <c r="B229" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C229" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D229" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="22" t="inlineStr">
+        <is>
+          <t>Wizards of the Coast MLB Showdown</t>
+        </is>
+      </c>
+      <c r="B230" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C230" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D230" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="23" t="inlineStr">
+        <is>
+          <t>Zee-Nut</t>
+        </is>
+      </c>
+      <c r="B231" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C231" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D231"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/spreadsheet/CardLedger-Google-Sheets.xlsx
+++ b/spreadsheet/CardLedger-Google-Sheets.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sales'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clients'!$A$1:$H$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Clients'!$1:$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Brands &amp; Makes'!$A$1:$D$231</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Brands &amp; Makes'!$A$1:$D$282</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -724,12 +724,12 @@
       </c>
       <c r="B1" s="8" t="inlineStr">
         <is>
-          <t>Player / Card</t>
+          <t>Player / Character / Card</t>
         </is>
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>Sport</t>
+          <t>Card category</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
@@ -17305,9 +17305,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Custom brand" error="This brand is not in the reference list. You may keep it or add it to Brands &amp; Makes." promptTitle="Brand or product line" prompt="Choose a listed brand, or enter a custom release." type="list" errorStyle="warning">
       <formula1>INDIRECT("'Brands &amp; Makes'!$A$2:$A$1001")</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Choose a card category or keep a custom category." type="list" errorStyle="warning">
+      <formula1>"Baseball,Basketball,Football,Hockey,Soccer,Pokémon,Marvel,Disney,Magic: The Gathering,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Check this value" error="Enter a valid non-negative amount or whole-number quantity." type="whole" errorStyle="stop" operator="greaterThanOrEqual">
       <formula1>1</formula1>
@@ -47070,7 +47073,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="B4" s="20" t="inlineStr">
         <is>
-          <t>1. Inventory: use one unique Lot ID per purchase batch (example LOT-001). Enter player, sport, pieces purchased, purchase cost per card, and estimated market value per card.</t>
+          <t>1. Inventory: use one unique Lot ID per purchase batch (example LOT-001). Enter player or character, card category, pieces purchased, purchase cost per card, and estimated market value per card.</t>
         </is>
       </c>
     </row>
@@ -47190,7 +47193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D231"/>
+  <dimension ref="A1:D282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -47708,259 +47711,259 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney Collect! by Topps (digital)</t>
         </is>
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Digital collectible app; not a physical printed card product.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="23" t="inlineStr">
         <is>
-          <t>Donruss Americana</t>
+          <t>Disney Lorcana (Ravensburger)</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>Donruss Classics</t>
+          <t>Disney Lorcana Azurite Sea</t>
         </is>
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="23" t="inlineStr">
         <is>
-          <t>Donruss Diamond Kings</t>
+          <t>Disney Lorcana Into the Inklands</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>Donruss Elite</t>
+          <t>Disney Lorcana Rise of the Floodborn</t>
         </is>
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>Donruss Elite Extra Edition</t>
+          <t>Disney Lorcana Shimmering Skies</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C29" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D29" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>Donruss Leaf</t>
+          <t>Disney Lorcana The First Chapter</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Donruss Optic</t>
+          <t>Disney Lorcana Ursula’s Return</t>
         </is>
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>Donruss Signature Series</t>
+          <t>Disney Panini</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Donruss Studio</t>
+          <t>Disney Topps</t>
         </is>
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>Donruss Threads</t>
+          <t>Disney Weiss Schwarz (Bushiroad)</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Donruss</t>
+          <t>Disney</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Dover</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C35" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D35" s="23" t="inlineStr">
@@ -47972,17 +47975,17 @@
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss Americana</t>
         </is>
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -47994,12 +47997,12 @@
     <row r="37">
       <c r="A37" s="23" t="inlineStr">
         <is>
-          <t>Fleer E-X</t>
+          <t>Donruss Classics</t>
         </is>
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C37" s="23" t="inlineStr">
@@ -48016,12 +48019,12 @@
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>Fleer Flair</t>
+          <t>Donruss Diamond Kings</t>
         </is>
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C38" s="22" t="inlineStr">
@@ -48038,12 +48041,12 @@
     <row r="39">
       <c r="A39" s="23" t="inlineStr">
         <is>
-          <t>Fleer Flair Showcase</t>
+          <t>Donruss Elite</t>
         </is>
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C39" s="23" t="inlineStr">
@@ -48060,12 +48063,12 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Fleer Focus</t>
+          <t>Donruss Elite Extra Edition</t>
         </is>
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C40" s="22" t="inlineStr">
@@ -48082,12 +48085,12 @@
     <row r="41">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Fleer Greats of the Game</t>
+          <t>Donruss Leaf</t>
         </is>
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C41" s="23" t="inlineStr">
@@ -48104,12 +48107,12 @@
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>Fleer Hot Prospects</t>
+          <t>Donruss Optic</t>
         </is>
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C42" s="22" t="inlineStr">
@@ -48126,12 +48129,12 @@
     <row r="43">
       <c r="A43" s="23" t="inlineStr">
         <is>
-          <t>Fleer Metal</t>
+          <t>Donruss Signature Series</t>
         </is>
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C43" s="23" t="inlineStr">
@@ -48148,12 +48151,12 @@
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>Fleer Metal Universe</t>
+          <t>Donruss Studio</t>
         </is>
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C44" s="22" t="inlineStr">
@@ -48170,12 +48173,12 @@
     <row r="45">
       <c r="A45" s="23" t="inlineStr">
         <is>
-          <t>Fleer Mystique</t>
+          <t>Donruss Threads</t>
         </is>
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Donruss</t>
         </is>
       </c>
       <c r="C45" s="23" t="inlineStr">
@@ -48192,12 +48195,12 @@
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>Fleer Showcase</t>
+          <t>Dover</t>
         </is>
       </c>
       <c r="B46" s="22" t="inlineStr">
         <is>
-          <t>Fleer</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C46" s="22" t="inlineStr">
@@ -48214,7 +48217,7 @@
     <row r="47">
       <c r="A47" s="23" t="inlineStr">
         <is>
-          <t>Fleer Tradition</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="B47" s="23" t="inlineStr">
@@ -48224,7 +48227,7 @@
       </c>
       <c r="C47" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D47" s="23" t="inlineStr">
@@ -48236,7 +48239,7 @@
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>Fleer Ultra</t>
+          <t>Fleer E-X</t>
         </is>
       </c>
       <c r="B48" s="22" t="inlineStr">
@@ -48258,12 +48261,12 @@
     <row r="49">
       <c r="A49" s="23" t="inlineStr">
         <is>
-          <t>Goodwin &amp; Company</t>
+          <t>Fleer Flair</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C49" s="23" t="inlineStr">
@@ -48280,12 +48283,12 @@
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>Goudey</t>
+          <t>Fleer Flair Showcase</t>
         </is>
       </c>
       <c r="B50" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C50" s="22" t="inlineStr">
@@ -48302,12 +48305,12 @@
     <row r="51">
       <c r="A51" s="23" t="inlineStr">
         <is>
-          <t>Gum Inc.</t>
+          <t>Fleer Focus</t>
         </is>
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C51" s="23" t="inlineStr">
@@ -48324,12 +48327,12 @@
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>Honus Bonus</t>
+          <t>Fleer Greats of the Game</t>
         </is>
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C52" s="22" t="inlineStr">
@@ -48346,17 +48349,17 @@
     <row r="53">
       <c r="A53" s="23" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer Hot Prospects</t>
         </is>
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C53" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D53" s="23" t="inlineStr">
@@ -48368,12 +48371,12 @@
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>In The Game Between the Pipes</t>
+          <t>Fleer Metal</t>
         </is>
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C54" s="22" t="inlineStr">
@@ -48390,12 +48393,12 @@
     <row r="55">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>In The Game Heroes and Prospects</t>
+          <t>Fleer Metal Universe</t>
         </is>
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C55" s="23" t="inlineStr">
@@ -48412,12 +48415,12 @@
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>In The Game Superlative</t>
+          <t>Fleer Mystique</t>
         </is>
       </c>
       <c r="B56" s="22" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C56" s="22" t="inlineStr">
@@ -48434,12 +48437,12 @@
     <row r="57">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>In The Game Ultimate Memorabilia</t>
+          <t>Fleer Showcase</t>
         </is>
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>In The Game</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C57" s="23" t="inlineStr">
@@ -48456,12 +48459,12 @@
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>Kellogg's</t>
+          <t>Fleer Tradition</t>
         </is>
       </c>
       <c r="B58" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C58" s="22" t="inlineStr">
@@ -48478,17 +48481,17 @@
     <row r="59">
       <c r="A59" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Fleer Ultra</t>
         </is>
       </c>
       <c r="B59" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Fleer</t>
         </is>
       </c>
       <c r="C59" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D59" s="23" t="inlineStr">
@@ -48500,12 +48503,12 @@
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>Leaf Decadence</t>
+          <t>Goodwin &amp; Company</t>
         </is>
       </c>
       <c r="B60" s="22" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C60" s="22" t="inlineStr">
@@ -48522,12 +48525,12 @@
     <row r="61">
       <c r="A61" s="23" t="inlineStr">
         <is>
-          <t>Leaf In The Game Used</t>
+          <t>Goudey</t>
         </is>
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C61" s="23" t="inlineStr">
@@ -48544,12 +48547,12 @@
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>Leaf Lumber</t>
+          <t>Gum Inc.</t>
         </is>
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C62" s="22" t="inlineStr">
@@ -48566,12 +48569,12 @@
     <row r="63">
       <c r="A63" s="23" t="inlineStr">
         <is>
-          <t>Leaf Metal</t>
+          <t>Honus Bonus</t>
         </is>
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C63" s="23" t="inlineStr">
@@ -48588,17 +48591,17 @@
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>Leaf Pop Century</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="C64" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D64" s="22" t="inlineStr">
@@ -48610,12 +48613,12 @@
     <row r="65">
       <c r="A65" s="23" t="inlineStr">
         <is>
-          <t>Leaf Pro Set</t>
+          <t>In The Game Between the Pipes</t>
         </is>
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="C65" s="23" t="inlineStr">
@@ -48632,12 +48635,12 @@
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>Leaf Signature Series</t>
+          <t>In The Game Heroes and Prospects</t>
         </is>
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="C66" s="22" t="inlineStr">
@@ -48654,12 +48657,12 @@
     <row r="67">
       <c r="A67" s="23" t="inlineStr">
         <is>
-          <t>Leaf Trinity</t>
+          <t>In The Game Superlative</t>
         </is>
       </c>
       <c r="B67" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="C67" s="23" t="inlineStr">
@@ -48676,12 +48679,12 @@
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>Leaf Ultimate</t>
+          <t>In The Game Ultimate Memorabilia</t>
         </is>
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>In The Game</t>
         </is>
       </c>
       <c r="C68" s="22" t="inlineStr">
@@ -48698,12 +48701,12 @@
     <row r="69">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>Leaf Ultimate Draft</t>
+          <t>Kellogg's</t>
         </is>
       </c>
       <c r="B69" s="23" t="inlineStr">
         <is>
-          <t>Leaf</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C69" s="23" t="inlineStr">
@@ -48720,7 +48723,7 @@
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>Leaf Valiant</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="B70" s="22" t="inlineStr">
@@ -48730,7 +48733,7 @@
       </c>
       <c r="C70" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D70" s="22" t="inlineStr">
@@ -48742,12 +48745,12 @@
     <row r="71">
       <c r="A71" s="23" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Leaf Decadence</t>
         </is>
       </c>
       <c r="B71" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C71" s="23" t="inlineStr">
@@ -48764,12 +48767,12 @@
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>Mother's Cookies</t>
+          <t>Leaf In The Game Used</t>
         </is>
       </c>
       <c r="B72" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C72" s="22" t="inlineStr">
@@ -48786,17 +48789,17 @@
     <row r="73">
       <c r="A73" s="23" t="inlineStr">
         <is>
-          <t>O-Pee-Chee</t>
+          <t>Leaf Lumber</t>
         </is>
       </c>
       <c r="B73" s="23" t="inlineStr">
         <is>
-          <t>O-Pee-Chee</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C73" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D73" s="23" t="inlineStr">
@@ -48808,12 +48811,12 @@
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>O-Pee-Chee Premier</t>
+          <t>Leaf Metal</t>
         </is>
       </c>
       <c r="B74" s="22" t="inlineStr">
         <is>
-          <t>O-Pee-Chee</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C74" s="22" t="inlineStr">
@@ -48830,12 +48833,12 @@
     <row r="75">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>Onyx</t>
+          <t>Leaf Pop Century</t>
         </is>
       </c>
       <c r="B75" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C75" s="23" t="inlineStr">
@@ -48852,17 +48855,17 @@
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf Pro Set</t>
         </is>
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C76" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D76" s="22" t="inlineStr">
@@ -48874,12 +48877,12 @@
     <row r="77">
       <c r="A77" s="23" t="inlineStr">
         <is>
-          <t>Pacific Cramer</t>
+          <t>Leaf Signature Series</t>
         </is>
       </c>
       <c r="B77" s="23" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C77" s="23" t="inlineStr">
@@ -48896,12 +48899,12 @@
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>Pacific Crown Royale</t>
+          <t>Leaf Trinity</t>
         </is>
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C78" s="22" t="inlineStr">
@@ -48918,12 +48921,12 @@
     <row r="79">
       <c r="A79" s="23" t="inlineStr">
         <is>
-          <t>Pacific Invincible</t>
+          <t>Leaf Ultimate</t>
         </is>
       </c>
       <c r="B79" s="23" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C79" s="23" t="inlineStr">
@@ -48940,12 +48943,12 @@
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>Pacific Prism</t>
+          <t>Leaf Ultimate Draft</t>
         </is>
       </c>
       <c r="B80" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C80" s="22" t="inlineStr">
@@ -48962,12 +48965,12 @@
     <row r="81">
       <c r="A81" s="23" t="inlineStr">
         <is>
-          <t>Pacific Private Stock</t>
+          <t>Leaf Valiant</t>
         </is>
       </c>
       <c r="B81" s="23" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Leaf</t>
         </is>
       </c>
       <c r="C81" s="23" t="inlineStr">
@@ -48984,12 +48987,12 @@
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>Pacific Prizm</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="B82" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C82" s="22" t="inlineStr">
@@ -49006,650 +49009,650 @@
     <row r="83">
       <c r="A83" s="23" t="inlineStr">
         <is>
-          <t>Pacific Revolution</t>
+          <t>Magic Alpha</t>
         </is>
       </c>
       <c r="B83" s="23" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C83" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D83" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>Pacific Titanium</t>
+          <t>Magic Beta</t>
         </is>
       </c>
       <c r="B84" s="22" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C84" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D84" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="23" t="inlineStr">
         <is>
-          <t>Pacific Vanguard</t>
+          <t>Magic Commander products</t>
         </is>
       </c>
       <c r="B85" s="23" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C85" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D85" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic Core Sets</t>
         </is>
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C86" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D86" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="23" t="inlineStr">
         <is>
-          <t>Panini Absolute</t>
+          <t>Magic Jumpstart</t>
         </is>
       </c>
       <c r="B87" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C87" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D87" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="22" t="inlineStr">
         <is>
-          <t>Panini Adrenalyn XL</t>
+          <t>Magic Masters products</t>
         </is>
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C88" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D88" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="23" t="inlineStr">
         <is>
-          <t>Panini Black</t>
+          <t>Magic Modern Horizons</t>
         </is>
       </c>
       <c r="B89" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C89" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D89" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="22" t="inlineStr">
         <is>
-          <t>Panini Certified</t>
+          <t>Magic Modern Horizons 2</t>
         </is>
       </c>
       <c r="B90" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C90" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D90" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="23" t="inlineStr">
         <is>
-          <t>Panini Chronicles</t>
+          <t>Magic Modern Horizons 3</t>
         </is>
       </c>
       <c r="B91" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C91" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D91" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="22" t="inlineStr">
         <is>
-          <t>Panini Contenders</t>
+          <t>Magic Revised</t>
         </is>
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C92" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D92" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="23" t="inlineStr">
         <is>
-          <t>Panini Contenders Optic</t>
+          <t>Magic Secret Lair</t>
         </is>
       </c>
       <c r="B93" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C93" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D93" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="22" t="inlineStr">
         <is>
-          <t>Panini Court Kings</t>
+          <t>Magic Universes Beyond</t>
         </is>
       </c>
       <c r="B94" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C94" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D94" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="23" t="inlineStr">
         <is>
-          <t>Panini Crown Royale</t>
+          <t>Magic Unlimited</t>
         </is>
       </c>
       <c r="B95" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C95" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D95" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="22" t="inlineStr">
         <is>
-          <t>Panini Elite</t>
+          <t>Magic: The Gathering (Wizards of the Coast)</t>
         </is>
       </c>
       <c r="B96" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Magic: The Gathering</t>
         </is>
       </c>
       <c r="C96" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D96" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="23" t="inlineStr">
         <is>
-          <t>Panini Encased</t>
+          <t>Marvel Annual</t>
         </is>
       </c>
       <c r="B97" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C97" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D97" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="22" t="inlineStr">
         <is>
-          <t>Panini Flawless</t>
+          <t>Marvel Beginnings</t>
         </is>
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C98" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D98" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="23" t="inlineStr">
         <is>
-          <t>Panini Gold Standard</t>
+          <t>Marvel Black Diamond</t>
         </is>
       </c>
       <c r="B99" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C99" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="22" t="inlineStr">
         <is>
-          <t>Panini Hoops</t>
+          <t>Marvel Fleer</t>
         </is>
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C100" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D100" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="23" t="inlineStr">
         <is>
-          <t>Panini Illusions</t>
+          <t>Marvel Fleer Ultra</t>
         </is>
       </c>
       <c r="B101" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C101" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D101" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="22" t="inlineStr">
         <is>
-          <t>Panini Immaculate Collection</t>
+          <t>Marvel Impel</t>
         </is>
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C102" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D102" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="23" t="inlineStr">
         <is>
-          <t>Panini Impeccable</t>
+          <t>Marvel Masterpieces</t>
         </is>
       </c>
       <c r="B103" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C103" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D103" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="22" t="inlineStr">
         <is>
-          <t>Panini Instant</t>
+          <t>Marvel Metal Universe</t>
         </is>
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C104" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D104" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="23" t="inlineStr">
         <is>
-          <t>Panini Limited</t>
+          <t>Marvel Platinum</t>
         </is>
       </c>
       <c r="B105" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C105" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D105" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="22" t="inlineStr">
         <is>
-          <t>Panini Luminance</t>
+          <t>Marvel Premier</t>
         </is>
       </c>
       <c r="B106" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C106" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D106" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="23" t="inlineStr">
         <is>
-          <t>Panini Mosaic</t>
+          <t>Marvel Rittenhouse</t>
         </is>
       </c>
       <c r="B107" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C107" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D107" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="22" t="inlineStr">
         <is>
-          <t>Panini National Treasures</t>
+          <t>Marvel SkyBox</t>
         </is>
       </c>
       <c r="B108" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C108" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D108" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="23" t="inlineStr">
         <is>
-          <t>Panini NBA Hoops</t>
+          <t>Marvel Topps</t>
         </is>
       </c>
       <c r="B109" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C109" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D109" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="22" t="inlineStr">
         <is>
-          <t>Panini Noir</t>
+          <t>Marvel Universe</t>
         </is>
       </c>
       <c r="B110" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C110" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D110" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="23" t="inlineStr">
         <is>
-          <t>Panini Obsidian</t>
+          <t>Marvel Upper Deck</t>
         </is>
       </c>
       <c r="B111" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Marvel</t>
         </is>
       </c>
       <c r="C111" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D111" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="22" t="inlineStr">
         <is>
-          <t>Panini One</t>
+          <t>Mother's Cookies</t>
         </is>
       </c>
       <c r="B112" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C112" s="22" t="inlineStr">
@@ -49666,17 +49669,17 @@
     <row r="113">
       <c r="A113" s="23" t="inlineStr">
         <is>
-          <t>Panini One and One</t>
+          <t>O-Pee-Chee</t>
         </is>
       </c>
       <c r="B113" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>O-Pee-Chee</t>
         </is>
       </c>
       <c r="C113" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D113" s="23" t="inlineStr">
@@ -49688,12 +49691,12 @@
     <row r="114">
       <c r="A114" s="22" t="inlineStr">
         <is>
-          <t>Panini Origins</t>
+          <t>O-Pee-Chee Premier</t>
         </is>
       </c>
       <c r="B114" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>O-Pee-Chee</t>
         </is>
       </c>
       <c r="C114" s="22" t="inlineStr">
@@ -49710,12 +49713,12 @@
     <row r="115">
       <c r="A115" s="23" t="inlineStr">
         <is>
-          <t>Panini Phoenix</t>
+          <t>Onyx</t>
         </is>
       </c>
       <c r="B115" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C115" s="23" t="inlineStr">
@@ -49732,17 +49735,17 @@
     <row r="116">
       <c r="A116" s="22" t="inlineStr">
         <is>
-          <t>Panini Playbook</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="B116" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C116" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D116" s="22" t="inlineStr">
@@ -49754,12 +49757,12 @@
     <row r="117">
       <c r="A117" s="23" t="inlineStr">
         <is>
-          <t>Panini Prestige</t>
+          <t>Pacific Cramer</t>
         </is>
       </c>
       <c r="B117" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C117" s="23" t="inlineStr">
@@ -49776,12 +49779,12 @@
     <row r="118">
       <c r="A118" s="22" t="inlineStr">
         <is>
-          <t>Panini Prizm</t>
+          <t>Pacific Crown Royale</t>
         </is>
       </c>
       <c r="B118" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C118" s="22" t="inlineStr">
@@ -49798,12 +49801,12 @@
     <row r="119">
       <c r="A119" s="23" t="inlineStr">
         <is>
-          <t>Panini Revolution</t>
+          <t>Pacific Invincible</t>
         </is>
       </c>
       <c r="B119" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C119" s="23" t="inlineStr">
@@ -49820,12 +49823,12 @@
     <row r="120">
       <c r="A120" s="22" t="inlineStr">
         <is>
-          <t>Panini Select</t>
+          <t>Pacific Prism</t>
         </is>
       </c>
       <c r="B120" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C120" s="22" t="inlineStr">
@@ -49842,12 +49845,12 @@
     <row r="121">
       <c r="A121" s="23" t="inlineStr">
         <is>
-          <t>Panini Spectra</t>
+          <t>Pacific Private Stock</t>
         </is>
       </c>
       <c r="B121" s="23" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C121" s="23" t="inlineStr">
@@ -49864,12 +49867,12 @@
     <row r="122">
       <c r="A122" s="22" t="inlineStr">
         <is>
-          <t>Panini XR</t>
+          <t>Pacific Prizm</t>
         </is>
       </c>
       <c r="B122" s="22" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C122" s="22" t="inlineStr">
@@ -49886,12 +49889,12 @@
     <row r="123">
       <c r="A123" s="23" t="inlineStr">
         <is>
-          <t>Parkhurst</t>
+          <t>Pacific Revolution</t>
         </is>
       </c>
       <c r="B123" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C123" s="23" t="inlineStr">
@@ -49908,17 +49911,17 @@
     <row r="124">
       <c r="A124" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Pacific Titanium</t>
         </is>
       </c>
       <c r="B124" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C124" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D124" s="22" t="inlineStr">
@@ -49930,12 +49933,12 @@
     <row r="125">
       <c r="A125" s="23" t="inlineStr">
         <is>
-          <t>Pinnacle Aficionado</t>
+          <t>Pacific Vanguard</t>
         </is>
       </c>
       <c r="B125" s="23" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Pacific</t>
         </is>
       </c>
       <c r="C125" s="23" t="inlineStr">
@@ -49952,17 +49955,17 @@
     <row r="126">
       <c r="A126" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle Certified</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="B126" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C126" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D126" s="22" t="inlineStr">
@@ -49974,12 +49977,12 @@
     <row r="127">
       <c r="A127" s="23" t="inlineStr">
         <is>
-          <t>Pinnacle Inside</t>
+          <t>Panini Absolute</t>
         </is>
       </c>
       <c r="B127" s="23" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C127" s="23" t="inlineStr">
@@ -49996,12 +49999,12 @@
     <row r="128">
       <c r="A128" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle Zenith</t>
+          <t>Panini Adrenalyn XL</t>
         </is>
       </c>
       <c r="B128" s="22" t="inlineStr">
         <is>
-          <t>Pinnacle</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C128" s="22" t="inlineStr">
@@ -50018,12 +50021,12 @@
     <row r="129">
       <c r="A129" s="23" t="inlineStr">
         <is>
-          <t>Post</t>
+          <t>Panini Black</t>
         </is>
       </c>
       <c r="B129" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C129" s="23" t="inlineStr">
@@ -50040,17 +50043,17 @@
     <row r="130">
       <c r="A130" s="22" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini Certified</t>
         </is>
       </c>
       <c r="B130" s="22" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C130" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D130" s="22" t="inlineStr">
@@ -50062,12 +50065,12 @@
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
-          <t>Press Pass Eclipse</t>
+          <t>Panini Chronicles</t>
         </is>
       </c>
       <c r="B131" s="23" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C131" s="23" t="inlineStr">
@@ -50084,12 +50087,12 @@
     <row r="132">
       <c r="A132" s="22" t="inlineStr">
         <is>
-          <t>Press Pass Legends</t>
+          <t>Panini Contenders</t>
         </is>
       </c>
       <c r="B132" s="22" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C132" s="22" t="inlineStr">
@@ -50106,12 +50109,12 @@
     <row r="133">
       <c r="A133" s="23" t="inlineStr">
         <is>
-          <t>Press Pass Premium</t>
+          <t>Panini Contenders Optic</t>
         </is>
       </c>
       <c r="B133" s="23" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C133" s="23" t="inlineStr">
@@ -50128,12 +50131,12 @@
     <row r="134">
       <c r="A134" s="22" t="inlineStr">
         <is>
-          <t>Press Pass SE</t>
+          <t>Panini Court Kings</t>
         </is>
       </c>
       <c r="B134" s="22" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C134" s="22" t="inlineStr">
@@ -50150,12 +50153,12 @@
     <row r="135">
       <c r="A135" s="23" t="inlineStr">
         <is>
-          <t>Press Pass Showcase</t>
+          <t>Panini Crown Royale</t>
         </is>
       </c>
       <c r="B135" s="23" t="inlineStr">
         <is>
-          <t>Press Pass</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C135" s="23" t="inlineStr">
@@ -50172,17 +50175,17 @@
     <row r="136">
       <c r="A136" s="22" t="inlineStr">
         <is>
-          <t>Pro Set</t>
+          <t>Panini Elite</t>
         </is>
       </c>
       <c r="B136" s="22" t="inlineStr">
         <is>
-          <t>Pro Set</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C136" s="22" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D136" s="22" t="inlineStr">
@@ -50194,12 +50197,12 @@
     <row r="137">
       <c r="A137" s="23" t="inlineStr">
         <is>
-          <t>Pro Set Platinum</t>
+          <t>Panini Encased</t>
         </is>
       </c>
       <c r="B137" s="23" t="inlineStr">
         <is>
-          <t>Pro Set</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C137" s="23" t="inlineStr">
@@ -50216,12 +50219,12 @@
     <row r="138">
       <c r="A138" s="22" t="inlineStr">
         <is>
-          <t>Pro Set Power</t>
+          <t>Panini Flawless</t>
         </is>
       </c>
       <c r="B138" s="22" t="inlineStr">
         <is>
-          <t>Pro Set</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C138" s="22" t="inlineStr">
@@ -50238,12 +50241,12 @@
     <row r="139">
       <c r="A139" s="23" t="inlineStr">
         <is>
-          <t>Rittenhouse</t>
+          <t>Panini Gold Standard</t>
         </is>
       </c>
       <c r="B139" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C139" s="23" t="inlineStr">
@@ -50260,12 +50263,12 @@
     <row r="140">
       <c r="A140" s="22" t="inlineStr">
         <is>
-          <t>Royal Rookies</t>
+          <t>Panini Hoops</t>
         </is>
       </c>
       <c r="B140" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C140" s="22" t="inlineStr">
@@ -50282,17 +50285,17 @@
     <row r="141">
       <c r="A141" s="23" t="inlineStr">
         <is>
-          <t>SAGE</t>
+          <t>Panini Illusions</t>
         </is>
       </c>
       <c r="B141" s="23" t="inlineStr">
         <is>
-          <t>SAGE</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C141" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D141" s="23" t="inlineStr">
@@ -50304,12 +50307,12 @@
     <row r="142">
       <c r="A142" s="22" t="inlineStr">
         <is>
-          <t>SAGE Aspire</t>
+          <t>Panini Immaculate Collection</t>
         </is>
       </c>
       <c r="B142" s="22" t="inlineStr">
         <is>
-          <t>SAGE</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C142" s="22" t="inlineStr">
@@ -50326,12 +50329,12 @@
     <row r="143">
       <c r="A143" s="23" t="inlineStr">
         <is>
-          <t>SAGE Autographed</t>
+          <t>Panini Impeccable</t>
         </is>
       </c>
       <c r="B143" s="23" t="inlineStr">
         <is>
-          <t>SAGE</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C143" s="23" t="inlineStr">
@@ -50348,12 +50351,12 @@
     <row r="144">
       <c r="A144" s="22" t="inlineStr">
         <is>
-          <t>SAGE HIT</t>
+          <t>Panini Instant</t>
         </is>
       </c>
       <c r="B144" s="22" t="inlineStr">
         <is>
-          <t>SAGE</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C144" s="22" t="inlineStr">
@@ -50370,17 +50373,17 @@
     <row r="145">
       <c r="A145" s="23" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Panini Limited</t>
         </is>
       </c>
       <c r="B145" s="23" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C145" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D145" s="23" t="inlineStr">
@@ -50392,12 +50395,12 @@
     <row r="146">
       <c r="A146" s="22" t="inlineStr">
         <is>
-          <t>Score Pinnacle</t>
+          <t>Panini Luminance</t>
         </is>
       </c>
       <c r="B146" s="22" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C146" s="22" t="inlineStr">
@@ -50414,12 +50417,12 @@
     <row r="147">
       <c r="A147" s="23" t="inlineStr">
         <is>
-          <t>Score Select</t>
+          <t>Panini Mosaic</t>
         </is>
       </c>
       <c r="B147" s="23" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C147" s="23" t="inlineStr">
@@ -50436,12 +50439,12 @@
     <row r="148">
       <c r="A148" s="22" t="inlineStr">
         <is>
-          <t>Score Summit</t>
+          <t>Panini National Treasures</t>
         </is>
       </c>
       <c r="B148" s="22" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C148" s="22" t="inlineStr">
@@ -50458,17 +50461,17 @@
     <row r="149">
       <c r="A149" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini NBA Hoops</t>
         </is>
       </c>
       <c r="B149" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C149" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D149" s="23" t="inlineStr">
@@ -50480,12 +50483,12 @@
     <row r="150">
       <c r="A150" s="22" t="inlineStr">
         <is>
-          <t>SkyBox Autographics</t>
+          <t>Panini Noir</t>
         </is>
       </c>
       <c r="B150" s="22" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C150" s="22" t="inlineStr">
@@ -50502,12 +50505,12 @@
     <row r="151">
       <c r="A151" s="23" t="inlineStr">
         <is>
-          <t>SkyBox Dominion</t>
+          <t>Panini Obsidian</t>
         </is>
       </c>
       <c r="B151" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C151" s="23" t="inlineStr">
@@ -50524,12 +50527,12 @@
     <row r="152">
       <c r="A152" s="22" t="inlineStr">
         <is>
-          <t>SkyBox E-X</t>
+          <t>Panini One</t>
         </is>
       </c>
       <c r="B152" s="22" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C152" s="22" t="inlineStr">
@@ -50546,12 +50549,12 @@
     <row r="153">
       <c r="A153" s="23" t="inlineStr">
         <is>
-          <t>SkyBox E-X2000</t>
+          <t>Panini One and One</t>
         </is>
       </c>
       <c r="B153" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C153" s="23" t="inlineStr">
@@ -50568,12 +50571,12 @@
     <row r="154">
       <c r="A154" s="22" t="inlineStr">
         <is>
-          <t>SkyBox E-X2001</t>
+          <t>Panini Origins</t>
         </is>
       </c>
       <c r="B154" s="22" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C154" s="22" t="inlineStr">
@@ -50590,12 +50593,12 @@
     <row r="155">
       <c r="A155" s="23" t="inlineStr">
         <is>
-          <t>SkyBox Metal Universe</t>
+          <t>Panini Phoenix</t>
         </is>
       </c>
       <c r="B155" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C155" s="23" t="inlineStr">
@@ -50612,12 +50615,12 @@
     <row r="156">
       <c r="A156" s="22" t="inlineStr">
         <is>
-          <t>SkyBox Premium</t>
+          <t>Panini Playbook</t>
         </is>
       </c>
       <c r="B156" s="22" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C156" s="22" t="inlineStr">
@@ -50634,12 +50637,12 @@
     <row r="157">
       <c r="A157" s="23" t="inlineStr">
         <is>
-          <t>SkyBox Z-Force</t>
+          <t>Panini Prestige</t>
         </is>
       </c>
       <c r="B157" s="23" t="inlineStr">
         <is>
-          <t>SkyBox</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C157" s="23" t="inlineStr">
@@ -50656,12 +50659,12 @@
     <row r="158">
       <c r="A158" s="22" t="inlineStr">
         <is>
-          <t>Sport Kings</t>
+          <t>Panini Prizm</t>
         </is>
       </c>
       <c r="B158" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C158" s="22" t="inlineStr">
@@ -50678,12 +50681,12 @@
     <row r="159">
       <c r="A159" s="23" t="inlineStr">
         <is>
-          <t>TCMA</t>
+          <t>Panini Revolution</t>
         </is>
       </c>
       <c r="B159" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C159" s="23" t="inlineStr">
@@ -50700,12 +50703,12 @@
     <row r="160">
       <c r="A160" s="22" t="inlineStr">
         <is>
-          <t>Tobacco cards (T-series)</t>
+          <t>Panini Select</t>
         </is>
       </c>
       <c r="B160" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C160" s="22" t="inlineStr">
@@ -50722,17 +50725,17 @@
     <row r="161">
       <c r="A161" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Panini Spectra</t>
         </is>
       </c>
       <c r="B161" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C161" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D161" s="23" t="inlineStr">
@@ -50744,12 +50747,12 @@
     <row r="162">
       <c r="A162" s="22" t="inlineStr">
         <is>
-          <t>Topps Allen &amp; Ginter</t>
+          <t>Panini XR</t>
         </is>
       </c>
       <c r="B162" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="C162" s="22" t="inlineStr">
@@ -50766,12 +50769,12 @@
     <row r="163">
       <c r="A163" s="23" t="inlineStr">
         <is>
-          <t>Topps Archives</t>
+          <t>Parkhurst</t>
         </is>
       </c>
       <c r="B163" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C163" s="23" t="inlineStr">
@@ -50788,17 +50791,17 @@
     <row r="164">
       <c r="A164" s="22" t="inlineStr">
         <is>
-          <t>Topps Archives Signature Series</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="B164" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="C164" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D164" s="22" t="inlineStr">
@@ -50810,12 +50813,12 @@
     <row r="165">
       <c r="A165" s="23" t="inlineStr">
         <is>
-          <t>Topps Big League</t>
+          <t>Pinnacle Aficionado</t>
         </is>
       </c>
       <c r="B165" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="C165" s="23" t="inlineStr">
@@ -50832,12 +50835,12 @@
     <row r="166">
       <c r="A166" s="22" t="inlineStr">
         <is>
-          <t>Topps Bundesliga</t>
+          <t>Pinnacle Certified</t>
         </is>
       </c>
       <c r="B166" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="C166" s="22" t="inlineStr">
@@ -50854,12 +50857,12 @@
     <row r="167">
       <c r="A167" s="23" t="inlineStr">
         <is>
-          <t>Topps Chrome</t>
+          <t>Pinnacle Inside</t>
         </is>
       </c>
       <c r="B167" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="C167" s="23" t="inlineStr">
@@ -50876,12 +50879,12 @@
     <row r="168">
       <c r="A168" s="22" t="inlineStr">
         <is>
-          <t>Topps Chrome Black</t>
+          <t>Pinnacle Zenith</t>
         </is>
       </c>
       <c r="B168" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pinnacle</t>
         </is>
       </c>
       <c r="C168" s="22" t="inlineStr">
@@ -50898,254 +50901,254 @@
     <row r="169">
       <c r="A169" s="23" t="inlineStr">
         <is>
-          <t>Topps Chrome Platinum Anniversary</t>
+          <t>Pokémon Black &amp; White Series</t>
         </is>
       </c>
       <c r="B169" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C169" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D169" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="22" t="inlineStr">
         <is>
-          <t>Topps Chrome Sapphire</t>
+          <t>Pokémon Diamond &amp; Pearl Series</t>
         </is>
       </c>
       <c r="B170" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C170" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D170" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="23" t="inlineStr">
         <is>
-          <t>Topps Chrome Update</t>
+          <t>Pokémon EX Series</t>
         </is>
       </c>
       <c r="B171" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C171" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D171" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="22" t="inlineStr">
         <is>
-          <t>Topps Cosmic Chrome</t>
+          <t>Pokémon HeartGold &amp; SoulSilver Series</t>
         </is>
       </c>
       <c r="B172" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C172" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D172" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="23" t="inlineStr">
         <is>
-          <t>Topps Definitive</t>
+          <t>Pokémon Platinum Series</t>
         </is>
       </c>
       <c r="B173" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C173" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D173" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="22" t="inlineStr">
         <is>
-          <t>Topps Dynasty</t>
+          <t>Pokémon Scarlet &amp; Violet Series</t>
         </is>
       </c>
       <c r="B174" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C174" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D174" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="23" t="inlineStr">
         <is>
-          <t>Topps Finest</t>
+          <t>Pokémon Sun &amp; Moon Series</t>
         </is>
       </c>
       <c r="B175" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C175" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D175" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="22" t="inlineStr">
         <is>
-          <t>Topps Fire</t>
+          <t>Pokémon Sword &amp; Shield Series</t>
         </is>
       </c>
       <c r="B176" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C176" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D176" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="23" t="inlineStr">
         <is>
-          <t>Topps Five Star</t>
+          <t>Pokémon TCG</t>
         </is>
       </c>
       <c r="B177" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C177" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D177" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="22" t="inlineStr">
         <is>
-          <t>Topps Gallery</t>
+          <t>Pokémon Wizards of the Coast era</t>
         </is>
       </c>
       <c r="B178" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C178" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D178" s="22" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="23" t="inlineStr">
         <is>
-          <t>Topps Gold Label</t>
+          <t>Pokémon XY Series</t>
         </is>
       </c>
       <c r="B179" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pokémon</t>
         </is>
       </c>
       <c r="C179" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Trading-card franchise / product label</t>
         </is>
       </c>
       <c r="D179" s="23" t="inlineStr">
         <is>
-          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+          <t>Representative franchise/product label, not an exhaustive set checklist. Record the exact set and language in your inventory notes.</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="22" t="inlineStr">
         <is>
-          <t>Topps Gypsy Queen</t>
+          <t>Post</t>
         </is>
       </c>
       <c r="B180" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C180" s="22" t="inlineStr">
@@ -51162,17 +51165,17 @@
     <row r="181">
       <c r="A181" s="23" t="inlineStr">
         <is>
-          <t>Topps Heritage</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="B181" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C181" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D181" s="23" t="inlineStr">
@@ -51184,12 +51187,12 @@
     <row r="182">
       <c r="A182" s="22" t="inlineStr">
         <is>
-          <t>Topps Inception</t>
+          <t>Press Pass Eclipse</t>
         </is>
       </c>
       <c r="B182" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C182" s="22" t="inlineStr">
@@ -51206,12 +51209,12 @@
     <row r="183">
       <c r="A183" s="23" t="inlineStr">
         <is>
-          <t>Topps Living Set</t>
+          <t>Press Pass Legends</t>
         </is>
       </c>
       <c r="B183" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C183" s="23" t="inlineStr">
@@ -51228,12 +51231,12 @@
     <row r="184">
       <c r="A184" s="22" t="inlineStr">
         <is>
-          <t>Topps Match Attax</t>
+          <t>Press Pass Premium</t>
         </is>
       </c>
       <c r="B184" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C184" s="22" t="inlineStr">
@@ -51250,12 +51253,12 @@
     <row r="185">
       <c r="A185" s="23" t="inlineStr">
         <is>
-          <t>Topps Museum Collection</t>
+          <t>Press Pass SE</t>
         </is>
       </c>
       <c r="B185" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C185" s="23" t="inlineStr">
@@ -51272,12 +51275,12 @@
     <row r="186">
       <c r="A186" s="22" t="inlineStr">
         <is>
-          <t>Topps NOW</t>
+          <t>Press Pass Showcase</t>
         </is>
       </c>
       <c r="B186" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Press Pass</t>
         </is>
       </c>
       <c r="C186" s="22" t="inlineStr">
@@ -51294,17 +51297,17 @@
     <row r="187">
       <c r="A187" s="23" t="inlineStr">
         <is>
-          <t>Topps Opening Day</t>
+          <t>Pro Set</t>
         </is>
       </c>
       <c r="B187" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pro Set</t>
         </is>
       </c>
       <c r="C187" s="23" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D187" s="23" t="inlineStr">
@@ -51316,12 +51319,12 @@
     <row r="188">
       <c r="A188" s="22" t="inlineStr">
         <is>
-          <t>Topps Pro Debut</t>
+          <t>Pro Set Platinum</t>
         </is>
       </c>
       <c r="B188" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pro Set</t>
         </is>
       </c>
       <c r="C188" s="22" t="inlineStr">
@@ -51338,12 +51341,12 @@
     <row r="189">
       <c r="A189" s="23" t="inlineStr">
         <is>
-          <t>Topps Stadium Club</t>
+          <t>Pro Set Power</t>
         </is>
       </c>
       <c r="B189" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Pro Set</t>
         </is>
       </c>
       <c r="C189" s="23" t="inlineStr">
@@ -51360,12 +51363,12 @@
     <row r="190">
       <c r="A190" s="22" t="inlineStr">
         <is>
-          <t>Topps Stadium Club Chrome</t>
+          <t>Rittenhouse</t>
         </is>
       </c>
       <c r="B190" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C190" s="22" t="inlineStr">
@@ -51382,12 +51385,12 @@
     <row r="191">
       <c r="A191" s="23" t="inlineStr">
         <is>
-          <t>Topps T206</t>
+          <t>Royal Rookies</t>
         </is>
       </c>
       <c r="B191" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C191" s="23" t="inlineStr">
@@ -51404,17 +51407,17 @@
     <row r="192">
       <c r="A192" s="22" t="inlineStr">
         <is>
-          <t>Topps Tier One</t>
+          <t>SAGE</t>
         </is>
       </c>
       <c r="B192" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>SAGE</t>
         </is>
       </c>
       <c r="C192" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D192" s="22" t="inlineStr">
@@ -51426,12 +51429,12 @@
     <row r="193">
       <c r="A193" s="23" t="inlineStr">
         <is>
-          <t>Topps Transcendent</t>
+          <t>SAGE Aspire</t>
         </is>
       </c>
       <c r="B193" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>SAGE</t>
         </is>
       </c>
       <c r="C193" s="23" t="inlineStr">
@@ -51448,12 +51451,12 @@
     <row r="194">
       <c r="A194" s="22" t="inlineStr">
         <is>
-          <t>Topps Tribute</t>
+          <t>SAGE Autographed</t>
         </is>
       </c>
       <c r="B194" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>SAGE</t>
         </is>
       </c>
       <c r="C194" s="22" t="inlineStr">
@@ -51470,12 +51473,12 @@
     <row r="195">
       <c r="A195" s="23" t="inlineStr">
         <is>
-          <t>Topps Triple Threads</t>
+          <t>SAGE HIT</t>
         </is>
       </c>
       <c r="B195" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>SAGE</t>
         </is>
       </c>
       <c r="C195" s="23" t="inlineStr">
@@ -51492,17 +51495,17 @@
     <row r="196">
       <c r="A196" s="22" t="inlineStr">
         <is>
-          <t>Topps UEFA Club Competitions</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="B196" s="22" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="C196" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D196" s="22" t="inlineStr">
@@ -51514,12 +51517,12 @@
     <row r="197">
       <c r="A197" s="23" t="inlineStr">
         <is>
-          <t>Topps Update</t>
+          <t>Score Pinnacle</t>
         </is>
       </c>
       <c r="B197" s="23" t="inlineStr">
         <is>
-          <t>Topps</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="C197" s="23" t="inlineStr">
@@ -51536,12 +51539,12 @@
     <row r="198">
       <c r="A198" s="22" t="inlineStr">
         <is>
-          <t>Tristar</t>
+          <t>Score Select</t>
         </is>
       </c>
       <c r="B198" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="C198" s="22" t="inlineStr">
@@ -51558,12 +51561,12 @@
     <row r="199">
       <c r="A199" s="23" t="inlineStr">
         <is>
-          <t>Tristar Hidden Treasures</t>
+          <t>Score Summit</t>
         </is>
       </c>
       <c r="B199" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="C199" s="23" t="inlineStr">
@@ -51580,17 +51583,17 @@
     <row r="200">
       <c r="A200" s="22" t="inlineStr">
         <is>
-          <t>Tristar Obak</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="B200" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C200" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D200" s="22" t="inlineStr">
@@ -51602,17 +51605,17 @@
     <row r="201">
       <c r="A201" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox Autographics</t>
         </is>
       </c>
       <c r="B201" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C201" s="23" t="inlineStr">
         <is>
-          <t>Brand / maker</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D201" s="23" t="inlineStr">
@@ -51624,12 +51627,12 @@
     <row r="202">
       <c r="A202" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Allure</t>
+          <t>SkyBox Dominion</t>
         </is>
       </c>
       <c r="B202" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C202" s="22" t="inlineStr">
@@ -51646,12 +51649,12 @@
     <row r="203">
       <c r="A203" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Artifacts</t>
+          <t>SkyBox E-X</t>
         </is>
       </c>
       <c r="B203" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C203" s="23" t="inlineStr">
@@ -51668,12 +51671,12 @@
     <row r="204">
       <c r="A204" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Black Diamond</t>
+          <t>SkyBox E-X2000</t>
         </is>
       </c>
       <c r="B204" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C204" s="22" t="inlineStr">
@@ -51690,12 +51693,12 @@
     <row r="205">
       <c r="A205" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck CHL</t>
+          <t>SkyBox E-X2001</t>
         </is>
       </c>
       <c r="B205" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C205" s="23" t="inlineStr">
@@ -51712,12 +51715,12 @@
     <row r="206">
       <c r="A206" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Clear Cut</t>
+          <t>SkyBox Metal Universe</t>
         </is>
       </c>
       <c r="B206" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C206" s="22" t="inlineStr">
@@ -51734,12 +51737,12 @@
     <row r="207">
       <c r="A207" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Credentials</t>
+          <t>SkyBox Premium</t>
         </is>
       </c>
       <c r="B207" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C207" s="23" t="inlineStr">
@@ -51756,12 +51759,12 @@
     <row r="208">
       <c r="A208" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Exquisite Collection</t>
+          <t>SkyBox Z-Force</t>
         </is>
       </c>
       <c r="B208" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>SkyBox</t>
         </is>
       </c>
       <c r="C208" s="22" t="inlineStr">
@@ -51778,12 +51781,12 @@
     <row r="209">
       <c r="A209" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Extended Series</t>
+          <t>Sport Kings</t>
         </is>
       </c>
       <c r="B209" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C209" s="23" t="inlineStr">
@@ -51800,12 +51803,12 @@
     <row r="210">
       <c r="A210" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Goodwin Champions</t>
+          <t>TCMA</t>
         </is>
       </c>
       <c r="B210" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C210" s="22" t="inlineStr">
@@ -51822,12 +51825,12 @@
     <row r="211">
       <c r="A211" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Ice</t>
+          <t>Tobacco cards (T-series)</t>
         </is>
       </c>
       <c r="B211" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Other / historical</t>
         </is>
       </c>
       <c r="C211" s="23" t="inlineStr">
@@ -51844,17 +51847,17 @@
     <row r="212">
       <c r="A212" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck MVP</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="B212" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C212" s="22" t="inlineStr">
         <is>
-          <t>Product line / collecting label</t>
+          <t>Brand / maker</t>
         </is>
       </c>
       <c r="D212" s="22" t="inlineStr">
@@ -51866,12 +51869,12 @@
     <row r="213">
       <c r="A213" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck O-Pee-Chee</t>
+          <t>Topps Allen &amp; Ginter</t>
         </is>
       </c>
       <c r="B213" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C213" s="23" t="inlineStr">
@@ -51888,12 +51891,12 @@
     <row r="214">
       <c r="A214" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck O-Pee-Chee Platinum</t>
+          <t>Topps Archives</t>
         </is>
       </c>
       <c r="B214" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C214" s="22" t="inlineStr">
@@ -51910,12 +51913,12 @@
     <row r="215">
       <c r="A215" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Parkhurst</t>
+          <t>Topps Archives Signature Series</t>
         </is>
       </c>
       <c r="B215" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C215" s="23" t="inlineStr">
@@ -51932,12 +51935,12 @@
     <row r="216">
       <c r="A216" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Parkhurst Champions</t>
+          <t>Topps Big League</t>
         </is>
       </c>
       <c r="B216" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C216" s="22" t="inlineStr">
@@ -51954,12 +51957,12 @@
     <row r="217">
       <c r="A217" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Premier</t>
+          <t>Topps Bundesliga</t>
         </is>
       </c>
       <c r="B217" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C217" s="23" t="inlineStr">
@@ -51976,12 +51979,12 @@
     <row r="218">
       <c r="A218" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Series 1</t>
+          <t>Topps Chrome</t>
         </is>
       </c>
       <c r="B218" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C218" s="22" t="inlineStr">
@@ -51998,12 +52001,12 @@
     <row r="219">
       <c r="A219" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Series 2</t>
+          <t>Topps Chrome Black</t>
         </is>
       </c>
       <c r="B219" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C219" s="23" t="inlineStr">
@@ -52020,12 +52023,12 @@
     <row r="220">
       <c r="A220" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck SP Authentic</t>
+          <t>Topps Chrome Platinum Anniversary</t>
         </is>
       </c>
       <c r="B220" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C220" s="22" t="inlineStr">
@@ -52042,12 +52045,12 @@
     <row r="221">
       <c r="A221" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck SP Game Used</t>
+          <t>Topps Chrome Sapphire</t>
         </is>
       </c>
       <c r="B221" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C221" s="23" t="inlineStr">
@@ -52064,12 +52067,12 @@
     <row r="222">
       <c r="A222" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck SP Signature</t>
+          <t>Topps Chrome Update</t>
         </is>
       </c>
       <c r="B222" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C222" s="22" t="inlineStr">
@@ -52086,12 +52089,12 @@
     <row r="223">
       <c r="A223" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck SPx</t>
+          <t>Topps Cosmic Chrome</t>
         </is>
       </c>
       <c r="B223" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C223" s="23" t="inlineStr">
@@ -52108,12 +52111,12 @@
     <row r="224">
       <c r="A224" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Synergy</t>
+          <t>Topps Definitive</t>
         </is>
       </c>
       <c r="B224" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C224" s="22" t="inlineStr">
@@ -52130,12 +52133,12 @@
     <row r="225">
       <c r="A225" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck The Cup</t>
+          <t>Topps Dynasty</t>
         </is>
       </c>
       <c r="B225" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C225" s="23" t="inlineStr">
@@ -52152,12 +52155,12 @@
     <row r="226">
       <c r="A226" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Trilogy</t>
+          <t>Topps Finest</t>
         </is>
       </c>
       <c r="B226" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C226" s="22" t="inlineStr">
@@ -52174,12 +52177,12 @@
     <row r="227">
       <c r="A227" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck Ultimate Collection</t>
+          <t>Topps Fire</t>
         </is>
       </c>
       <c r="B227" s="23" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C227" s="23" t="inlineStr">
@@ -52196,34 +52199,34 @@
     <row r="228">
       <c r="A228" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck Young Guns</t>
+          <t>Topps Five Star</t>
         </is>
       </c>
       <c r="B228" s="22" t="inlineStr">
         <is>
-          <t>Upper Deck</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C228" s="22" t="inlineStr">
         <is>
-          <t>Insert / rookie subset</t>
+          <t>Product line / collecting label</t>
         </is>
       </c>
       <c r="D228" s="22" t="inlineStr">
         <is>
-          <t>Young Guns is a subset, not a separate manufacturer.</t>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="23" t="inlineStr">
         <is>
-          <t>Wild Card</t>
+          <t>Topps Gallery</t>
         </is>
       </c>
       <c r="B229" s="23" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C229" s="23" t="inlineStr">
@@ -52240,12 +52243,12 @@
     <row r="230">
       <c r="A230" s="22" t="inlineStr">
         <is>
-          <t>Wizards of the Coast MLB Showdown</t>
+          <t>Topps Gold Label</t>
         </is>
       </c>
       <c r="B230" s="22" t="inlineStr">
         <is>
-          <t>Other / historical</t>
+          <t>Topps</t>
         </is>
       </c>
       <c r="C230" s="22" t="inlineStr">
@@ -52262,27 +52265,1149 @@
     <row r="231">
       <c r="A231" s="23" t="inlineStr">
         <is>
+          <t>Topps Gypsy Queen</t>
+        </is>
+      </c>
+      <c r="B231" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C231" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="22" t="inlineStr">
+        <is>
+          <t>Topps Heritage</t>
+        </is>
+      </c>
+      <c r="B232" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C232" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D232" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="23" t="inlineStr">
+        <is>
+          <t>Topps Inception</t>
+        </is>
+      </c>
+      <c r="B233" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C233" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D233" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="22" t="inlineStr">
+        <is>
+          <t>Topps Living Set</t>
+        </is>
+      </c>
+      <c r="B234" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C234" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D234" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="23" t="inlineStr">
+        <is>
+          <t>Topps Match Attax</t>
+        </is>
+      </c>
+      <c r="B235" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C235" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D235" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="22" t="inlineStr">
+        <is>
+          <t>Topps Museum Collection</t>
+        </is>
+      </c>
+      <c r="B236" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C236" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D236" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="23" t="inlineStr">
+        <is>
+          <t>Topps NOW</t>
+        </is>
+      </c>
+      <c r="B237" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C237" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D237" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="22" t="inlineStr">
+        <is>
+          <t>Topps Opening Day</t>
+        </is>
+      </c>
+      <c r="B238" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C238" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D238" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="23" t="inlineStr">
+        <is>
+          <t>Topps Pro Debut</t>
+        </is>
+      </c>
+      <c r="B239" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C239" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D239" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="22" t="inlineStr">
+        <is>
+          <t>Topps Stadium Club</t>
+        </is>
+      </c>
+      <c r="B240" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C240" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D240" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="23" t="inlineStr">
+        <is>
+          <t>Topps Stadium Club Chrome</t>
+        </is>
+      </c>
+      <c r="B241" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C241" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D241" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="22" t="inlineStr">
+        <is>
+          <t>Topps T206</t>
+        </is>
+      </c>
+      <c r="B242" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C242" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D242" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="23" t="inlineStr">
+        <is>
+          <t>Topps Tier One</t>
+        </is>
+      </c>
+      <c r="B243" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C243" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D243" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="22" t="inlineStr">
+        <is>
+          <t>Topps Transcendent</t>
+        </is>
+      </c>
+      <c r="B244" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C244" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D244" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="23" t="inlineStr">
+        <is>
+          <t>Topps Tribute</t>
+        </is>
+      </c>
+      <c r="B245" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C245" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D245" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="22" t="inlineStr">
+        <is>
+          <t>Topps Triple Threads</t>
+        </is>
+      </c>
+      <c r="B246" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C246" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D246" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="23" t="inlineStr">
+        <is>
+          <t>Topps UEFA Club Competitions</t>
+        </is>
+      </c>
+      <c r="B247" s="23" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C247" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D247" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="22" t="inlineStr">
+        <is>
+          <t>Topps Update</t>
+        </is>
+      </c>
+      <c r="B248" s="22" t="inlineStr">
+        <is>
+          <t>Topps</t>
+        </is>
+      </c>
+      <c r="C248" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D248" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="23" t="inlineStr">
+        <is>
+          <t>Tristar</t>
+        </is>
+      </c>
+      <c r="B249" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C249" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D249" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="22" t="inlineStr">
+        <is>
+          <t>Tristar Hidden Treasures</t>
+        </is>
+      </c>
+      <c r="B250" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C250" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D250" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="23" t="inlineStr">
+        <is>
+          <t>Tristar Obak</t>
+        </is>
+      </c>
+      <c r="B251" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C251" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D251" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="B252" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C252" s="22" t="inlineStr">
+        <is>
+          <t>Brand / maker</t>
+        </is>
+      </c>
+      <c r="D252" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Allure</t>
+        </is>
+      </c>
+      <c r="B253" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C253" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D253" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Artifacts</t>
+        </is>
+      </c>
+      <c r="B254" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C254" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D254" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Black Diamond</t>
+        </is>
+      </c>
+      <c r="B255" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C255" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D255" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck CHL</t>
+        </is>
+      </c>
+      <c r="B256" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C256" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D256" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Clear Cut</t>
+        </is>
+      </c>
+      <c r="B257" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C257" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D257" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Credentials</t>
+        </is>
+      </c>
+      <c r="B258" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C258" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D258" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Exquisite Collection</t>
+        </is>
+      </c>
+      <c r="B259" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C259" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D259" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Extended Series</t>
+        </is>
+      </c>
+      <c r="B260" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C260" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D260" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Goodwin Champions</t>
+        </is>
+      </c>
+      <c r="B261" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C261" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D261" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Ice</t>
+        </is>
+      </c>
+      <c r="B262" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C262" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D262" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck MVP</t>
+        </is>
+      </c>
+      <c r="B263" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C263" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D263" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck O-Pee-Chee</t>
+        </is>
+      </c>
+      <c r="B264" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C264" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D264" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck O-Pee-Chee Platinum</t>
+        </is>
+      </c>
+      <c r="B265" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C265" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D265" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Parkhurst</t>
+        </is>
+      </c>
+      <c r="B266" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C266" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D266" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Parkhurst Champions</t>
+        </is>
+      </c>
+      <c r="B267" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C267" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D267" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Premier</t>
+        </is>
+      </c>
+      <c r="B268" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C268" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D268" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Series 1</t>
+        </is>
+      </c>
+      <c r="B269" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C269" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D269" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Series 2</t>
+        </is>
+      </c>
+      <c r="B270" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C270" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D270" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Authentic</t>
+        </is>
+      </c>
+      <c r="B271" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C271" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D271" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Game Used</t>
+        </is>
+      </c>
+      <c r="B272" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C272" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D272" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck SP Signature</t>
+        </is>
+      </c>
+      <c r="B273" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C273" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D273" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck SPx</t>
+        </is>
+      </c>
+      <c r="B274" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C274" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D274" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Synergy</t>
+        </is>
+      </c>
+      <c r="B275" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C275" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D275" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck The Cup</t>
+        </is>
+      </c>
+      <c r="B276" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C276" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D276" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Trilogy</t>
+        </is>
+      </c>
+      <c r="B277" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C277" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D277" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck Ultimate Collection</t>
+        </is>
+      </c>
+      <c r="B278" s="22" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C278" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D278" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck Young Guns</t>
+        </is>
+      </c>
+      <c r="B279" s="23" t="inlineStr">
+        <is>
+          <t>Upper Deck</t>
+        </is>
+      </c>
+      <c r="C279" s="23" t="inlineStr">
+        <is>
+          <t>Insert / rookie subset</t>
+        </is>
+      </c>
+      <c r="D279" s="23" t="inlineStr">
+        <is>
+          <t>Young Guns is a subset, not a separate manufacturer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="22" t="inlineStr">
+        <is>
+          <t>Wild Card</t>
+        </is>
+      </c>
+      <c r="B280" s="22" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C280" s="22" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D280" s="22" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="23" t="inlineStr">
+        <is>
+          <t>Wizards of the Coast MLB Showdown</t>
+        </is>
+      </c>
+      <c r="B281" s="23" t="inlineStr">
+        <is>
+          <t>Other / historical</t>
+        </is>
+      </c>
+      <c r="C281" s="23" t="inlineStr">
+        <is>
+          <t>Product line / collecting label</t>
+        </is>
+      </c>
+      <c r="D281" s="23" t="inlineStr">
+        <is>
+          <t>Historical family label; manufacturer and licensing vary by release year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="22" t="inlineStr">
+        <is>
           <t>Zee-Nut</t>
         </is>
       </c>
-      <c r="B231" s="23" t="inlineStr">
+      <c r="B282" s="22" t="inlineStr">
         <is>
           <t>Other / historical</t>
         </is>
       </c>
-      <c r="C231" s="23" t="inlineStr">
+      <c r="C282" s="22" t="inlineStr">
         <is>
           <t>Product line / collecting label</t>
         </is>
       </c>
-      <c r="D231" s="23" t="inlineStr">
+      <c r="D282" s="22" t="inlineStr">
         <is>
           <t>Historical family label; manufacturer and licensing vary by release year.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D231"/>
+  <autoFilter ref="A1:D282"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/spreadsheet/CardLedger-Google-Sheets.xlsx
+++ b/spreadsheet/CardLedger-Google-Sheets.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Brands &amp; Makes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventory'!$A$1:$P$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Inventory'!$A$1:$S$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Inventory'!$1:$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Sales'!$A$1:$Q$501</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Sales'!$1:$1</definedName>
@@ -695,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P501"/>
+  <dimension ref="A1:S501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -714,6 +714,9 @@
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -795,6 +798,21 @@
       <c r="P1" s="8" t="inlineStr">
         <is>
           <t>Check</t>
+        </is>
+      </c>
+      <c r="Q1" s="8" t="inlineStr">
+        <is>
+          <t>Subset / parallel</t>
+        </is>
+      </c>
+      <c r="R1" s="8" t="inlineStr">
+        <is>
+          <t>Card serial number</t>
+        </is>
+      </c>
+      <c r="S1" s="8" t="inlineStr">
+        <is>
+          <t>Grading certificate #</t>
         </is>
       </c>
     </row>
@@ -830,6 +848,9 @@
         <f>IF(A2="","",IF(COUNTIF($A$2:$A$501,A2)&gt;1,"Duplicate lot ID",IF(OR(B2="",H2="",I2="",J2=""),"Complete required fields",IF(L2&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q2" s="9" t="n"/>
+      <c r="R2" s="9" t="n"/>
+      <c r="S2" s="9" t="n"/>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="14" t="n"/>
@@ -863,6 +884,9 @@
         <f>IF(A3="","",IF(COUNTIF($A$2:$A$501,A3)&gt;1,"Duplicate lot ID",IF(OR(B3="",H3="",I3="",J3=""),"Complete required fields",IF(L3&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q3" s="14" t="n"/>
+      <c r="R3" s="14" t="n"/>
+      <c r="S3" s="14" t="n"/>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="9" t="n"/>
@@ -896,6 +920,9 @@
         <f>IF(A4="","",IF(COUNTIF($A$2:$A$501,A4)&gt;1,"Duplicate lot ID",IF(OR(B4="",H4="",I4="",J4=""),"Complete required fields",IF(L4&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q4" s="9" t="n"/>
+      <c r="R4" s="9" t="n"/>
+      <c r="S4" s="9" t="n"/>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="14" t="n"/>
@@ -929,6 +956,9 @@
         <f>IF(A5="","",IF(COUNTIF($A$2:$A$501,A5)&gt;1,"Duplicate lot ID",IF(OR(B5="",H5="",I5="",J5=""),"Complete required fields",IF(L5&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q5" s="14" t="n"/>
+      <c r="R5" s="14" t="n"/>
+      <c r="S5" s="14" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="9" t="n"/>
@@ -962,6 +992,9 @@
         <f>IF(A6="","",IF(COUNTIF($A$2:$A$501,A6)&gt;1,"Duplicate lot ID",IF(OR(B6="",H6="",I6="",J6=""),"Complete required fields",IF(L6&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q6" s="9" t="n"/>
+      <c r="R6" s="9" t="n"/>
+      <c r="S6" s="9" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="14" t="n"/>
@@ -995,6 +1028,9 @@
         <f>IF(A7="","",IF(COUNTIF($A$2:$A$501,A7)&gt;1,"Duplicate lot ID",IF(OR(B7="",H7="",I7="",J7=""),"Complete required fields",IF(L7&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q7" s="14" t="n"/>
+      <c r="R7" s="14" t="n"/>
+      <c r="S7" s="14" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="9" t="n"/>
@@ -1028,6 +1064,9 @@
         <f>IF(A8="","",IF(COUNTIF($A$2:$A$501,A8)&gt;1,"Duplicate lot ID",IF(OR(B8="",H8="",I8="",J8=""),"Complete required fields",IF(L8&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q8" s="9" t="n"/>
+      <c r="R8" s="9" t="n"/>
+      <c r="S8" s="9" t="n"/>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="14" t="n"/>
@@ -1061,6 +1100,9 @@
         <f>IF(A9="","",IF(COUNTIF($A$2:$A$501,A9)&gt;1,"Duplicate lot ID",IF(OR(B9="",H9="",I9="",J9=""),"Complete required fields",IF(L9&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q9" s="14" t="n"/>
+      <c r="R9" s="14" t="n"/>
+      <c r="S9" s="14" t="n"/>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="9" t="n"/>
@@ -1094,6 +1136,9 @@
         <f>IF(A10="","",IF(COUNTIF($A$2:$A$501,A10)&gt;1,"Duplicate lot ID",IF(OR(B10="",H10="",I10="",J10=""),"Complete required fields",IF(L10&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q10" s="9" t="n"/>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="9" t="n"/>
     </row>
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="14" t="n"/>
@@ -1127,6 +1172,9 @@
         <f>IF(A11="","",IF(COUNTIF($A$2:$A$501,A11)&gt;1,"Duplicate lot ID",IF(OR(B11="",H11="",I11="",J11=""),"Complete required fields",IF(L11&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q11" s="14" t="n"/>
+      <c r="R11" s="14" t="n"/>
+      <c r="S11" s="14" t="n"/>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="9" t="n"/>
@@ -1160,6 +1208,9 @@
         <f>IF(A12="","",IF(COUNTIF($A$2:$A$501,A12)&gt;1,"Duplicate lot ID",IF(OR(B12="",H12="",I12="",J12=""),"Complete required fields",IF(L12&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q12" s="9" t="n"/>
+      <c r="R12" s="9" t="n"/>
+      <c r="S12" s="9" t="n"/>
     </row>
     <row r="13" ht="23" customHeight="1">
       <c r="A13" s="14" t="n"/>
@@ -1193,6 +1244,9 @@
         <f>IF(A13="","",IF(COUNTIF($A$2:$A$501,A13)&gt;1,"Duplicate lot ID",IF(OR(B13="",H13="",I13="",J13=""),"Complete required fields",IF(L13&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q13" s="14" t="n"/>
+      <c r="R13" s="14" t="n"/>
+      <c r="S13" s="14" t="n"/>
     </row>
     <row r="14" ht="23" customHeight="1">
       <c r="A14" s="9" t="n"/>
@@ -1226,6 +1280,9 @@
         <f>IF(A14="","",IF(COUNTIF($A$2:$A$501,A14)&gt;1,"Duplicate lot ID",IF(OR(B14="",H14="",I14="",J14=""),"Complete required fields",IF(L14&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q14" s="9" t="n"/>
+      <c r="R14" s="9" t="n"/>
+      <c r="S14" s="9" t="n"/>
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="A15" s="14" t="n"/>
@@ -1259,6 +1316,9 @@
         <f>IF(A15="","",IF(COUNTIF($A$2:$A$501,A15)&gt;1,"Duplicate lot ID",IF(OR(B15="",H15="",I15="",J15=""),"Complete required fields",IF(L15&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q15" s="14" t="n"/>
+      <c r="R15" s="14" t="n"/>
+      <c r="S15" s="14" t="n"/>
     </row>
     <row r="16" ht="23" customHeight="1">
       <c r="A16" s="9" t="n"/>
@@ -1292,6 +1352,9 @@
         <f>IF(A16="","",IF(COUNTIF($A$2:$A$501,A16)&gt;1,"Duplicate lot ID",IF(OR(B16="",H16="",I16="",J16=""),"Complete required fields",IF(L16&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q16" s="9" t="n"/>
+      <c r="R16" s="9" t="n"/>
+      <c r="S16" s="9" t="n"/>
     </row>
     <row r="17" ht="23" customHeight="1">
       <c r="A17" s="14" t="n"/>
@@ -1325,6 +1388,9 @@
         <f>IF(A17="","",IF(COUNTIF($A$2:$A$501,A17)&gt;1,"Duplicate lot ID",IF(OR(B17="",H17="",I17="",J17=""),"Complete required fields",IF(L17&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q17" s="14" t="n"/>
+      <c r="R17" s="14" t="n"/>
+      <c r="S17" s="14" t="n"/>
     </row>
     <row r="18" ht="23" customHeight="1">
       <c r="A18" s="9" t="n"/>
@@ -1358,6 +1424,9 @@
         <f>IF(A18="","",IF(COUNTIF($A$2:$A$501,A18)&gt;1,"Duplicate lot ID",IF(OR(B18="",H18="",I18="",J18=""),"Complete required fields",IF(L18&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="9" t="n"/>
     </row>
     <row r="19" ht="23" customHeight="1">
       <c r="A19" s="14" t="n"/>
@@ -1391,6 +1460,9 @@
         <f>IF(A19="","",IF(COUNTIF($A$2:$A$501,A19)&gt;1,"Duplicate lot ID",IF(OR(B19="",H19="",I19="",J19=""),"Complete required fields",IF(L19&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q19" s="14" t="n"/>
+      <c r="R19" s="14" t="n"/>
+      <c r="S19" s="14" t="n"/>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="9" t="n"/>
@@ -1424,6 +1496,9 @@
         <f>IF(A20="","",IF(COUNTIF($A$2:$A$501,A20)&gt;1,"Duplicate lot ID",IF(OR(B20="",H20="",I20="",J20=""),"Complete required fields",IF(L20&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="9" t="n"/>
     </row>
     <row r="21" ht="23" customHeight="1">
       <c r="A21" s="14" t="n"/>
@@ -1457,6 +1532,9 @@
         <f>IF(A21="","",IF(COUNTIF($A$2:$A$501,A21)&gt;1,"Duplicate lot ID",IF(OR(B21="",H21="",I21="",J21=""),"Complete required fields",IF(L21&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q21" s="14" t="n"/>
+      <c r="R21" s="14" t="n"/>
+      <c r="S21" s="14" t="n"/>
     </row>
     <row r="22" ht="23" customHeight="1">
       <c r="A22" s="9" t="n"/>
@@ -1490,6 +1568,9 @@
         <f>IF(A22="","",IF(COUNTIF($A$2:$A$501,A22)&gt;1,"Duplicate lot ID",IF(OR(B22="",H22="",I22="",J22=""),"Complete required fields",IF(L22&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q22" s="9" t="n"/>
+      <c r="R22" s="9" t="n"/>
+      <c r="S22" s="9" t="n"/>
     </row>
     <row r="23" ht="23" customHeight="1">
       <c r="A23" s="14" t="n"/>
@@ -1523,6 +1604,9 @@
         <f>IF(A23="","",IF(COUNTIF($A$2:$A$501,A23)&gt;1,"Duplicate lot ID",IF(OR(B23="",H23="",I23="",J23=""),"Complete required fields",IF(L23&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q23" s="14" t="n"/>
+      <c r="R23" s="14" t="n"/>
+      <c r="S23" s="14" t="n"/>
     </row>
     <row r="24" ht="23" customHeight="1">
       <c r="A24" s="9" t="n"/>
@@ -1556,6 +1640,9 @@
         <f>IF(A24="","",IF(COUNTIF($A$2:$A$501,A24)&gt;1,"Duplicate lot ID",IF(OR(B24="",H24="",I24="",J24=""),"Complete required fields",IF(L24&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q24" s="9" t="n"/>
+      <c r="R24" s="9" t="n"/>
+      <c r="S24" s="9" t="n"/>
     </row>
     <row r="25" ht="23" customHeight="1">
       <c r="A25" s="14" t="n"/>
@@ -1589,6 +1676,9 @@
         <f>IF(A25="","",IF(COUNTIF($A$2:$A$501,A25)&gt;1,"Duplicate lot ID",IF(OR(B25="",H25="",I25="",J25=""),"Complete required fields",IF(L25&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q25" s="14" t="n"/>
+      <c r="R25" s="14" t="n"/>
+      <c r="S25" s="14" t="n"/>
     </row>
     <row r="26" ht="23" customHeight="1">
       <c r="A26" s="9" t="n"/>
@@ -1622,6 +1712,9 @@
         <f>IF(A26="","",IF(COUNTIF($A$2:$A$501,A26)&gt;1,"Duplicate lot ID",IF(OR(B26="",H26="",I26="",J26=""),"Complete required fields",IF(L26&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q26" s="9" t="n"/>
+      <c r="R26" s="9" t="n"/>
+      <c r="S26" s="9" t="n"/>
     </row>
     <row r="27" ht="23" customHeight="1">
       <c r="A27" s="14" t="n"/>
@@ -1655,6 +1748,9 @@
         <f>IF(A27="","",IF(COUNTIF($A$2:$A$501,A27)&gt;1,"Duplicate lot ID",IF(OR(B27="",H27="",I27="",J27=""),"Complete required fields",IF(L27&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q27" s="14" t="n"/>
+      <c r="R27" s="14" t="n"/>
+      <c r="S27" s="14" t="n"/>
     </row>
     <row r="28" ht="23" customHeight="1">
       <c r="A28" s="9" t="n"/>
@@ -1688,6 +1784,9 @@
         <f>IF(A28="","",IF(COUNTIF($A$2:$A$501,A28)&gt;1,"Duplicate lot ID",IF(OR(B28="",H28="",I28="",J28=""),"Complete required fields",IF(L28&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q28" s="9" t="n"/>
+      <c r="R28" s="9" t="n"/>
+      <c r="S28" s="9" t="n"/>
     </row>
     <row r="29" ht="23" customHeight="1">
       <c r="A29" s="14" t="n"/>
@@ -1721,6 +1820,9 @@
         <f>IF(A29="","",IF(COUNTIF($A$2:$A$501,A29)&gt;1,"Duplicate lot ID",IF(OR(B29="",H29="",I29="",J29=""),"Complete required fields",IF(L29&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q29" s="14" t="n"/>
+      <c r="R29" s="14" t="n"/>
+      <c r="S29" s="14" t="n"/>
     </row>
     <row r="30" ht="23" customHeight="1">
       <c r="A30" s="9" t="n"/>
@@ -1754,6 +1856,9 @@
         <f>IF(A30="","",IF(COUNTIF($A$2:$A$501,A30)&gt;1,"Duplicate lot ID",IF(OR(B30="",H30="",I30="",J30=""),"Complete required fields",IF(L30&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q30" s="9" t="n"/>
+      <c r="R30" s="9" t="n"/>
+      <c r="S30" s="9" t="n"/>
     </row>
     <row r="31" ht="23" customHeight="1">
       <c r="A31" s="14" t="n"/>
@@ -1787,6 +1892,9 @@
         <f>IF(A31="","",IF(COUNTIF($A$2:$A$501,A31)&gt;1,"Duplicate lot ID",IF(OR(B31="",H31="",I31="",J31=""),"Complete required fields",IF(L31&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q31" s="14" t="n"/>
+      <c r="R31" s="14" t="n"/>
+      <c r="S31" s="14" t="n"/>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="9" t="n"/>
@@ -1820,6 +1928,9 @@
         <f>IF(A32="","",IF(COUNTIF($A$2:$A$501,A32)&gt;1,"Duplicate lot ID",IF(OR(B32="",H32="",I32="",J32=""),"Complete required fields",IF(L32&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q32" s="9" t="n"/>
+      <c r="R32" s="9" t="n"/>
+      <c r="S32" s="9" t="n"/>
     </row>
     <row r="33" ht="23" customHeight="1">
       <c r="A33" s="14" t="n"/>
@@ -1853,6 +1964,9 @@
         <f>IF(A33="","",IF(COUNTIF($A$2:$A$501,A33)&gt;1,"Duplicate lot ID",IF(OR(B33="",H33="",I33="",J33=""),"Complete required fields",IF(L33&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q33" s="14" t="n"/>
+      <c r="R33" s="14" t="n"/>
+      <c r="S33" s="14" t="n"/>
     </row>
     <row r="34" ht="23" customHeight="1">
       <c r="A34" s="9" t="n"/>
@@ -1886,6 +2000,9 @@
         <f>IF(A34="","",IF(COUNTIF($A$2:$A$501,A34)&gt;1,"Duplicate lot ID",IF(OR(B34="",H34="",I34="",J34=""),"Complete required fields",IF(L34&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
+      <c r="S34" s="9" t="n"/>
     </row>
     <row r="35" ht="23" customHeight="1">
       <c r="A35" s="14" t="n"/>
@@ -1919,6 +2036,9 @@
         <f>IF(A35="","",IF(COUNTIF($A$2:$A$501,A35)&gt;1,"Duplicate lot ID",IF(OR(B35="",H35="",I35="",J35=""),"Complete required fields",IF(L35&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q35" s="14" t="n"/>
+      <c r="R35" s="14" t="n"/>
+      <c r="S35" s="14" t="n"/>
     </row>
     <row r="36" ht="23" customHeight="1">
       <c r="A36" s="9" t="n"/>
@@ -1952,6 +2072,9 @@
         <f>IF(A36="","",IF(COUNTIF($A$2:$A$501,A36)&gt;1,"Duplicate lot ID",IF(OR(B36="",H36="",I36="",J36=""),"Complete required fields",IF(L36&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q36" s="9" t="n"/>
+      <c r="R36" s="9" t="n"/>
+      <c r="S36" s="9" t="n"/>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="14" t="n"/>
@@ -1985,6 +2108,9 @@
         <f>IF(A37="","",IF(COUNTIF($A$2:$A$501,A37)&gt;1,"Duplicate lot ID",IF(OR(B37="",H37="",I37="",J37=""),"Complete required fields",IF(L37&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q37" s="14" t="n"/>
+      <c r="R37" s="14" t="n"/>
+      <c r="S37" s="14" t="n"/>
     </row>
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="9" t="n"/>
@@ -2018,6 +2144,9 @@
         <f>IF(A38="","",IF(COUNTIF($A$2:$A$501,A38)&gt;1,"Duplicate lot ID",IF(OR(B38="",H38="",I38="",J38=""),"Complete required fields",IF(L38&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q38" s="9" t="n"/>
+      <c r="R38" s="9" t="n"/>
+      <c r="S38" s="9" t="n"/>
     </row>
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="14" t="n"/>
@@ -2051,6 +2180,9 @@
         <f>IF(A39="","",IF(COUNTIF($A$2:$A$501,A39)&gt;1,"Duplicate lot ID",IF(OR(B39="",H39="",I39="",J39=""),"Complete required fields",IF(L39&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q39" s="14" t="n"/>
+      <c r="R39" s="14" t="n"/>
+      <c r="S39" s="14" t="n"/>
     </row>
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="9" t="n"/>
@@ -2084,6 +2216,9 @@
         <f>IF(A40="","",IF(COUNTIF($A$2:$A$501,A40)&gt;1,"Duplicate lot ID",IF(OR(B40="",H40="",I40="",J40=""),"Complete required fields",IF(L40&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q40" s="9" t="n"/>
+      <c r="R40" s="9" t="n"/>
+      <c r="S40" s="9" t="n"/>
     </row>
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="14" t="n"/>
@@ -2117,6 +2252,9 @@
         <f>IF(A41="","",IF(COUNTIF($A$2:$A$501,A41)&gt;1,"Duplicate lot ID",IF(OR(B41="",H41="",I41="",J41=""),"Complete required fields",IF(L41&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q41" s="14" t="n"/>
+      <c r="R41" s="14" t="n"/>
+      <c r="S41" s="14" t="n"/>
     </row>
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="9" t="n"/>
@@ -2150,6 +2288,9 @@
         <f>IF(A42="","",IF(COUNTIF($A$2:$A$501,A42)&gt;1,"Duplicate lot ID",IF(OR(B42="",H42="",I42="",J42=""),"Complete required fields",IF(L42&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q42" s="9" t="n"/>
+      <c r="R42" s="9" t="n"/>
+      <c r="S42" s="9" t="n"/>
     </row>
     <row r="43" ht="23" customHeight="1">
       <c r="A43" s="14" t="n"/>
@@ -2183,6 +2324,9 @@
         <f>IF(A43="","",IF(COUNTIF($A$2:$A$501,A43)&gt;1,"Duplicate lot ID",IF(OR(B43="",H43="",I43="",J43=""),"Complete required fields",IF(L43&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q43" s="14" t="n"/>
+      <c r="R43" s="14" t="n"/>
+      <c r="S43" s="14" t="n"/>
     </row>
     <row r="44" ht="23" customHeight="1">
       <c r="A44" s="9" t="n"/>
@@ -2216,6 +2360,9 @@
         <f>IF(A44="","",IF(COUNTIF($A$2:$A$501,A44)&gt;1,"Duplicate lot ID",IF(OR(B44="",H44="",I44="",J44=""),"Complete required fields",IF(L44&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q44" s="9" t="n"/>
+      <c r="R44" s="9" t="n"/>
+      <c r="S44" s="9" t="n"/>
     </row>
     <row r="45" ht="23" customHeight="1">
       <c r="A45" s="14" t="n"/>
@@ -2249,6 +2396,9 @@
         <f>IF(A45="","",IF(COUNTIF($A$2:$A$501,A45)&gt;1,"Duplicate lot ID",IF(OR(B45="",H45="",I45="",J45=""),"Complete required fields",IF(L45&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q45" s="14" t="n"/>
+      <c r="R45" s="14" t="n"/>
+      <c r="S45" s="14" t="n"/>
     </row>
     <row r="46" ht="23" customHeight="1">
       <c r="A46" s="9" t="n"/>
@@ -2282,6 +2432,9 @@
         <f>IF(A46="","",IF(COUNTIF($A$2:$A$501,A46)&gt;1,"Duplicate lot ID",IF(OR(B46="",H46="",I46="",J46=""),"Complete required fields",IF(L46&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q46" s="9" t="n"/>
+      <c r="R46" s="9" t="n"/>
+      <c r="S46" s="9" t="n"/>
     </row>
     <row r="47" ht="23" customHeight="1">
       <c r="A47" s="14" t="n"/>
@@ -2315,6 +2468,9 @@
         <f>IF(A47="","",IF(COUNTIF($A$2:$A$501,A47)&gt;1,"Duplicate lot ID",IF(OR(B47="",H47="",I47="",J47=""),"Complete required fields",IF(L47&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q47" s="14" t="n"/>
+      <c r="R47" s="14" t="n"/>
+      <c r="S47" s="14" t="n"/>
     </row>
     <row r="48" ht="23" customHeight="1">
       <c r="A48" s="9" t="n"/>
@@ -2348,6 +2504,9 @@
         <f>IF(A48="","",IF(COUNTIF($A$2:$A$501,A48)&gt;1,"Duplicate lot ID",IF(OR(B48="",H48="",I48="",J48=""),"Complete required fields",IF(L48&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q48" s="9" t="n"/>
+      <c r="R48" s="9" t="n"/>
+      <c r="S48" s="9" t="n"/>
     </row>
     <row r="49" ht="23" customHeight="1">
       <c r="A49" s="14" t="n"/>
@@ -2381,6 +2540,9 @@
         <f>IF(A49="","",IF(COUNTIF($A$2:$A$501,A49)&gt;1,"Duplicate lot ID",IF(OR(B49="",H49="",I49="",J49=""),"Complete required fields",IF(L49&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q49" s="14" t="n"/>
+      <c r="R49" s="14" t="n"/>
+      <c r="S49" s="14" t="n"/>
     </row>
     <row r="50" ht="23" customHeight="1">
       <c r="A50" s="9" t="n"/>
@@ -2414,6 +2576,9 @@
         <f>IF(A50="","",IF(COUNTIF($A$2:$A$501,A50)&gt;1,"Duplicate lot ID",IF(OR(B50="",H50="",I50="",J50=""),"Complete required fields",IF(L50&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="9" t="n"/>
+      <c r="S50" s="9" t="n"/>
     </row>
     <row r="51" ht="23" customHeight="1">
       <c r="A51" s="14" t="n"/>
@@ -2447,6 +2612,9 @@
         <f>IF(A51="","",IF(COUNTIF($A$2:$A$501,A51)&gt;1,"Duplicate lot ID",IF(OR(B51="",H51="",I51="",J51=""),"Complete required fields",IF(L51&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q51" s="14" t="n"/>
+      <c r="R51" s="14" t="n"/>
+      <c r="S51" s="14" t="n"/>
     </row>
     <row r="52" ht="23" customHeight="1">
       <c r="A52" s="9" t="n"/>
@@ -2480,6 +2648,9 @@
         <f>IF(A52="","",IF(COUNTIF($A$2:$A$501,A52)&gt;1,"Duplicate lot ID",IF(OR(B52="",H52="",I52="",J52=""),"Complete required fields",IF(L52&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q52" s="9" t="n"/>
+      <c r="R52" s="9" t="n"/>
+      <c r="S52" s="9" t="n"/>
     </row>
     <row r="53" ht="23" customHeight="1">
       <c r="A53" s="14" t="n"/>
@@ -2513,6 +2684,9 @@
         <f>IF(A53="","",IF(COUNTIF($A$2:$A$501,A53)&gt;1,"Duplicate lot ID",IF(OR(B53="",H53="",I53="",J53=""),"Complete required fields",IF(L53&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q53" s="14" t="n"/>
+      <c r="R53" s="14" t="n"/>
+      <c r="S53" s="14" t="n"/>
     </row>
     <row r="54" ht="23" customHeight="1">
       <c r="A54" s="9" t="n"/>
@@ -2546,6 +2720,9 @@
         <f>IF(A54="","",IF(COUNTIF($A$2:$A$501,A54)&gt;1,"Duplicate lot ID",IF(OR(B54="",H54="",I54="",J54=""),"Complete required fields",IF(L54&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q54" s="9" t="n"/>
+      <c r="R54" s="9" t="n"/>
+      <c r="S54" s="9" t="n"/>
     </row>
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="14" t="n"/>
@@ -2579,6 +2756,9 @@
         <f>IF(A55="","",IF(COUNTIF($A$2:$A$501,A55)&gt;1,"Duplicate lot ID",IF(OR(B55="",H55="",I55="",J55=""),"Complete required fields",IF(L55&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q55" s="14" t="n"/>
+      <c r="R55" s="14" t="n"/>
+      <c r="S55" s="14" t="n"/>
     </row>
     <row r="56" ht="23" customHeight="1">
       <c r="A56" s="9" t="n"/>
@@ -2612,6 +2792,9 @@
         <f>IF(A56="","",IF(COUNTIF($A$2:$A$501,A56)&gt;1,"Duplicate lot ID",IF(OR(B56="",H56="",I56="",J56=""),"Complete required fields",IF(L56&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q56" s="9" t="n"/>
+      <c r="R56" s="9" t="n"/>
+      <c r="S56" s="9" t="n"/>
     </row>
     <row r="57" ht="23" customHeight="1">
       <c r="A57" s="14" t="n"/>
@@ -2645,6 +2828,9 @@
         <f>IF(A57="","",IF(COUNTIF($A$2:$A$501,A57)&gt;1,"Duplicate lot ID",IF(OR(B57="",H57="",I57="",J57=""),"Complete required fields",IF(L57&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q57" s="14" t="n"/>
+      <c r="R57" s="14" t="n"/>
+      <c r="S57" s="14" t="n"/>
     </row>
     <row r="58" ht="23" customHeight="1">
       <c r="A58" s="9" t="n"/>
@@ -2678,6 +2864,9 @@
         <f>IF(A58="","",IF(COUNTIF($A$2:$A$501,A58)&gt;1,"Duplicate lot ID",IF(OR(B58="",H58="",I58="",J58=""),"Complete required fields",IF(L58&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q58" s="9" t="n"/>
+      <c r="R58" s="9" t="n"/>
+      <c r="S58" s="9" t="n"/>
     </row>
     <row r="59" ht="23" customHeight="1">
       <c r="A59" s="14" t="n"/>
@@ -2711,6 +2900,9 @@
         <f>IF(A59="","",IF(COUNTIF($A$2:$A$501,A59)&gt;1,"Duplicate lot ID",IF(OR(B59="",H59="",I59="",J59=""),"Complete required fields",IF(L59&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q59" s="14" t="n"/>
+      <c r="R59" s="14" t="n"/>
+      <c r="S59" s="14" t="n"/>
     </row>
     <row r="60" ht="23" customHeight="1">
       <c r="A60" s="9" t="n"/>
@@ -2744,6 +2936,9 @@
         <f>IF(A60="","",IF(COUNTIF($A$2:$A$501,A60)&gt;1,"Duplicate lot ID",IF(OR(B60="",H60="",I60="",J60=""),"Complete required fields",IF(L60&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q60" s="9" t="n"/>
+      <c r="R60" s="9" t="n"/>
+      <c r="S60" s="9" t="n"/>
     </row>
     <row r="61" ht="23" customHeight="1">
       <c r="A61" s="14" t="n"/>
@@ -2777,6 +2972,9 @@
         <f>IF(A61="","",IF(COUNTIF($A$2:$A$501,A61)&gt;1,"Duplicate lot ID",IF(OR(B61="",H61="",I61="",J61=""),"Complete required fields",IF(L61&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q61" s="14" t="n"/>
+      <c r="R61" s="14" t="n"/>
+      <c r="S61" s="14" t="n"/>
     </row>
     <row r="62" ht="23" customHeight="1">
       <c r="A62" s="9" t="n"/>
@@ -2810,6 +3008,9 @@
         <f>IF(A62="","",IF(COUNTIF($A$2:$A$501,A62)&gt;1,"Duplicate lot ID",IF(OR(B62="",H62="",I62="",J62=""),"Complete required fields",IF(L62&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q62" s="9" t="n"/>
+      <c r="R62" s="9" t="n"/>
+      <c r="S62" s="9" t="n"/>
     </row>
     <row r="63" ht="23" customHeight="1">
       <c r="A63" s="14" t="n"/>
@@ -2843,6 +3044,9 @@
         <f>IF(A63="","",IF(COUNTIF($A$2:$A$501,A63)&gt;1,"Duplicate lot ID",IF(OR(B63="",H63="",I63="",J63=""),"Complete required fields",IF(L63&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q63" s="14" t="n"/>
+      <c r="R63" s="14" t="n"/>
+      <c r="S63" s="14" t="n"/>
     </row>
     <row r="64" ht="23" customHeight="1">
       <c r="A64" s="9" t="n"/>
@@ -2876,6 +3080,9 @@
         <f>IF(A64="","",IF(COUNTIF($A$2:$A$501,A64)&gt;1,"Duplicate lot ID",IF(OR(B64="",H64="",I64="",J64=""),"Complete required fields",IF(L64&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q64" s="9" t="n"/>
+      <c r="R64" s="9" t="n"/>
+      <c r="S64" s="9" t="n"/>
     </row>
     <row r="65" ht="23" customHeight="1">
       <c r="A65" s="14" t="n"/>
@@ -2909,6 +3116,9 @@
         <f>IF(A65="","",IF(COUNTIF($A$2:$A$501,A65)&gt;1,"Duplicate lot ID",IF(OR(B65="",H65="",I65="",J65=""),"Complete required fields",IF(L65&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q65" s="14" t="n"/>
+      <c r="R65" s="14" t="n"/>
+      <c r="S65" s="14" t="n"/>
     </row>
     <row r="66" ht="23" customHeight="1">
       <c r="A66" s="9" t="n"/>
@@ -2942,6 +3152,9 @@
         <f>IF(A66="","",IF(COUNTIF($A$2:$A$501,A66)&gt;1,"Duplicate lot ID",IF(OR(B66="",H66="",I66="",J66=""),"Complete required fields",IF(L66&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q66" s="9" t="n"/>
+      <c r="R66" s="9" t="n"/>
+      <c r="S66" s="9" t="n"/>
     </row>
     <row r="67" ht="23" customHeight="1">
       <c r="A67" s="14" t="n"/>
@@ -2975,6 +3188,9 @@
         <f>IF(A67="","",IF(COUNTIF($A$2:$A$501,A67)&gt;1,"Duplicate lot ID",IF(OR(B67="",H67="",I67="",J67=""),"Complete required fields",IF(L67&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q67" s="14" t="n"/>
+      <c r="R67" s="14" t="n"/>
+      <c r="S67" s="14" t="n"/>
     </row>
     <row r="68" ht="23" customHeight="1">
       <c r="A68" s="9" t="n"/>
@@ -3008,6 +3224,9 @@
         <f>IF(A68="","",IF(COUNTIF($A$2:$A$501,A68)&gt;1,"Duplicate lot ID",IF(OR(B68="",H68="",I68="",J68=""),"Complete required fields",IF(L68&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q68" s="9" t="n"/>
+      <c r="R68" s="9" t="n"/>
+      <c r="S68" s="9" t="n"/>
     </row>
     <row r="69" ht="23" customHeight="1">
       <c r="A69" s="14" t="n"/>
@@ -3041,6 +3260,9 @@
         <f>IF(A69="","",IF(COUNTIF($A$2:$A$501,A69)&gt;1,"Duplicate lot ID",IF(OR(B69="",H69="",I69="",J69=""),"Complete required fields",IF(L69&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q69" s="14" t="n"/>
+      <c r="R69" s="14" t="n"/>
+      <c r="S69" s="14" t="n"/>
     </row>
     <row r="70" ht="23" customHeight="1">
       <c r="A70" s="9" t="n"/>
@@ -3074,6 +3296,9 @@
         <f>IF(A70="","",IF(COUNTIF($A$2:$A$501,A70)&gt;1,"Duplicate lot ID",IF(OR(B70="",H70="",I70="",J70=""),"Complete required fields",IF(L70&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q70" s="9" t="n"/>
+      <c r="R70" s="9" t="n"/>
+      <c r="S70" s="9" t="n"/>
     </row>
     <row r="71" ht="23" customHeight="1">
       <c r="A71" s="14" t="n"/>
@@ -3107,6 +3332,9 @@
         <f>IF(A71="","",IF(COUNTIF($A$2:$A$501,A71)&gt;1,"Duplicate lot ID",IF(OR(B71="",H71="",I71="",J71=""),"Complete required fields",IF(L71&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q71" s="14" t="n"/>
+      <c r="R71" s="14" t="n"/>
+      <c r="S71" s="14" t="n"/>
     </row>
     <row r="72" ht="23" customHeight="1">
       <c r="A72" s="9" t="n"/>
@@ -3140,6 +3368,9 @@
         <f>IF(A72="","",IF(COUNTIF($A$2:$A$501,A72)&gt;1,"Duplicate lot ID",IF(OR(B72="",H72="",I72="",J72=""),"Complete required fields",IF(L72&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q72" s="9" t="n"/>
+      <c r="R72" s="9" t="n"/>
+      <c r="S72" s="9" t="n"/>
     </row>
     <row r="73" ht="23" customHeight="1">
       <c r="A73" s="14" t="n"/>
@@ -3173,6 +3404,9 @@
         <f>IF(A73="","",IF(COUNTIF($A$2:$A$501,A73)&gt;1,"Duplicate lot ID",IF(OR(B73="",H73="",I73="",J73=""),"Complete required fields",IF(L73&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q73" s="14" t="n"/>
+      <c r="R73" s="14" t="n"/>
+      <c r="S73" s="14" t="n"/>
     </row>
     <row r="74" ht="23" customHeight="1">
       <c r="A74" s="9" t="n"/>
@@ -3206,6 +3440,9 @@
         <f>IF(A74="","",IF(COUNTIF($A$2:$A$501,A74)&gt;1,"Duplicate lot ID",IF(OR(B74="",H74="",I74="",J74=""),"Complete required fields",IF(L74&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q74" s="9" t="n"/>
+      <c r="R74" s="9" t="n"/>
+      <c r="S74" s="9" t="n"/>
     </row>
     <row r="75" ht="23" customHeight="1">
       <c r="A75" s="14" t="n"/>
@@ -3239,6 +3476,9 @@
         <f>IF(A75="","",IF(COUNTIF($A$2:$A$501,A75)&gt;1,"Duplicate lot ID",IF(OR(B75="",H75="",I75="",J75=""),"Complete required fields",IF(L75&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q75" s="14" t="n"/>
+      <c r="R75" s="14" t="n"/>
+      <c r="S75" s="14" t="n"/>
     </row>
     <row r="76" ht="23" customHeight="1">
       <c r="A76" s="9" t="n"/>
@@ -3272,6 +3512,9 @@
         <f>IF(A76="","",IF(COUNTIF($A$2:$A$501,A76)&gt;1,"Duplicate lot ID",IF(OR(B76="",H76="",I76="",J76=""),"Complete required fields",IF(L76&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q76" s="9" t="n"/>
+      <c r="R76" s="9" t="n"/>
+      <c r="S76" s="9" t="n"/>
     </row>
     <row r="77" ht="23" customHeight="1">
       <c r="A77" s="14" t="n"/>
@@ -3305,6 +3548,9 @@
         <f>IF(A77="","",IF(COUNTIF($A$2:$A$501,A77)&gt;1,"Duplicate lot ID",IF(OR(B77="",H77="",I77="",J77=""),"Complete required fields",IF(L77&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q77" s="14" t="n"/>
+      <c r="R77" s="14" t="n"/>
+      <c r="S77" s="14" t="n"/>
     </row>
     <row r="78" ht="23" customHeight="1">
       <c r="A78" s="9" t="n"/>
@@ -3338,6 +3584,9 @@
         <f>IF(A78="","",IF(COUNTIF($A$2:$A$501,A78)&gt;1,"Duplicate lot ID",IF(OR(B78="",H78="",I78="",J78=""),"Complete required fields",IF(L78&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q78" s="9" t="n"/>
+      <c r="R78" s="9" t="n"/>
+      <c r="S78" s="9" t="n"/>
     </row>
     <row r="79" ht="23" customHeight="1">
       <c r="A79" s="14" t="n"/>
@@ -3371,6 +3620,9 @@
         <f>IF(A79="","",IF(COUNTIF($A$2:$A$501,A79)&gt;1,"Duplicate lot ID",IF(OR(B79="",H79="",I79="",J79=""),"Complete required fields",IF(L79&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q79" s="14" t="n"/>
+      <c r="R79" s="14" t="n"/>
+      <c r="S79" s="14" t="n"/>
     </row>
     <row r="80" ht="23" customHeight="1">
       <c r="A80" s="9" t="n"/>
@@ -3404,6 +3656,9 @@
         <f>IF(A80="","",IF(COUNTIF($A$2:$A$501,A80)&gt;1,"Duplicate lot ID",IF(OR(B80="",H80="",I80="",J80=""),"Complete required fields",IF(L80&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q80" s="9" t="n"/>
+      <c r="R80" s="9" t="n"/>
+      <c r="S80" s="9" t="n"/>
     </row>
     <row r="81" ht="23" customHeight="1">
       <c r="A81" s="14" t="n"/>
@@ -3437,6 +3692,9 @@
         <f>IF(A81="","",IF(COUNTIF($A$2:$A$501,A81)&gt;1,"Duplicate lot ID",IF(OR(B81="",H81="",I81="",J81=""),"Complete required fields",IF(L81&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q81" s="14" t="n"/>
+      <c r="R81" s="14" t="n"/>
+      <c r="S81" s="14" t="n"/>
     </row>
     <row r="82" ht="23" customHeight="1">
       <c r="A82" s="9" t="n"/>
@@ -3470,6 +3728,9 @@
         <f>IF(A82="","",IF(COUNTIF($A$2:$A$501,A82)&gt;1,"Duplicate lot ID",IF(OR(B82="",H82="",I82="",J82=""),"Complete required fields",IF(L82&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q82" s="9" t="n"/>
+      <c r="R82" s="9" t="n"/>
+      <c r="S82" s="9" t="n"/>
     </row>
     <row r="83" ht="23" customHeight="1">
       <c r="A83" s="14" t="n"/>
@@ -3503,6 +3764,9 @@
         <f>IF(A83="","",IF(COUNTIF($A$2:$A$501,A83)&gt;1,"Duplicate lot ID",IF(OR(B83="",H83="",I83="",J83=""),"Complete required fields",IF(L83&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q83" s="14" t="n"/>
+      <c r="R83" s="14" t="n"/>
+      <c r="S83" s="14" t="n"/>
     </row>
     <row r="84" ht="23" customHeight="1">
       <c r="A84" s="9" t="n"/>
@@ -3536,6 +3800,9 @@
         <f>IF(A84="","",IF(COUNTIF($A$2:$A$501,A84)&gt;1,"Duplicate lot ID",IF(OR(B84="",H84="",I84="",J84=""),"Complete required fields",IF(L84&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q84" s="9" t="n"/>
+      <c r="R84" s="9" t="n"/>
+      <c r="S84" s="9" t="n"/>
     </row>
     <row r="85" ht="23" customHeight="1">
       <c r="A85" s="14" t="n"/>
@@ -3569,6 +3836,9 @@
         <f>IF(A85="","",IF(COUNTIF($A$2:$A$501,A85)&gt;1,"Duplicate lot ID",IF(OR(B85="",H85="",I85="",J85=""),"Complete required fields",IF(L85&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q85" s="14" t="n"/>
+      <c r="R85" s="14" t="n"/>
+      <c r="S85" s="14" t="n"/>
     </row>
     <row r="86" ht="23" customHeight="1">
       <c r="A86" s="9" t="n"/>
@@ -3602,6 +3872,9 @@
         <f>IF(A86="","",IF(COUNTIF($A$2:$A$501,A86)&gt;1,"Duplicate lot ID",IF(OR(B86="",H86="",I86="",J86=""),"Complete required fields",IF(L86&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q86" s="9" t="n"/>
+      <c r="R86" s="9" t="n"/>
+      <c r="S86" s="9" t="n"/>
     </row>
     <row r="87" ht="23" customHeight="1">
       <c r="A87" s="14" t="n"/>
@@ -3635,6 +3908,9 @@
         <f>IF(A87="","",IF(COUNTIF($A$2:$A$501,A87)&gt;1,"Duplicate lot ID",IF(OR(B87="",H87="",I87="",J87=""),"Complete required fields",IF(L87&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q87" s="14" t="n"/>
+      <c r="R87" s="14" t="n"/>
+      <c r="S87" s="14" t="n"/>
     </row>
     <row r="88" ht="23" customHeight="1">
       <c r="A88" s="9" t="n"/>
@@ -3668,6 +3944,9 @@
         <f>IF(A88="","",IF(COUNTIF($A$2:$A$501,A88)&gt;1,"Duplicate lot ID",IF(OR(B88="",H88="",I88="",J88=""),"Complete required fields",IF(L88&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q88" s="9" t="n"/>
+      <c r="R88" s="9" t="n"/>
+      <c r="S88" s="9" t="n"/>
     </row>
     <row r="89" ht="23" customHeight="1">
       <c r="A89" s="14" t="n"/>
@@ -3701,6 +3980,9 @@
         <f>IF(A89="","",IF(COUNTIF($A$2:$A$501,A89)&gt;1,"Duplicate lot ID",IF(OR(B89="",H89="",I89="",J89=""),"Complete required fields",IF(L89&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q89" s="14" t="n"/>
+      <c r="R89" s="14" t="n"/>
+      <c r="S89" s="14" t="n"/>
     </row>
     <row r="90" ht="23" customHeight="1">
       <c r="A90" s="9" t="n"/>
@@ -3734,6 +4016,9 @@
         <f>IF(A90="","",IF(COUNTIF($A$2:$A$501,A90)&gt;1,"Duplicate lot ID",IF(OR(B90="",H90="",I90="",J90=""),"Complete required fields",IF(L90&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q90" s="9" t="n"/>
+      <c r="R90" s="9" t="n"/>
+      <c r="S90" s="9" t="n"/>
     </row>
     <row r="91" ht="23" customHeight="1">
       <c r="A91" s="14" t="n"/>
@@ -3767,6 +4052,9 @@
         <f>IF(A91="","",IF(COUNTIF($A$2:$A$501,A91)&gt;1,"Duplicate lot ID",IF(OR(B91="",H91="",I91="",J91=""),"Complete required fields",IF(L91&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q91" s="14" t="n"/>
+      <c r="R91" s="14" t="n"/>
+      <c r="S91" s="14" t="n"/>
     </row>
     <row r="92" ht="23" customHeight="1">
       <c r="A92" s="9" t="n"/>
@@ -3800,6 +4088,9 @@
         <f>IF(A92="","",IF(COUNTIF($A$2:$A$501,A92)&gt;1,"Duplicate lot ID",IF(OR(B92="",H92="",I92="",J92=""),"Complete required fields",IF(L92&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q92" s="9" t="n"/>
+      <c r="R92" s="9" t="n"/>
+      <c r="S92" s="9" t="n"/>
     </row>
     <row r="93" ht="23" customHeight="1">
       <c r="A93" s="14" t="n"/>
@@ -3833,6 +4124,9 @@
         <f>IF(A93="","",IF(COUNTIF($A$2:$A$501,A93)&gt;1,"Duplicate lot ID",IF(OR(B93="",H93="",I93="",J93=""),"Complete required fields",IF(L93&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q93" s="14" t="n"/>
+      <c r="R93" s="14" t="n"/>
+      <c r="S93" s="14" t="n"/>
     </row>
     <row r="94" ht="23" customHeight="1">
       <c r="A94" s="9" t="n"/>
@@ -3866,6 +4160,9 @@
         <f>IF(A94="","",IF(COUNTIF($A$2:$A$501,A94)&gt;1,"Duplicate lot ID",IF(OR(B94="",H94="",I94="",J94=""),"Complete required fields",IF(L94&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q94" s="9" t="n"/>
+      <c r="R94" s="9" t="n"/>
+      <c r="S94" s="9" t="n"/>
     </row>
     <row r="95" ht="23" customHeight="1">
       <c r="A95" s="14" t="n"/>
@@ -3899,6 +4196,9 @@
         <f>IF(A95="","",IF(COUNTIF($A$2:$A$501,A95)&gt;1,"Duplicate lot ID",IF(OR(B95="",H95="",I95="",J95=""),"Complete required fields",IF(L95&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q95" s="14" t="n"/>
+      <c r="R95" s="14" t="n"/>
+      <c r="S95" s="14" t="n"/>
     </row>
     <row r="96" ht="23" customHeight="1">
       <c r="A96" s="9" t="n"/>
@@ -3932,6 +4232,9 @@
         <f>IF(A96="","",IF(COUNTIF($A$2:$A$501,A96)&gt;1,"Duplicate lot ID",IF(OR(B96="",H96="",I96="",J96=""),"Complete required fields",IF(L96&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q96" s="9" t="n"/>
+      <c r="R96" s="9" t="n"/>
+      <c r="S96" s="9" t="n"/>
     </row>
     <row r="97" ht="23" customHeight="1">
       <c r="A97" s="14" t="n"/>
@@ -3965,6 +4268,9 @@
         <f>IF(A97="","",IF(COUNTIF($A$2:$A$501,A97)&gt;1,"Duplicate lot ID",IF(OR(B97="",H97="",I97="",J97=""),"Complete required fields",IF(L97&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q97" s="14" t="n"/>
+      <c r="R97" s="14" t="n"/>
+      <c r="S97" s="14" t="n"/>
     </row>
     <row r="98" ht="23" customHeight="1">
       <c r="A98" s="9" t="n"/>
@@ -3998,6 +4304,9 @@
         <f>IF(A98="","",IF(COUNTIF($A$2:$A$501,A98)&gt;1,"Duplicate lot ID",IF(OR(B98="",H98="",I98="",J98=""),"Complete required fields",IF(L98&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q98" s="9" t="n"/>
+      <c r="R98" s="9" t="n"/>
+      <c r="S98" s="9" t="n"/>
     </row>
     <row r="99" ht="23" customHeight="1">
       <c r="A99" s="14" t="n"/>
@@ -4031,6 +4340,9 @@
         <f>IF(A99="","",IF(COUNTIF($A$2:$A$501,A99)&gt;1,"Duplicate lot ID",IF(OR(B99="",H99="",I99="",J99=""),"Complete required fields",IF(L99&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q99" s="14" t="n"/>
+      <c r="R99" s="14" t="n"/>
+      <c r="S99" s="14" t="n"/>
     </row>
     <row r="100" ht="23" customHeight="1">
       <c r="A100" s="9" t="n"/>
@@ -4064,6 +4376,9 @@
         <f>IF(A100="","",IF(COUNTIF($A$2:$A$501,A100)&gt;1,"Duplicate lot ID",IF(OR(B100="",H100="",I100="",J100=""),"Complete required fields",IF(L100&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q100" s="9" t="n"/>
+      <c r="R100" s="9" t="n"/>
+      <c r="S100" s="9" t="n"/>
     </row>
     <row r="101" ht="23" customHeight="1">
       <c r="A101" s="14" t="n"/>
@@ -4097,6 +4412,9 @@
         <f>IF(A101="","",IF(COUNTIF($A$2:$A$501,A101)&gt;1,"Duplicate lot ID",IF(OR(B101="",H101="",I101="",J101=""),"Complete required fields",IF(L101&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q101" s="14" t="n"/>
+      <c r="R101" s="14" t="n"/>
+      <c r="S101" s="14" t="n"/>
     </row>
     <row r="102" ht="23" customHeight="1">
       <c r="A102" s="9" t="n"/>
@@ -4130,6 +4448,9 @@
         <f>IF(A102="","",IF(COUNTIF($A$2:$A$501,A102)&gt;1,"Duplicate lot ID",IF(OR(B102="",H102="",I102="",J102=""),"Complete required fields",IF(L102&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q102" s="9" t="n"/>
+      <c r="R102" s="9" t="n"/>
+      <c r="S102" s="9" t="n"/>
     </row>
     <row r="103" ht="23" customHeight="1">
       <c r="A103" s="14" t="n"/>
@@ -4163,6 +4484,9 @@
         <f>IF(A103="","",IF(COUNTIF($A$2:$A$501,A103)&gt;1,"Duplicate lot ID",IF(OR(B103="",H103="",I103="",J103=""),"Complete required fields",IF(L103&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q103" s="14" t="n"/>
+      <c r="R103" s="14" t="n"/>
+      <c r="S103" s="14" t="n"/>
     </row>
     <row r="104" ht="23" customHeight="1">
       <c r="A104" s="9" t="n"/>
@@ -4196,6 +4520,9 @@
         <f>IF(A104="","",IF(COUNTIF($A$2:$A$501,A104)&gt;1,"Duplicate lot ID",IF(OR(B104="",H104="",I104="",J104=""),"Complete required fields",IF(L104&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q104" s="9" t="n"/>
+      <c r="R104" s="9" t="n"/>
+      <c r="S104" s="9" t="n"/>
     </row>
     <row r="105" ht="23" customHeight="1">
       <c r="A105" s="14" t="n"/>
@@ -4229,6 +4556,9 @@
         <f>IF(A105="","",IF(COUNTIF($A$2:$A$501,A105)&gt;1,"Duplicate lot ID",IF(OR(B105="",H105="",I105="",J105=""),"Complete required fields",IF(L105&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q105" s="14" t="n"/>
+      <c r="R105" s="14" t="n"/>
+      <c r="S105" s="14" t="n"/>
     </row>
     <row r="106" ht="23" customHeight="1">
       <c r="A106" s="9" t="n"/>
@@ -4262,6 +4592,9 @@
         <f>IF(A106="","",IF(COUNTIF($A$2:$A$501,A106)&gt;1,"Duplicate lot ID",IF(OR(B106="",H106="",I106="",J106=""),"Complete required fields",IF(L106&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q106" s="9" t="n"/>
+      <c r="R106" s="9" t="n"/>
+      <c r="S106" s="9" t="n"/>
     </row>
     <row r="107" ht="23" customHeight="1">
       <c r="A107" s="14" t="n"/>
@@ -4295,6 +4628,9 @@
         <f>IF(A107="","",IF(COUNTIF($A$2:$A$501,A107)&gt;1,"Duplicate lot ID",IF(OR(B107="",H107="",I107="",J107=""),"Complete required fields",IF(L107&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q107" s="14" t="n"/>
+      <c r="R107" s="14" t="n"/>
+      <c r="S107" s="14" t="n"/>
     </row>
     <row r="108" ht="23" customHeight="1">
       <c r="A108" s="9" t="n"/>
@@ -4328,6 +4664,9 @@
         <f>IF(A108="","",IF(COUNTIF($A$2:$A$501,A108)&gt;1,"Duplicate lot ID",IF(OR(B108="",H108="",I108="",J108=""),"Complete required fields",IF(L108&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q108" s="9" t="n"/>
+      <c r="R108" s="9" t="n"/>
+      <c r="S108" s="9" t="n"/>
     </row>
     <row r="109" ht="23" customHeight="1">
       <c r="A109" s="14" t="n"/>
@@ -4361,6 +4700,9 @@
         <f>IF(A109="","",IF(COUNTIF($A$2:$A$501,A109)&gt;1,"Duplicate lot ID",IF(OR(B109="",H109="",I109="",J109=""),"Complete required fields",IF(L109&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q109" s="14" t="n"/>
+      <c r="R109" s="14" t="n"/>
+      <c r="S109" s="14" t="n"/>
     </row>
     <row r="110" ht="23" customHeight="1">
       <c r="A110" s="9" t="n"/>
@@ -4394,6 +4736,9 @@
         <f>IF(A110="","",IF(COUNTIF($A$2:$A$501,A110)&gt;1,"Duplicate lot ID",IF(OR(B110="",H110="",I110="",J110=""),"Complete required fields",IF(L110&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q110" s="9" t="n"/>
+      <c r="R110" s="9" t="n"/>
+      <c r="S110" s="9" t="n"/>
     </row>
     <row r="111" ht="23" customHeight="1">
       <c r="A111" s="14" t="n"/>
@@ -4427,6 +4772,9 @@
         <f>IF(A111="","",IF(COUNTIF($A$2:$A$501,A111)&gt;1,"Duplicate lot ID",IF(OR(B111="",H111="",I111="",J111=""),"Complete required fields",IF(L111&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q111" s="14" t="n"/>
+      <c r="R111" s="14" t="n"/>
+      <c r="S111" s="14" t="n"/>
     </row>
     <row r="112" ht="23" customHeight="1">
       <c r="A112" s="9" t="n"/>
@@ -4460,6 +4808,9 @@
         <f>IF(A112="","",IF(COUNTIF($A$2:$A$501,A112)&gt;1,"Duplicate lot ID",IF(OR(B112="",H112="",I112="",J112=""),"Complete required fields",IF(L112&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q112" s="9" t="n"/>
+      <c r="R112" s="9" t="n"/>
+      <c r="S112" s="9" t="n"/>
     </row>
     <row r="113" ht="23" customHeight="1">
       <c r="A113" s="14" t="n"/>
@@ -4493,6 +4844,9 @@
         <f>IF(A113="","",IF(COUNTIF($A$2:$A$501,A113)&gt;1,"Duplicate lot ID",IF(OR(B113="",H113="",I113="",J113=""),"Complete required fields",IF(L113&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q113" s="14" t="n"/>
+      <c r="R113" s="14" t="n"/>
+      <c r="S113" s="14" t="n"/>
     </row>
     <row r="114" ht="23" customHeight="1">
       <c r="A114" s="9" t="n"/>
@@ -4526,6 +4880,9 @@
         <f>IF(A114="","",IF(COUNTIF($A$2:$A$501,A114)&gt;1,"Duplicate lot ID",IF(OR(B114="",H114="",I114="",J114=""),"Complete required fields",IF(L114&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q114" s="9" t="n"/>
+      <c r="R114" s="9" t="n"/>
+      <c r="S114" s="9" t="n"/>
     </row>
     <row r="115" ht="23" customHeight="1">
       <c r="A115" s="14" t="n"/>
@@ -4559,6 +4916,9 @@
         <f>IF(A115="","",IF(COUNTIF($A$2:$A$501,A115)&gt;1,"Duplicate lot ID",IF(OR(B115="",H115="",I115="",J115=""),"Complete required fields",IF(L115&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q115" s="14" t="n"/>
+      <c r="R115" s="14" t="n"/>
+      <c r="S115" s="14" t="n"/>
     </row>
     <row r="116" ht="23" customHeight="1">
       <c r="A116" s="9" t="n"/>
@@ -4592,6 +4952,9 @@
         <f>IF(A116="","",IF(COUNTIF($A$2:$A$501,A116)&gt;1,"Duplicate lot ID",IF(OR(B116="",H116="",I116="",J116=""),"Complete required fields",IF(L116&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q116" s="9" t="n"/>
+      <c r="R116" s="9" t="n"/>
+      <c r="S116" s="9" t="n"/>
     </row>
     <row r="117" ht="23" customHeight="1">
       <c r="A117" s="14" t="n"/>
@@ -4625,6 +4988,9 @@
         <f>IF(A117="","",IF(COUNTIF($A$2:$A$501,A117)&gt;1,"Duplicate lot ID",IF(OR(B117="",H117="",I117="",J117=""),"Complete required fields",IF(L117&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q117" s="14" t="n"/>
+      <c r="R117" s="14" t="n"/>
+      <c r="S117" s="14" t="n"/>
     </row>
     <row r="118" ht="23" customHeight="1">
       <c r="A118" s="9" t="n"/>
@@ -4658,6 +5024,9 @@
         <f>IF(A118="","",IF(COUNTIF($A$2:$A$501,A118)&gt;1,"Duplicate lot ID",IF(OR(B118="",H118="",I118="",J118=""),"Complete required fields",IF(L118&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q118" s="9" t="n"/>
+      <c r="R118" s="9" t="n"/>
+      <c r="S118" s="9" t="n"/>
     </row>
     <row r="119" ht="23" customHeight="1">
       <c r="A119" s="14" t="n"/>
@@ -4691,6 +5060,9 @@
         <f>IF(A119="","",IF(COUNTIF($A$2:$A$501,A119)&gt;1,"Duplicate lot ID",IF(OR(B119="",H119="",I119="",J119=""),"Complete required fields",IF(L119&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q119" s="14" t="n"/>
+      <c r="R119" s="14" t="n"/>
+      <c r="S119" s="14" t="n"/>
     </row>
     <row r="120" ht="23" customHeight="1">
       <c r="A120" s="9" t="n"/>
@@ -4724,6 +5096,9 @@
         <f>IF(A120="","",IF(COUNTIF($A$2:$A$501,A120)&gt;1,"Duplicate lot ID",IF(OR(B120="",H120="",I120="",J120=""),"Complete required fields",IF(L120&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q120" s="9" t="n"/>
+      <c r="R120" s="9" t="n"/>
+      <c r="S120" s="9" t="n"/>
     </row>
     <row r="121" ht="23" customHeight="1">
       <c r="A121" s="14" t="n"/>
@@ -4757,6 +5132,9 @@
         <f>IF(A121="","",IF(COUNTIF($A$2:$A$501,A121)&gt;1,"Duplicate lot ID",IF(OR(B121="",H121="",I121="",J121=""),"Complete required fields",IF(L121&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q121" s="14" t="n"/>
+      <c r="R121" s="14" t="n"/>
+      <c r="S121" s="14" t="n"/>
     </row>
     <row r="122" ht="23" customHeight="1">
       <c r="A122" s="9" t="n"/>
@@ -4790,6 +5168,9 @@
         <f>IF(A122="","",IF(COUNTIF($A$2:$A$501,A122)&gt;1,"Duplicate lot ID",IF(OR(B122="",H122="",I122="",J122=""),"Complete required fields",IF(L122&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q122" s="9" t="n"/>
+      <c r="R122" s="9" t="n"/>
+      <c r="S122" s="9" t="n"/>
     </row>
     <row r="123" ht="23" customHeight="1">
       <c r="A123" s="14" t="n"/>
@@ -4823,6 +5204,9 @@
         <f>IF(A123="","",IF(COUNTIF($A$2:$A$501,A123)&gt;1,"Duplicate lot ID",IF(OR(B123="",H123="",I123="",J123=""),"Complete required fields",IF(L123&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q123" s="14" t="n"/>
+      <c r="R123" s="14" t="n"/>
+      <c r="S123" s="14" t="n"/>
     </row>
     <row r="124" ht="23" customHeight="1">
       <c r="A124" s="9" t="n"/>
@@ -4856,6 +5240,9 @@
         <f>IF(A124="","",IF(COUNTIF($A$2:$A$501,A124)&gt;1,"Duplicate lot ID",IF(OR(B124="",H124="",I124="",J124=""),"Complete required fields",IF(L124&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q124" s="9" t="n"/>
+      <c r="R124" s="9" t="n"/>
+      <c r="S124" s="9" t="n"/>
     </row>
     <row r="125" ht="23" customHeight="1">
       <c r="A125" s="14" t="n"/>
@@ -4889,6 +5276,9 @@
         <f>IF(A125="","",IF(COUNTIF($A$2:$A$501,A125)&gt;1,"Duplicate lot ID",IF(OR(B125="",H125="",I125="",J125=""),"Complete required fields",IF(L125&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q125" s="14" t="n"/>
+      <c r="R125" s="14" t="n"/>
+      <c r="S125" s="14" t="n"/>
     </row>
     <row r="126" ht="23" customHeight="1">
       <c r="A126" s="9" t="n"/>
@@ -4922,6 +5312,9 @@
         <f>IF(A126="","",IF(COUNTIF($A$2:$A$501,A126)&gt;1,"Duplicate lot ID",IF(OR(B126="",H126="",I126="",J126=""),"Complete required fields",IF(L126&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q126" s="9" t="n"/>
+      <c r="R126" s="9" t="n"/>
+      <c r="S126" s="9" t="n"/>
     </row>
     <row r="127" ht="23" customHeight="1">
       <c r="A127" s="14" t="n"/>
@@ -4955,6 +5348,9 @@
         <f>IF(A127="","",IF(COUNTIF($A$2:$A$501,A127)&gt;1,"Duplicate lot ID",IF(OR(B127="",H127="",I127="",J127=""),"Complete required fields",IF(L127&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q127" s="14" t="n"/>
+      <c r="R127" s="14" t="n"/>
+      <c r="S127" s="14" t="n"/>
     </row>
     <row r="128" ht="23" customHeight="1">
       <c r="A128" s="9" t="n"/>
@@ -4988,6 +5384,9 @@
         <f>IF(A128="","",IF(COUNTIF($A$2:$A$501,A128)&gt;1,"Duplicate lot ID",IF(OR(B128="",H128="",I128="",J128=""),"Complete required fields",IF(L128&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q128" s="9" t="n"/>
+      <c r="R128" s="9" t="n"/>
+      <c r="S128" s="9" t="n"/>
     </row>
     <row r="129" ht="23" customHeight="1">
       <c r="A129" s="14" t="n"/>
@@ -5021,6 +5420,9 @@
         <f>IF(A129="","",IF(COUNTIF($A$2:$A$501,A129)&gt;1,"Duplicate lot ID",IF(OR(B129="",H129="",I129="",J129=""),"Complete required fields",IF(L129&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q129" s="14" t="n"/>
+      <c r="R129" s="14" t="n"/>
+      <c r="S129" s="14" t="n"/>
     </row>
     <row r="130" ht="23" customHeight="1">
       <c r="A130" s="9" t="n"/>
@@ -5054,6 +5456,9 @@
         <f>IF(A130="","",IF(COUNTIF($A$2:$A$501,A130)&gt;1,"Duplicate lot ID",IF(OR(B130="",H130="",I130="",J130=""),"Complete required fields",IF(L130&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q130" s="9" t="n"/>
+      <c r="R130" s="9" t="n"/>
+      <c r="S130" s="9" t="n"/>
     </row>
     <row r="131" ht="23" customHeight="1">
       <c r="A131" s="14" t="n"/>
@@ -5087,6 +5492,9 @@
         <f>IF(A131="","",IF(COUNTIF($A$2:$A$501,A131)&gt;1,"Duplicate lot ID",IF(OR(B131="",H131="",I131="",J131=""),"Complete required fields",IF(L131&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q131" s="14" t="n"/>
+      <c r="R131" s="14" t="n"/>
+      <c r="S131" s="14" t="n"/>
     </row>
     <row r="132" ht="23" customHeight="1">
       <c r="A132" s="9" t="n"/>
@@ -5120,6 +5528,9 @@
         <f>IF(A132="","",IF(COUNTIF($A$2:$A$501,A132)&gt;1,"Duplicate lot ID",IF(OR(B132="",H132="",I132="",J132=""),"Complete required fields",IF(L132&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q132" s="9" t="n"/>
+      <c r="R132" s="9" t="n"/>
+      <c r="S132" s="9" t="n"/>
     </row>
     <row r="133" ht="23" customHeight="1">
       <c r="A133" s="14" t="n"/>
@@ -5153,6 +5564,9 @@
         <f>IF(A133="","",IF(COUNTIF($A$2:$A$501,A133)&gt;1,"Duplicate lot ID",IF(OR(B133="",H133="",I133="",J133=""),"Complete required fields",IF(L133&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q133" s="14" t="n"/>
+      <c r="R133" s="14" t="n"/>
+      <c r="S133" s="14" t="n"/>
     </row>
     <row r="134" ht="23" customHeight="1">
       <c r="A134" s="9" t="n"/>
@@ -5186,6 +5600,9 @@
         <f>IF(A134="","",IF(COUNTIF($A$2:$A$501,A134)&gt;1,"Duplicate lot ID",IF(OR(B134="",H134="",I134="",J134=""),"Complete required fields",IF(L134&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q134" s="9" t="n"/>
+      <c r="R134" s="9" t="n"/>
+      <c r="S134" s="9" t="n"/>
     </row>
     <row r="135" ht="23" customHeight="1">
       <c r="A135" s="14" t="n"/>
@@ -5219,6 +5636,9 @@
         <f>IF(A135="","",IF(COUNTIF($A$2:$A$501,A135)&gt;1,"Duplicate lot ID",IF(OR(B135="",H135="",I135="",J135=""),"Complete required fields",IF(L135&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q135" s="14" t="n"/>
+      <c r="R135" s="14" t="n"/>
+      <c r="S135" s="14" t="n"/>
     </row>
     <row r="136" ht="23" customHeight="1">
       <c r="A136" s="9" t="n"/>
@@ -5252,6 +5672,9 @@
         <f>IF(A136="","",IF(COUNTIF($A$2:$A$501,A136)&gt;1,"Duplicate lot ID",IF(OR(B136="",H136="",I136="",J136=""),"Complete required fields",IF(L136&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q136" s="9" t="n"/>
+      <c r="R136" s="9" t="n"/>
+      <c r="S136" s="9" t="n"/>
     </row>
     <row r="137" ht="23" customHeight="1">
       <c r="A137" s="14" t="n"/>
@@ -5285,6 +5708,9 @@
         <f>IF(A137="","",IF(COUNTIF($A$2:$A$501,A137)&gt;1,"Duplicate lot ID",IF(OR(B137="",H137="",I137="",J137=""),"Complete required fields",IF(L137&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q137" s="14" t="n"/>
+      <c r="R137" s="14" t="n"/>
+      <c r="S137" s="14" t="n"/>
     </row>
     <row r="138" ht="23" customHeight="1">
       <c r="A138" s="9" t="n"/>
@@ -5318,6 +5744,9 @@
         <f>IF(A138="","",IF(COUNTIF($A$2:$A$501,A138)&gt;1,"Duplicate lot ID",IF(OR(B138="",H138="",I138="",J138=""),"Complete required fields",IF(L138&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q138" s="9" t="n"/>
+      <c r="R138" s="9" t="n"/>
+      <c r="S138" s="9" t="n"/>
     </row>
     <row r="139" ht="23" customHeight="1">
       <c r="A139" s="14" t="n"/>
@@ -5351,6 +5780,9 @@
         <f>IF(A139="","",IF(COUNTIF($A$2:$A$501,A139)&gt;1,"Duplicate lot ID",IF(OR(B139="",H139="",I139="",J139=""),"Complete required fields",IF(L139&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q139" s="14" t="n"/>
+      <c r="R139" s="14" t="n"/>
+      <c r="S139" s="14" t="n"/>
     </row>
     <row r="140" ht="23" customHeight="1">
       <c r="A140" s="9" t="n"/>
@@ -5384,6 +5816,9 @@
         <f>IF(A140="","",IF(COUNTIF($A$2:$A$501,A140)&gt;1,"Duplicate lot ID",IF(OR(B140="",H140="",I140="",J140=""),"Complete required fields",IF(L140&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q140" s="9" t="n"/>
+      <c r="R140" s="9" t="n"/>
+      <c r="S140" s="9" t="n"/>
     </row>
     <row r="141" ht="23" customHeight="1">
       <c r="A141" s="14" t="n"/>
@@ -5417,6 +5852,9 @@
         <f>IF(A141="","",IF(COUNTIF($A$2:$A$501,A141)&gt;1,"Duplicate lot ID",IF(OR(B141="",H141="",I141="",J141=""),"Complete required fields",IF(L141&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q141" s="14" t="n"/>
+      <c r="R141" s="14" t="n"/>
+      <c r="S141" s="14" t="n"/>
     </row>
     <row r="142" ht="23" customHeight="1">
       <c r="A142" s="9" t="n"/>
@@ -5450,6 +5888,9 @@
         <f>IF(A142="","",IF(COUNTIF($A$2:$A$501,A142)&gt;1,"Duplicate lot ID",IF(OR(B142="",H142="",I142="",J142=""),"Complete required fields",IF(L142&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q142" s="9" t="n"/>
+      <c r="R142" s="9" t="n"/>
+      <c r="S142" s="9" t="n"/>
     </row>
     <row r="143" ht="23" customHeight="1">
       <c r="A143" s="14" t="n"/>
@@ -5483,6 +5924,9 @@
         <f>IF(A143="","",IF(COUNTIF($A$2:$A$501,A143)&gt;1,"Duplicate lot ID",IF(OR(B143="",H143="",I143="",J143=""),"Complete required fields",IF(L143&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q143" s="14" t="n"/>
+      <c r="R143" s="14" t="n"/>
+      <c r="S143" s="14" t="n"/>
     </row>
     <row r="144" ht="23" customHeight="1">
       <c r="A144" s="9" t="n"/>
@@ -5516,6 +5960,9 @@
         <f>IF(A144="","",IF(COUNTIF($A$2:$A$501,A144)&gt;1,"Duplicate lot ID",IF(OR(B144="",H144="",I144="",J144=""),"Complete required fields",IF(L144&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q144" s="9" t="n"/>
+      <c r="R144" s="9" t="n"/>
+      <c r="S144" s="9" t="n"/>
     </row>
     <row r="145" ht="23" customHeight="1">
       <c r="A145" s="14" t="n"/>
@@ -5549,6 +5996,9 @@
         <f>IF(A145="","",IF(COUNTIF($A$2:$A$501,A145)&gt;1,"Duplicate lot ID",IF(OR(B145="",H145="",I145="",J145=""),"Complete required fields",IF(L145&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q145" s="14" t="n"/>
+      <c r="R145" s="14" t="n"/>
+      <c r="S145" s="14" t="n"/>
     </row>
     <row r="146" ht="23" customHeight="1">
       <c r="A146" s="9" t="n"/>
@@ -5582,6 +6032,9 @@
         <f>IF(A146="","",IF(COUNTIF($A$2:$A$501,A146)&gt;1,"Duplicate lot ID",IF(OR(B146="",H146="",I146="",J146=""),"Complete required fields",IF(L146&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q146" s="9" t="n"/>
+      <c r="R146" s="9" t="n"/>
+      <c r="S146" s="9" t="n"/>
     </row>
     <row r="147" ht="23" customHeight="1">
       <c r="A147" s="14" t="n"/>
@@ -5615,6 +6068,9 @@
         <f>IF(A147="","",IF(COUNTIF($A$2:$A$501,A147)&gt;1,"Duplicate lot ID",IF(OR(B147="",H147="",I147="",J147=""),"Complete required fields",IF(L147&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q147" s="14" t="n"/>
+      <c r="R147" s="14" t="n"/>
+      <c r="S147" s="14" t="n"/>
     </row>
     <row r="148" ht="23" customHeight="1">
       <c r="A148" s="9" t="n"/>
@@ -5648,6 +6104,9 @@
         <f>IF(A148="","",IF(COUNTIF($A$2:$A$501,A148)&gt;1,"Duplicate lot ID",IF(OR(B148="",H148="",I148="",J148=""),"Complete required fields",IF(L148&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q148" s="9" t="n"/>
+      <c r="R148" s="9" t="n"/>
+      <c r="S148" s="9" t="n"/>
     </row>
     <row r="149" ht="23" customHeight="1">
       <c r="A149" s="14" t="n"/>
@@ -5681,6 +6140,9 @@
         <f>IF(A149="","",IF(COUNTIF($A$2:$A$501,A149)&gt;1,"Duplicate lot ID",IF(OR(B149="",H149="",I149="",J149=""),"Complete required fields",IF(L149&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q149" s="14" t="n"/>
+      <c r="R149" s="14" t="n"/>
+      <c r="S149" s="14" t="n"/>
     </row>
     <row r="150" ht="23" customHeight="1">
       <c r="A150" s="9" t="n"/>
@@ -5714,6 +6176,9 @@
         <f>IF(A150="","",IF(COUNTIF($A$2:$A$501,A150)&gt;1,"Duplicate lot ID",IF(OR(B150="",H150="",I150="",J150=""),"Complete required fields",IF(L150&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q150" s="9" t="n"/>
+      <c r="R150" s="9" t="n"/>
+      <c r="S150" s="9" t="n"/>
     </row>
     <row r="151" ht="23" customHeight="1">
       <c r="A151" s="14" t="n"/>
@@ -5747,6 +6212,9 @@
         <f>IF(A151="","",IF(COUNTIF($A$2:$A$501,A151)&gt;1,"Duplicate lot ID",IF(OR(B151="",H151="",I151="",J151=""),"Complete required fields",IF(L151&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q151" s="14" t="n"/>
+      <c r="R151" s="14" t="n"/>
+      <c r="S151" s="14" t="n"/>
     </row>
     <row r="152" ht="23" customHeight="1">
       <c r="A152" s="9" t="n"/>
@@ -5780,6 +6248,9 @@
         <f>IF(A152="","",IF(COUNTIF($A$2:$A$501,A152)&gt;1,"Duplicate lot ID",IF(OR(B152="",H152="",I152="",J152=""),"Complete required fields",IF(L152&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q152" s="9" t="n"/>
+      <c r="R152" s="9" t="n"/>
+      <c r="S152" s="9" t="n"/>
     </row>
     <row r="153" ht="23" customHeight="1">
       <c r="A153" s="14" t="n"/>
@@ -5813,6 +6284,9 @@
         <f>IF(A153="","",IF(COUNTIF($A$2:$A$501,A153)&gt;1,"Duplicate lot ID",IF(OR(B153="",H153="",I153="",J153=""),"Complete required fields",IF(L153&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q153" s="14" t="n"/>
+      <c r="R153" s="14" t="n"/>
+      <c r="S153" s="14" t="n"/>
     </row>
     <row r="154" ht="23" customHeight="1">
       <c r="A154" s="9" t="n"/>
@@ -5846,6 +6320,9 @@
         <f>IF(A154="","",IF(COUNTIF($A$2:$A$501,A154)&gt;1,"Duplicate lot ID",IF(OR(B154="",H154="",I154="",J154=""),"Complete required fields",IF(L154&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q154" s="9" t="n"/>
+      <c r="R154" s="9" t="n"/>
+      <c r="S154" s="9" t="n"/>
     </row>
     <row r="155" ht="23" customHeight="1">
       <c r="A155" s="14" t="n"/>
@@ -5879,6 +6356,9 @@
         <f>IF(A155="","",IF(COUNTIF($A$2:$A$501,A155)&gt;1,"Duplicate lot ID",IF(OR(B155="",H155="",I155="",J155=""),"Complete required fields",IF(L155&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q155" s="14" t="n"/>
+      <c r="R155" s="14" t="n"/>
+      <c r="S155" s="14" t="n"/>
     </row>
     <row r="156" ht="23" customHeight="1">
       <c r="A156" s="9" t="n"/>
@@ -5912,6 +6392,9 @@
         <f>IF(A156="","",IF(COUNTIF($A$2:$A$501,A156)&gt;1,"Duplicate lot ID",IF(OR(B156="",H156="",I156="",J156=""),"Complete required fields",IF(L156&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q156" s="9" t="n"/>
+      <c r="R156" s="9" t="n"/>
+      <c r="S156" s="9" t="n"/>
     </row>
     <row r="157" ht="23" customHeight="1">
       <c r="A157" s="14" t="n"/>
@@ -5945,6 +6428,9 @@
         <f>IF(A157="","",IF(COUNTIF($A$2:$A$501,A157)&gt;1,"Duplicate lot ID",IF(OR(B157="",H157="",I157="",J157=""),"Complete required fields",IF(L157&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q157" s="14" t="n"/>
+      <c r="R157" s="14" t="n"/>
+      <c r="S157" s="14" t="n"/>
     </row>
     <row r="158" ht="23" customHeight="1">
       <c r="A158" s="9" t="n"/>
@@ -5978,6 +6464,9 @@
         <f>IF(A158="","",IF(COUNTIF($A$2:$A$501,A158)&gt;1,"Duplicate lot ID",IF(OR(B158="",H158="",I158="",J158=""),"Complete required fields",IF(L158&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q158" s="9" t="n"/>
+      <c r="R158" s="9" t="n"/>
+      <c r="S158" s="9" t="n"/>
     </row>
     <row r="159" ht="23" customHeight="1">
       <c r="A159" s="14" t="n"/>
@@ -6011,6 +6500,9 @@
         <f>IF(A159="","",IF(COUNTIF($A$2:$A$501,A159)&gt;1,"Duplicate lot ID",IF(OR(B159="",H159="",I159="",J159=""),"Complete required fields",IF(L159&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q159" s="14" t="n"/>
+      <c r="R159" s="14" t="n"/>
+      <c r="S159" s="14" t="n"/>
     </row>
     <row r="160" ht="23" customHeight="1">
       <c r="A160" s="9" t="n"/>
@@ -6044,6 +6536,9 @@
         <f>IF(A160="","",IF(COUNTIF($A$2:$A$501,A160)&gt;1,"Duplicate lot ID",IF(OR(B160="",H160="",I160="",J160=""),"Complete required fields",IF(L160&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q160" s="9" t="n"/>
+      <c r="R160" s="9" t="n"/>
+      <c r="S160" s="9" t="n"/>
     </row>
     <row r="161" ht="23" customHeight="1">
       <c r="A161" s="14" t="n"/>
@@ -6077,6 +6572,9 @@
         <f>IF(A161="","",IF(COUNTIF($A$2:$A$501,A161)&gt;1,"Duplicate lot ID",IF(OR(B161="",H161="",I161="",J161=""),"Complete required fields",IF(L161&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q161" s="14" t="n"/>
+      <c r="R161" s="14" t="n"/>
+      <c r="S161" s="14" t="n"/>
     </row>
     <row r="162" ht="23" customHeight="1">
       <c r="A162" s="9" t="n"/>
@@ -6110,6 +6608,9 @@
         <f>IF(A162="","",IF(COUNTIF($A$2:$A$501,A162)&gt;1,"Duplicate lot ID",IF(OR(B162="",H162="",I162="",J162=""),"Complete required fields",IF(L162&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q162" s="9" t="n"/>
+      <c r="R162" s="9" t="n"/>
+      <c r="S162" s="9" t="n"/>
     </row>
     <row r="163" ht="23" customHeight="1">
       <c r="A163" s="14" t="n"/>
@@ -6143,6 +6644,9 @@
         <f>IF(A163="","",IF(COUNTIF($A$2:$A$501,A163)&gt;1,"Duplicate lot ID",IF(OR(B163="",H163="",I163="",J163=""),"Complete required fields",IF(L163&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q163" s="14" t="n"/>
+      <c r="R163" s="14" t="n"/>
+      <c r="S163" s="14" t="n"/>
     </row>
     <row r="164" ht="23" customHeight="1">
       <c r="A164" s="9" t="n"/>
@@ -6176,6 +6680,9 @@
         <f>IF(A164="","",IF(COUNTIF($A$2:$A$501,A164)&gt;1,"Duplicate lot ID",IF(OR(B164="",H164="",I164="",J164=""),"Complete required fields",IF(L164&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q164" s="9" t="n"/>
+      <c r="R164" s="9" t="n"/>
+      <c r="S164" s="9" t="n"/>
     </row>
     <row r="165" ht="23" customHeight="1">
       <c r="A165" s="14" t="n"/>
@@ -6209,6 +6716,9 @@
         <f>IF(A165="","",IF(COUNTIF($A$2:$A$501,A165)&gt;1,"Duplicate lot ID",IF(OR(B165="",H165="",I165="",J165=""),"Complete required fields",IF(L165&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q165" s="14" t="n"/>
+      <c r="R165" s="14" t="n"/>
+      <c r="S165" s="14" t="n"/>
     </row>
     <row r="166" ht="23" customHeight="1">
       <c r="A166" s="9" t="n"/>
@@ -6242,6 +6752,9 @@
         <f>IF(A166="","",IF(COUNTIF($A$2:$A$501,A166)&gt;1,"Duplicate lot ID",IF(OR(B166="",H166="",I166="",J166=""),"Complete required fields",IF(L166&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q166" s="9" t="n"/>
+      <c r="R166" s="9" t="n"/>
+      <c r="S166" s="9" t="n"/>
     </row>
     <row r="167" ht="23" customHeight="1">
       <c r="A167" s="14" t="n"/>
@@ -6275,6 +6788,9 @@
         <f>IF(A167="","",IF(COUNTIF($A$2:$A$501,A167)&gt;1,"Duplicate lot ID",IF(OR(B167="",H167="",I167="",J167=""),"Complete required fields",IF(L167&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q167" s="14" t="n"/>
+      <c r="R167" s="14" t="n"/>
+      <c r="S167" s="14" t="n"/>
     </row>
     <row r="168" ht="23" customHeight="1">
       <c r="A168" s="9" t="n"/>
@@ -6308,6 +6824,9 @@
         <f>IF(A168="","",IF(COUNTIF($A$2:$A$501,A168)&gt;1,"Duplicate lot ID",IF(OR(B168="",H168="",I168="",J168=""),"Complete required fields",IF(L168&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q168" s="9" t="n"/>
+      <c r="R168" s="9" t="n"/>
+      <c r="S168" s="9" t="n"/>
     </row>
     <row r="169" ht="23" customHeight="1">
       <c r="A169" s="14" t="n"/>
@@ -6341,6 +6860,9 @@
         <f>IF(A169="","",IF(COUNTIF($A$2:$A$501,A169)&gt;1,"Duplicate lot ID",IF(OR(B169="",H169="",I169="",J169=""),"Complete required fields",IF(L169&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q169" s="14" t="n"/>
+      <c r="R169" s="14" t="n"/>
+      <c r="S169" s="14" t="n"/>
     </row>
     <row r="170" ht="23" customHeight="1">
       <c r="A170" s="9" t="n"/>
@@ -6374,6 +6896,9 @@
         <f>IF(A170="","",IF(COUNTIF($A$2:$A$501,A170)&gt;1,"Duplicate lot ID",IF(OR(B170="",H170="",I170="",J170=""),"Complete required fields",IF(L170&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q170" s="9" t="n"/>
+      <c r="R170" s="9" t="n"/>
+      <c r="S170" s="9" t="n"/>
     </row>
     <row r="171" ht="23" customHeight="1">
       <c r="A171" s="14" t="n"/>
@@ -6407,6 +6932,9 @@
         <f>IF(A171="","",IF(COUNTIF($A$2:$A$501,A171)&gt;1,"Duplicate lot ID",IF(OR(B171="",H171="",I171="",J171=""),"Complete required fields",IF(L171&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q171" s="14" t="n"/>
+      <c r="R171" s="14" t="n"/>
+      <c r="S171" s="14" t="n"/>
     </row>
     <row r="172" ht="23" customHeight="1">
       <c r="A172" s="9" t="n"/>
@@ -6440,6 +6968,9 @@
         <f>IF(A172="","",IF(COUNTIF($A$2:$A$501,A172)&gt;1,"Duplicate lot ID",IF(OR(B172="",H172="",I172="",J172=""),"Complete required fields",IF(L172&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q172" s="9" t="n"/>
+      <c r="R172" s="9" t="n"/>
+      <c r="S172" s="9" t="n"/>
     </row>
     <row r="173" ht="23" customHeight="1">
       <c r="A173" s="14" t="n"/>
@@ -6473,6 +7004,9 @@
         <f>IF(A173="","",IF(COUNTIF($A$2:$A$501,A173)&gt;1,"Duplicate lot ID",IF(OR(B173="",H173="",I173="",J173=""),"Complete required fields",IF(L173&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q173" s="14" t="n"/>
+      <c r="R173" s="14" t="n"/>
+      <c r="S173" s="14" t="n"/>
     </row>
     <row r="174" ht="23" customHeight="1">
       <c r="A174" s="9" t="n"/>
@@ -6506,6 +7040,9 @@
         <f>IF(A174="","",IF(COUNTIF($A$2:$A$501,A174)&gt;1,"Duplicate lot ID",IF(OR(B174="",H174="",I174="",J174=""),"Complete required fields",IF(L174&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q174" s="9" t="n"/>
+      <c r="R174" s="9" t="n"/>
+      <c r="S174" s="9" t="n"/>
     </row>
     <row r="175" ht="23" customHeight="1">
       <c r="A175" s="14" t="n"/>
@@ -6539,6 +7076,9 @@
         <f>IF(A175="","",IF(COUNTIF($A$2:$A$501,A175)&gt;1,"Duplicate lot ID",IF(OR(B175="",H175="",I175="",J175=""),"Complete required fields",IF(L175&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q175" s="14" t="n"/>
+      <c r="R175" s="14" t="n"/>
+      <c r="S175" s="14" t="n"/>
     </row>
     <row r="176" ht="23" customHeight="1">
       <c r="A176" s="9" t="n"/>
@@ -6572,6 +7112,9 @@
         <f>IF(A176="","",IF(COUNTIF($A$2:$A$501,A176)&gt;1,"Duplicate lot ID",IF(OR(B176="",H176="",I176="",J176=""),"Complete required fields",IF(L176&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q176" s="9" t="n"/>
+      <c r="R176" s="9" t="n"/>
+      <c r="S176" s="9" t="n"/>
     </row>
     <row r="177" ht="23" customHeight="1">
       <c r="A177" s="14" t="n"/>
@@ -6605,6 +7148,9 @@
         <f>IF(A177="","",IF(COUNTIF($A$2:$A$501,A177)&gt;1,"Duplicate lot ID",IF(OR(B177="",H177="",I177="",J177=""),"Complete required fields",IF(L177&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q177" s="14" t="n"/>
+      <c r="R177" s="14" t="n"/>
+      <c r="S177" s="14" t="n"/>
     </row>
     <row r="178" ht="23" customHeight="1">
       <c r="A178" s="9" t="n"/>
@@ -6638,6 +7184,9 @@
         <f>IF(A178="","",IF(COUNTIF($A$2:$A$501,A178)&gt;1,"Duplicate lot ID",IF(OR(B178="",H178="",I178="",J178=""),"Complete required fields",IF(L178&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q178" s="9" t="n"/>
+      <c r="R178" s="9" t="n"/>
+      <c r="S178" s="9" t="n"/>
     </row>
     <row r="179" ht="23" customHeight="1">
       <c r="A179" s="14" t="n"/>
@@ -6671,6 +7220,9 @@
         <f>IF(A179="","",IF(COUNTIF($A$2:$A$501,A179)&gt;1,"Duplicate lot ID",IF(OR(B179="",H179="",I179="",J179=""),"Complete required fields",IF(L179&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q179" s="14" t="n"/>
+      <c r="R179" s="14" t="n"/>
+      <c r="S179" s="14" t="n"/>
     </row>
     <row r="180" ht="23" customHeight="1">
       <c r="A180" s="9" t="n"/>
@@ -6704,6 +7256,9 @@
         <f>IF(A180="","",IF(COUNTIF($A$2:$A$501,A180)&gt;1,"Duplicate lot ID",IF(OR(B180="",H180="",I180="",J180=""),"Complete required fields",IF(L180&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q180" s="9" t="n"/>
+      <c r="R180" s="9" t="n"/>
+      <c r="S180" s="9" t="n"/>
     </row>
     <row r="181" ht="23" customHeight="1">
       <c r="A181" s="14" t="n"/>
@@ -6737,6 +7292,9 @@
         <f>IF(A181="","",IF(COUNTIF($A$2:$A$501,A181)&gt;1,"Duplicate lot ID",IF(OR(B181="",H181="",I181="",J181=""),"Complete required fields",IF(L181&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q181" s="14" t="n"/>
+      <c r="R181" s="14" t="n"/>
+      <c r="S181" s="14" t="n"/>
     </row>
     <row r="182" ht="23" customHeight="1">
       <c r="A182" s="9" t="n"/>
@@ -6770,6 +7328,9 @@
         <f>IF(A182="","",IF(COUNTIF($A$2:$A$501,A182)&gt;1,"Duplicate lot ID",IF(OR(B182="",H182="",I182="",J182=""),"Complete required fields",IF(L182&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q182" s="9" t="n"/>
+      <c r="R182" s="9" t="n"/>
+      <c r="S182" s="9" t="n"/>
     </row>
     <row r="183" ht="23" customHeight="1">
       <c r="A183" s="14" t="n"/>
@@ -6803,6 +7364,9 @@
         <f>IF(A183="","",IF(COUNTIF($A$2:$A$501,A183)&gt;1,"Duplicate lot ID",IF(OR(B183="",H183="",I183="",J183=""),"Complete required fields",IF(L183&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q183" s="14" t="n"/>
+      <c r="R183" s="14" t="n"/>
+      <c r="S183" s="14" t="n"/>
     </row>
     <row r="184" ht="23" customHeight="1">
       <c r="A184" s="9" t="n"/>
@@ -6836,6 +7400,9 @@
         <f>IF(A184="","",IF(COUNTIF($A$2:$A$501,A184)&gt;1,"Duplicate lot ID",IF(OR(B184="",H184="",I184="",J184=""),"Complete required fields",IF(L184&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q184" s="9" t="n"/>
+      <c r="R184" s="9" t="n"/>
+      <c r="S184" s="9" t="n"/>
     </row>
     <row r="185" ht="23" customHeight="1">
       <c r="A185" s="14" t="n"/>
@@ -6869,6 +7436,9 @@
         <f>IF(A185="","",IF(COUNTIF($A$2:$A$501,A185)&gt;1,"Duplicate lot ID",IF(OR(B185="",H185="",I185="",J185=""),"Complete required fields",IF(L185&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q185" s="14" t="n"/>
+      <c r="R185" s="14" t="n"/>
+      <c r="S185" s="14" t="n"/>
     </row>
     <row r="186" ht="23" customHeight="1">
       <c r="A186" s="9" t="n"/>
@@ -6902,6 +7472,9 @@
         <f>IF(A186="","",IF(COUNTIF($A$2:$A$501,A186)&gt;1,"Duplicate lot ID",IF(OR(B186="",H186="",I186="",J186=""),"Complete required fields",IF(L186&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q186" s="9" t="n"/>
+      <c r="R186" s="9" t="n"/>
+      <c r="S186" s="9" t="n"/>
     </row>
     <row r="187" ht="23" customHeight="1">
       <c r="A187" s="14" t="n"/>
@@ -6935,6 +7508,9 @@
         <f>IF(A187="","",IF(COUNTIF($A$2:$A$501,A187)&gt;1,"Duplicate lot ID",IF(OR(B187="",H187="",I187="",J187=""),"Complete required fields",IF(L187&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q187" s="14" t="n"/>
+      <c r="R187" s="14" t="n"/>
+      <c r="S187" s="14" t="n"/>
     </row>
     <row r="188" ht="23" customHeight="1">
       <c r="A188" s="9" t="n"/>
@@ -6968,6 +7544,9 @@
         <f>IF(A188="","",IF(COUNTIF($A$2:$A$501,A188)&gt;1,"Duplicate lot ID",IF(OR(B188="",H188="",I188="",J188=""),"Complete required fields",IF(L188&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q188" s="9" t="n"/>
+      <c r="R188" s="9" t="n"/>
+      <c r="S188" s="9" t="n"/>
     </row>
     <row r="189" ht="23" customHeight="1">
       <c r="A189" s="14" t="n"/>
@@ -7001,6 +7580,9 @@
         <f>IF(A189="","",IF(COUNTIF($A$2:$A$501,A189)&gt;1,"Duplicate lot ID",IF(OR(B189="",H189="",I189="",J189=""),"Complete required fields",IF(L189&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q189" s="14" t="n"/>
+      <c r="R189" s="14" t="n"/>
+      <c r="S189" s="14" t="n"/>
     </row>
     <row r="190" ht="23" customHeight="1">
       <c r="A190" s="9" t="n"/>
@@ -7034,6 +7616,9 @@
         <f>IF(A190="","",IF(COUNTIF($A$2:$A$501,A190)&gt;1,"Duplicate lot ID",IF(OR(B190="",H190="",I190="",J190=""),"Complete required fields",IF(L190&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q190" s="9" t="n"/>
+      <c r="R190" s="9" t="n"/>
+      <c r="S190" s="9" t="n"/>
     </row>
     <row r="191" ht="23" customHeight="1">
       <c r="A191" s="14" t="n"/>
@@ -7067,6 +7652,9 @@
         <f>IF(A191="","",IF(COUNTIF($A$2:$A$501,A191)&gt;1,"Duplicate lot ID",IF(OR(B191="",H191="",I191="",J191=""),"Complete required fields",IF(L191&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q191" s="14" t="n"/>
+      <c r="R191" s="14" t="n"/>
+      <c r="S191" s="14" t="n"/>
     </row>
     <row r="192" ht="23" customHeight="1">
       <c r="A192" s="9" t="n"/>
@@ -7100,6 +7688,9 @@
         <f>IF(A192="","",IF(COUNTIF($A$2:$A$501,A192)&gt;1,"Duplicate lot ID",IF(OR(B192="",H192="",I192="",J192=""),"Complete required fields",IF(L192&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q192" s="9" t="n"/>
+      <c r="R192" s="9" t="n"/>
+      <c r="S192" s="9" t="n"/>
     </row>
     <row r="193" ht="23" customHeight="1">
       <c r="A193" s="14" t="n"/>
@@ -7133,6 +7724,9 @@
         <f>IF(A193="","",IF(COUNTIF($A$2:$A$501,A193)&gt;1,"Duplicate lot ID",IF(OR(B193="",H193="",I193="",J193=""),"Complete required fields",IF(L193&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q193" s="14" t="n"/>
+      <c r="R193" s="14" t="n"/>
+      <c r="S193" s="14" t="n"/>
     </row>
     <row r="194" ht="23" customHeight="1">
       <c r="A194" s="9" t="n"/>
@@ -7166,6 +7760,9 @@
         <f>IF(A194="","",IF(COUNTIF($A$2:$A$501,A194)&gt;1,"Duplicate lot ID",IF(OR(B194="",H194="",I194="",J194=""),"Complete required fields",IF(L194&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q194" s="9" t="n"/>
+      <c r="R194" s="9" t="n"/>
+      <c r="S194" s="9" t="n"/>
     </row>
     <row r="195" ht="23" customHeight="1">
       <c r="A195" s="14" t="n"/>
@@ -7199,6 +7796,9 @@
         <f>IF(A195="","",IF(COUNTIF($A$2:$A$501,A195)&gt;1,"Duplicate lot ID",IF(OR(B195="",H195="",I195="",J195=""),"Complete required fields",IF(L195&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q195" s="14" t="n"/>
+      <c r="R195" s="14" t="n"/>
+      <c r="S195" s="14" t="n"/>
     </row>
     <row r="196" ht="23" customHeight="1">
       <c r="A196" s="9" t="n"/>
@@ -7232,6 +7832,9 @@
         <f>IF(A196="","",IF(COUNTIF($A$2:$A$501,A196)&gt;1,"Duplicate lot ID",IF(OR(B196="",H196="",I196="",J196=""),"Complete required fields",IF(L196&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q196" s="9" t="n"/>
+      <c r="R196" s="9" t="n"/>
+      <c r="S196" s="9" t="n"/>
     </row>
     <row r="197" ht="23" customHeight="1">
       <c r="A197" s="14" t="n"/>
@@ -7265,6 +7868,9 @@
         <f>IF(A197="","",IF(COUNTIF($A$2:$A$501,A197)&gt;1,"Duplicate lot ID",IF(OR(B197="",H197="",I197="",J197=""),"Complete required fields",IF(L197&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q197" s="14" t="n"/>
+      <c r="R197" s="14" t="n"/>
+      <c r="S197" s="14" t="n"/>
     </row>
     <row r="198" ht="23" customHeight="1">
       <c r="A198" s="9" t="n"/>
@@ -7298,6 +7904,9 @@
         <f>IF(A198="","",IF(COUNTIF($A$2:$A$501,A198)&gt;1,"Duplicate lot ID",IF(OR(B198="",H198="",I198="",J198=""),"Complete required fields",IF(L198&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q198" s="9" t="n"/>
+      <c r="R198" s="9" t="n"/>
+      <c r="S198" s="9" t="n"/>
     </row>
     <row r="199" ht="23" customHeight="1">
       <c r="A199" s="14" t="n"/>
@@ -7331,6 +7940,9 @@
         <f>IF(A199="","",IF(COUNTIF($A$2:$A$501,A199)&gt;1,"Duplicate lot ID",IF(OR(B199="",H199="",I199="",J199=""),"Complete required fields",IF(L199&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q199" s="14" t="n"/>
+      <c r="R199" s="14" t="n"/>
+      <c r="S199" s="14" t="n"/>
     </row>
     <row r="200" ht="23" customHeight="1">
       <c r="A200" s="9" t="n"/>
@@ -7364,6 +7976,9 @@
         <f>IF(A200="","",IF(COUNTIF($A$2:$A$501,A200)&gt;1,"Duplicate lot ID",IF(OR(B200="",H200="",I200="",J200=""),"Complete required fields",IF(L200&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q200" s="9" t="n"/>
+      <c r="R200" s="9" t="n"/>
+      <c r="S200" s="9" t="n"/>
     </row>
     <row r="201" ht="23" customHeight="1">
       <c r="A201" s="14" t="n"/>
@@ -7397,6 +8012,9 @@
         <f>IF(A201="","",IF(COUNTIF($A$2:$A$501,A201)&gt;1,"Duplicate lot ID",IF(OR(B201="",H201="",I201="",J201=""),"Complete required fields",IF(L201&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q201" s="14" t="n"/>
+      <c r="R201" s="14" t="n"/>
+      <c r="S201" s="14" t="n"/>
     </row>
     <row r="202" ht="23" customHeight="1">
       <c r="A202" s="9" t="n"/>
@@ -7430,6 +8048,9 @@
         <f>IF(A202="","",IF(COUNTIF($A$2:$A$501,A202)&gt;1,"Duplicate lot ID",IF(OR(B202="",H202="",I202="",J202=""),"Complete required fields",IF(L202&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q202" s="9" t="n"/>
+      <c r="R202" s="9" t="n"/>
+      <c r="S202" s="9" t="n"/>
     </row>
     <row r="203" ht="23" customHeight="1">
       <c r="A203" s="14" t="n"/>
@@ -7463,6 +8084,9 @@
         <f>IF(A203="","",IF(COUNTIF($A$2:$A$501,A203)&gt;1,"Duplicate lot ID",IF(OR(B203="",H203="",I203="",J203=""),"Complete required fields",IF(L203&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q203" s="14" t="n"/>
+      <c r="R203" s="14" t="n"/>
+      <c r="S203" s="14" t="n"/>
     </row>
     <row r="204" ht="23" customHeight="1">
       <c r="A204" s="9" t="n"/>
@@ -7496,6 +8120,9 @@
         <f>IF(A204="","",IF(COUNTIF($A$2:$A$501,A204)&gt;1,"Duplicate lot ID",IF(OR(B204="",H204="",I204="",J204=""),"Complete required fields",IF(L204&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q204" s="9" t="n"/>
+      <c r="R204" s="9" t="n"/>
+      <c r="S204" s="9" t="n"/>
     </row>
     <row r="205" ht="23" customHeight="1">
       <c r="A205" s="14" t="n"/>
@@ -7529,6 +8156,9 @@
         <f>IF(A205="","",IF(COUNTIF($A$2:$A$501,A205)&gt;1,"Duplicate lot ID",IF(OR(B205="",H205="",I205="",J205=""),"Complete required fields",IF(L205&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q205" s="14" t="n"/>
+      <c r="R205" s="14" t="n"/>
+      <c r="S205" s="14" t="n"/>
     </row>
     <row r="206" ht="23" customHeight="1">
       <c r="A206" s="9" t="n"/>
@@ -7562,6 +8192,9 @@
         <f>IF(A206="","",IF(COUNTIF($A$2:$A$501,A206)&gt;1,"Duplicate lot ID",IF(OR(B206="",H206="",I206="",J206=""),"Complete required fields",IF(L206&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q206" s="9" t="n"/>
+      <c r="R206" s="9" t="n"/>
+      <c r="S206" s="9" t="n"/>
     </row>
     <row r="207" ht="23" customHeight="1">
       <c r="A207" s="14" t="n"/>
@@ -7595,6 +8228,9 @@
         <f>IF(A207="","",IF(COUNTIF($A$2:$A$501,A207)&gt;1,"Duplicate lot ID",IF(OR(B207="",H207="",I207="",J207=""),"Complete required fields",IF(L207&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q207" s="14" t="n"/>
+      <c r="R207" s="14" t="n"/>
+      <c r="S207" s="14" t="n"/>
     </row>
     <row r="208" ht="23" customHeight="1">
       <c r="A208" s="9" t="n"/>
@@ -7628,6 +8264,9 @@
         <f>IF(A208="","",IF(COUNTIF($A$2:$A$501,A208)&gt;1,"Duplicate lot ID",IF(OR(B208="",H208="",I208="",J208=""),"Complete required fields",IF(L208&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q208" s="9" t="n"/>
+      <c r="R208" s="9" t="n"/>
+      <c r="S208" s="9" t="n"/>
     </row>
     <row r="209" ht="23" customHeight="1">
       <c r="A209" s="14" t="n"/>
@@ -7661,6 +8300,9 @@
         <f>IF(A209="","",IF(COUNTIF($A$2:$A$501,A209)&gt;1,"Duplicate lot ID",IF(OR(B209="",H209="",I209="",J209=""),"Complete required fields",IF(L209&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q209" s="14" t="n"/>
+      <c r="R209" s="14" t="n"/>
+      <c r="S209" s="14" t="n"/>
     </row>
     <row r="210" ht="23" customHeight="1">
       <c r="A210" s="9" t="n"/>
@@ -7694,6 +8336,9 @@
         <f>IF(A210="","",IF(COUNTIF($A$2:$A$501,A210)&gt;1,"Duplicate lot ID",IF(OR(B210="",H210="",I210="",J210=""),"Complete required fields",IF(L210&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q210" s="9" t="n"/>
+      <c r="R210" s="9" t="n"/>
+      <c r="S210" s="9" t="n"/>
     </row>
     <row r="211" ht="23" customHeight="1">
       <c r="A211" s="14" t="n"/>
@@ -7727,6 +8372,9 @@
         <f>IF(A211="","",IF(COUNTIF($A$2:$A$501,A211)&gt;1,"Duplicate lot ID",IF(OR(B211="",H211="",I211="",J211=""),"Complete required fields",IF(L211&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q211" s="14" t="n"/>
+      <c r="R211" s="14" t="n"/>
+      <c r="S211" s="14" t="n"/>
     </row>
     <row r="212" ht="23" customHeight="1">
       <c r="A212" s="9" t="n"/>
@@ -7760,6 +8408,9 @@
         <f>IF(A212="","",IF(COUNTIF($A$2:$A$501,A212)&gt;1,"Duplicate lot ID",IF(OR(B212="",H212="",I212="",J212=""),"Complete required fields",IF(L212&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q212" s="9" t="n"/>
+      <c r="R212" s="9" t="n"/>
+      <c r="S212" s="9" t="n"/>
     </row>
     <row r="213" ht="23" customHeight="1">
       <c r="A213" s="14" t="n"/>
@@ -7793,6 +8444,9 @@
         <f>IF(A213="","",IF(COUNTIF($A$2:$A$501,A213)&gt;1,"Duplicate lot ID",IF(OR(B213="",H213="",I213="",J213=""),"Complete required fields",IF(L213&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q213" s="14" t="n"/>
+      <c r="R213" s="14" t="n"/>
+      <c r="S213" s="14" t="n"/>
     </row>
     <row r="214" ht="23" customHeight="1">
       <c r="A214" s="9" t="n"/>
@@ -7826,6 +8480,9 @@
         <f>IF(A214="","",IF(COUNTIF($A$2:$A$501,A214)&gt;1,"Duplicate lot ID",IF(OR(B214="",H214="",I214="",J214=""),"Complete required fields",IF(L214&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q214" s="9" t="n"/>
+      <c r="R214" s="9" t="n"/>
+      <c r="S214" s="9" t="n"/>
     </row>
     <row r="215" ht="23" customHeight="1">
       <c r="A215" s="14" t="n"/>
@@ -7859,6 +8516,9 @@
         <f>IF(A215="","",IF(COUNTIF($A$2:$A$501,A215)&gt;1,"Duplicate lot ID",IF(OR(B215="",H215="",I215="",J215=""),"Complete required fields",IF(L215&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q215" s="14" t="n"/>
+      <c r="R215" s="14" t="n"/>
+      <c r="S215" s="14" t="n"/>
     </row>
     <row r="216" ht="23" customHeight="1">
       <c r="A216" s="9" t="n"/>
@@ -7892,6 +8552,9 @@
         <f>IF(A216="","",IF(COUNTIF($A$2:$A$501,A216)&gt;1,"Duplicate lot ID",IF(OR(B216="",H216="",I216="",J216=""),"Complete required fields",IF(L216&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q216" s="9" t="n"/>
+      <c r="R216" s="9" t="n"/>
+      <c r="S216" s="9" t="n"/>
     </row>
     <row r="217" ht="23" customHeight="1">
       <c r="A217" s="14" t="n"/>
@@ -7925,6 +8588,9 @@
         <f>IF(A217="","",IF(COUNTIF($A$2:$A$501,A217)&gt;1,"Duplicate lot ID",IF(OR(B217="",H217="",I217="",J217=""),"Complete required fields",IF(L217&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q217" s="14" t="n"/>
+      <c r="R217" s="14" t="n"/>
+      <c r="S217" s="14" t="n"/>
     </row>
     <row r="218" ht="23" customHeight="1">
       <c r="A218" s="9" t="n"/>
@@ -7958,6 +8624,9 @@
         <f>IF(A218="","",IF(COUNTIF($A$2:$A$501,A218)&gt;1,"Duplicate lot ID",IF(OR(B218="",H218="",I218="",J218=""),"Complete required fields",IF(L218&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q218" s="9" t="n"/>
+      <c r="R218" s="9" t="n"/>
+      <c r="S218" s="9" t="n"/>
     </row>
     <row r="219" ht="23" customHeight="1">
       <c r="A219" s="14" t="n"/>
@@ -7991,6 +8660,9 @@
         <f>IF(A219="","",IF(COUNTIF($A$2:$A$501,A219)&gt;1,"Duplicate lot ID",IF(OR(B219="",H219="",I219="",J219=""),"Complete required fields",IF(L219&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q219" s="14" t="n"/>
+      <c r="R219" s="14" t="n"/>
+      <c r="S219" s="14" t="n"/>
     </row>
     <row r="220" ht="23" customHeight="1">
       <c r="A220" s="9" t="n"/>
@@ -8024,6 +8696,9 @@
         <f>IF(A220="","",IF(COUNTIF($A$2:$A$501,A220)&gt;1,"Duplicate lot ID",IF(OR(B220="",H220="",I220="",J220=""),"Complete required fields",IF(L220&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q220" s="9" t="n"/>
+      <c r="R220" s="9" t="n"/>
+      <c r="S220" s="9" t="n"/>
     </row>
     <row r="221" ht="23" customHeight="1">
       <c r="A221" s="14" t="n"/>
@@ -8057,6 +8732,9 @@
         <f>IF(A221="","",IF(COUNTIF($A$2:$A$501,A221)&gt;1,"Duplicate lot ID",IF(OR(B221="",H221="",I221="",J221=""),"Complete required fields",IF(L221&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q221" s="14" t="n"/>
+      <c r="R221" s="14" t="n"/>
+      <c r="S221" s="14" t="n"/>
     </row>
     <row r="222" ht="23" customHeight="1">
       <c r="A222" s="9" t="n"/>
@@ -8090,6 +8768,9 @@
         <f>IF(A222="","",IF(COUNTIF($A$2:$A$501,A222)&gt;1,"Duplicate lot ID",IF(OR(B222="",H222="",I222="",J222=""),"Complete required fields",IF(L222&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q222" s="9" t="n"/>
+      <c r="R222" s="9" t="n"/>
+      <c r="S222" s="9" t="n"/>
     </row>
     <row r="223" ht="23" customHeight="1">
       <c r="A223" s="14" t="n"/>
@@ -8123,6 +8804,9 @@
         <f>IF(A223="","",IF(COUNTIF($A$2:$A$501,A223)&gt;1,"Duplicate lot ID",IF(OR(B223="",H223="",I223="",J223=""),"Complete required fields",IF(L223&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q223" s="14" t="n"/>
+      <c r="R223" s="14" t="n"/>
+      <c r="S223" s="14" t="n"/>
     </row>
     <row r="224" ht="23" customHeight="1">
       <c r="A224" s="9" t="n"/>
@@ -8156,6 +8840,9 @@
         <f>IF(A224="","",IF(COUNTIF($A$2:$A$501,A224)&gt;1,"Duplicate lot ID",IF(OR(B224="",H224="",I224="",J224=""),"Complete required fields",IF(L224&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q224" s="9" t="n"/>
+      <c r="R224" s="9" t="n"/>
+      <c r="S224" s="9" t="n"/>
     </row>
     <row r="225" ht="23" customHeight="1">
       <c r="A225" s="14" t="n"/>
@@ -8189,6 +8876,9 @@
         <f>IF(A225="","",IF(COUNTIF($A$2:$A$501,A225)&gt;1,"Duplicate lot ID",IF(OR(B225="",H225="",I225="",J225=""),"Complete required fields",IF(L225&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q225" s="14" t="n"/>
+      <c r="R225" s="14" t="n"/>
+      <c r="S225" s="14" t="n"/>
     </row>
     <row r="226" ht="23" customHeight="1">
       <c r="A226" s="9" t="n"/>
@@ -8222,6 +8912,9 @@
         <f>IF(A226="","",IF(COUNTIF($A$2:$A$501,A226)&gt;1,"Duplicate lot ID",IF(OR(B226="",H226="",I226="",J226=""),"Complete required fields",IF(L226&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q226" s="9" t="n"/>
+      <c r="R226" s="9" t="n"/>
+      <c r="S226" s="9" t="n"/>
     </row>
     <row r="227" ht="23" customHeight="1">
       <c r="A227" s="14" t="n"/>
@@ -8255,6 +8948,9 @@
         <f>IF(A227="","",IF(COUNTIF($A$2:$A$501,A227)&gt;1,"Duplicate lot ID",IF(OR(B227="",H227="",I227="",J227=""),"Complete required fields",IF(L227&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q227" s="14" t="n"/>
+      <c r="R227" s="14" t="n"/>
+      <c r="S227" s="14" t="n"/>
     </row>
     <row r="228" ht="23" customHeight="1">
       <c r="A228" s="9" t="n"/>
@@ -8288,6 +8984,9 @@
         <f>IF(A228="","",IF(COUNTIF($A$2:$A$501,A228)&gt;1,"Duplicate lot ID",IF(OR(B228="",H228="",I228="",J228=""),"Complete required fields",IF(L228&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q228" s="9" t="n"/>
+      <c r="R228" s="9" t="n"/>
+      <c r="S228" s="9" t="n"/>
     </row>
     <row r="229" ht="23" customHeight="1">
       <c r="A229" s="14" t="n"/>
@@ -8321,6 +9020,9 @@
         <f>IF(A229="","",IF(COUNTIF($A$2:$A$501,A229)&gt;1,"Duplicate lot ID",IF(OR(B229="",H229="",I229="",J229=""),"Complete required fields",IF(L229&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q229" s="14" t="n"/>
+      <c r="R229" s="14" t="n"/>
+      <c r="S229" s="14" t="n"/>
     </row>
     <row r="230" ht="23" customHeight="1">
       <c r="A230" s="9" t="n"/>
@@ -8354,6 +9056,9 @@
         <f>IF(A230="","",IF(COUNTIF($A$2:$A$501,A230)&gt;1,"Duplicate lot ID",IF(OR(B230="",H230="",I230="",J230=""),"Complete required fields",IF(L230&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q230" s="9" t="n"/>
+      <c r="R230" s="9" t="n"/>
+      <c r="S230" s="9" t="n"/>
     </row>
     <row r="231" ht="23" customHeight="1">
       <c r="A231" s="14" t="n"/>
@@ -8387,6 +9092,9 @@
         <f>IF(A231="","",IF(COUNTIF($A$2:$A$501,A231)&gt;1,"Duplicate lot ID",IF(OR(B231="",H231="",I231="",J231=""),"Complete required fields",IF(L231&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q231" s="14" t="n"/>
+      <c r="R231" s="14" t="n"/>
+      <c r="S231" s="14" t="n"/>
     </row>
     <row r="232" ht="23" customHeight="1">
       <c r="A232" s="9" t="n"/>
@@ -8420,6 +9128,9 @@
         <f>IF(A232="","",IF(COUNTIF($A$2:$A$501,A232)&gt;1,"Duplicate lot ID",IF(OR(B232="",H232="",I232="",J232=""),"Complete required fields",IF(L232&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q232" s="9" t="n"/>
+      <c r="R232" s="9" t="n"/>
+      <c r="S232" s="9" t="n"/>
     </row>
     <row r="233" ht="23" customHeight="1">
       <c r="A233" s="14" t="n"/>
@@ -8453,6 +9164,9 @@
         <f>IF(A233="","",IF(COUNTIF($A$2:$A$501,A233)&gt;1,"Duplicate lot ID",IF(OR(B233="",H233="",I233="",J233=""),"Complete required fields",IF(L233&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q233" s="14" t="n"/>
+      <c r="R233" s="14" t="n"/>
+      <c r="S233" s="14" t="n"/>
     </row>
     <row r="234" ht="23" customHeight="1">
       <c r="A234" s="9" t="n"/>
@@ -8486,6 +9200,9 @@
         <f>IF(A234="","",IF(COUNTIF($A$2:$A$501,A234)&gt;1,"Duplicate lot ID",IF(OR(B234="",H234="",I234="",J234=""),"Complete required fields",IF(L234&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q234" s="9" t="n"/>
+      <c r="R234" s="9" t="n"/>
+      <c r="S234" s="9" t="n"/>
     </row>
     <row r="235" ht="23" customHeight="1">
       <c r="A235" s="14" t="n"/>
@@ -8519,6 +9236,9 @@
         <f>IF(A235="","",IF(COUNTIF($A$2:$A$501,A235)&gt;1,"Duplicate lot ID",IF(OR(B235="",H235="",I235="",J235=""),"Complete required fields",IF(L235&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q235" s="14" t="n"/>
+      <c r="R235" s="14" t="n"/>
+      <c r="S235" s="14" t="n"/>
     </row>
     <row r="236" ht="23" customHeight="1">
       <c r="A236" s="9" t="n"/>
@@ -8552,6 +9272,9 @@
         <f>IF(A236="","",IF(COUNTIF($A$2:$A$501,A236)&gt;1,"Duplicate lot ID",IF(OR(B236="",H236="",I236="",J236=""),"Complete required fields",IF(L236&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q236" s="9" t="n"/>
+      <c r="R236" s="9" t="n"/>
+      <c r="S236" s="9" t="n"/>
     </row>
     <row r="237" ht="23" customHeight="1">
       <c r="A237" s="14" t="n"/>
@@ -8585,6 +9308,9 @@
         <f>IF(A237="","",IF(COUNTIF($A$2:$A$501,A237)&gt;1,"Duplicate lot ID",IF(OR(B237="",H237="",I237="",J237=""),"Complete required fields",IF(L237&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q237" s="14" t="n"/>
+      <c r="R237" s="14" t="n"/>
+      <c r="S237" s="14" t="n"/>
     </row>
     <row r="238" ht="23" customHeight="1">
       <c r="A238" s="9" t="n"/>
@@ -8618,6 +9344,9 @@
         <f>IF(A238="","",IF(COUNTIF($A$2:$A$501,A238)&gt;1,"Duplicate lot ID",IF(OR(B238="",H238="",I238="",J238=""),"Complete required fields",IF(L238&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q238" s="9" t="n"/>
+      <c r="R238" s="9" t="n"/>
+      <c r="S238" s="9" t="n"/>
     </row>
     <row r="239" ht="23" customHeight="1">
       <c r="A239" s="14" t="n"/>
@@ -8651,6 +9380,9 @@
         <f>IF(A239="","",IF(COUNTIF($A$2:$A$501,A239)&gt;1,"Duplicate lot ID",IF(OR(B239="",H239="",I239="",J239=""),"Complete required fields",IF(L239&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q239" s="14" t="n"/>
+      <c r="R239" s="14" t="n"/>
+      <c r="S239" s="14" t="n"/>
     </row>
     <row r="240" ht="23" customHeight="1">
       <c r="A240" s="9" t="n"/>
@@ -8684,6 +9416,9 @@
         <f>IF(A240="","",IF(COUNTIF($A$2:$A$501,A240)&gt;1,"Duplicate lot ID",IF(OR(B240="",H240="",I240="",J240=""),"Complete required fields",IF(L240&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q240" s="9" t="n"/>
+      <c r="R240" s="9" t="n"/>
+      <c r="S240" s="9" t="n"/>
     </row>
     <row r="241" ht="23" customHeight="1">
       <c r="A241" s="14" t="n"/>
@@ -8717,6 +9452,9 @@
         <f>IF(A241="","",IF(COUNTIF($A$2:$A$501,A241)&gt;1,"Duplicate lot ID",IF(OR(B241="",H241="",I241="",J241=""),"Complete required fields",IF(L241&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q241" s="14" t="n"/>
+      <c r="R241" s="14" t="n"/>
+      <c r="S241" s="14" t="n"/>
     </row>
     <row r="242" ht="23" customHeight="1">
       <c r="A242" s="9" t="n"/>
@@ -8750,6 +9488,9 @@
         <f>IF(A242="","",IF(COUNTIF($A$2:$A$501,A242)&gt;1,"Duplicate lot ID",IF(OR(B242="",H242="",I242="",J242=""),"Complete required fields",IF(L242&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q242" s="9" t="n"/>
+      <c r="R242" s="9" t="n"/>
+      <c r="S242" s="9" t="n"/>
     </row>
     <row r="243" ht="23" customHeight="1">
       <c r="A243" s="14" t="n"/>
@@ -8783,6 +9524,9 @@
         <f>IF(A243="","",IF(COUNTIF($A$2:$A$501,A243)&gt;1,"Duplicate lot ID",IF(OR(B243="",H243="",I243="",J243=""),"Complete required fields",IF(L243&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q243" s="14" t="n"/>
+      <c r="R243" s="14" t="n"/>
+      <c r="S243" s="14" t="n"/>
     </row>
     <row r="244" ht="23" customHeight="1">
       <c r="A244" s="9" t="n"/>
@@ -8816,6 +9560,9 @@
         <f>IF(A244="","",IF(COUNTIF($A$2:$A$501,A244)&gt;1,"Duplicate lot ID",IF(OR(B244="",H244="",I244="",J244=""),"Complete required fields",IF(L244&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q244" s="9" t="n"/>
+      <c r="R244" s="9" t="n"/>
+      <c r="S244" s="9" t="n"/>
     </row>
     <row r="245" ht="23" customHeight="1">
       <c r="A245" s="14" t="n"/>
@@ -8849,6 +9596,9 @@
         <f>IF(A245="","",IF(COUNTIF($A$2:$A$501,A245)&gt;1,"Duplicate lot ID",IF(OR(B245="",H245="",I245="",J245=""),"Complete required fields",IF(L245&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q245" s="14" t="n"/>
+      <c r="R245" s="14" t="n"/>
+      <c r="S245" s="14" t="n"/>
     </row>
     <row r="246" ht="23" customHeight="1">
       <c r="A246" s="9" t="n"/>
@@ -8882,6 +9632,9 @@
         <f>IF(A246="","",IF(COUNTIF($A$2:$A$501,A246)&gt;1,"Duplicate lot ID",IF(OR(B246="",H246="",I246="",J246=""),"Complete required fields",IF(L246&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q246" s="9" t="n"/>
+      <c r="R246" s="9" t="n"/>
+      <c r="S246" s="9" t="n"/>
     </row>
     <row r="247" ht="23" customHeight="1">
       <c r="A247" s="14" t="n"/>
@@ -8915,6 +9668,9 @@
         <f>IF(A247="","",IF(COUNTIF($A$2:$A$501,A247)&gt;1,"Duplicate lot ID",IF(OR(B247="",H247="",I247="",J247=""),"Complete required fields",IF(L247&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q247" s="14" t="n"/>
+      <c r="R247" s="14" t="n"/>
+      <c r="S247" s="14" t="n"/>
     </row>
     <row r="248" ht="23" customHeight="1">
       <c r="A248" s="9" t="n"/>
@@ -8948,6 +9704,9 @@
         <f>IF(A248="","",IF(COUNTIF($A$2:$A$501,A248)&gt;1,"Duplicate lot ID",IF(OR(B248="",H248="",I248="",J248=""),"Complete required fields",IF(L248&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q248" s="9" t="n"/>
+      <c r="R248" s="9" t="n"/>
+      <c r="S248" s="9" t="n"/>
     </row>
     <row r="249" ht="23" customHeight="1">
       <c r="A249" s="14" t="n"/>
@@ -8981,6 +9740,9 @@
         <f>IF(A249="","",IF(COUNTIF($A$2:$A$501,A249)&gt;1,"Duplicate lot ID",IF(OR(B249="",H249="",I249="",J249=""),"Complete required fields",IF(L249&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q249" s="14" t="n"/>
+      <c r="R249" s="14" t="n"/>
+      <c r="S249" s="14" t="n"/>
     </row>
     <row r="250" ht="23" customHeight="1">
       <c r="A250" s="9" t="n"/>
@@ -9014,6 +9776,9 @@
         <f>IF(A250="","",IF(COUNTIF($A$2:$A$501,A250)&gt;1,"Duplicate lot ID",IF(OR(B250="",H250="",I250="",J250=""),"Complete required fields",IF(L250&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q250" s="9" t="n"/>
+      <c r="R250" s="9" t="n"/>
+      <c r="S250" s="9" t="n"/>
     </row>
     <row r="251" ht="23" customHeight="1">
       <c r="A251" s="14" t="n"/>
@@ -9047,6 +9812,9 @@
         <f>IF(A251="","",IF(COUNTIF($A$2:$A$501,A251)&gt;1,"Duplicate lot ID",IF(OR(B251="",H251="",I251="",J251=""),"Complete required fields",IF(L251&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q251" s="14" t="n"/>
+      <c r="R251" s="14" t="n"/>
+      <c r="S251" s="14" t="n"/>
     </row>
     <row r="252" ht="23" customHeight="1">
       <c r="A252" s="9" t="n"/>
@@ -9080,6 +9848,9 @@
         <f>IF(A252="","",IF(COUNTIF($A$2:$A$501,A252)&gt;1,"Duplicate lot ID",IF(OR(B252="",H252="",I252="",J252=""),"Complete required fields",IF(L252&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q252" s="9" t="n"/>
+      <c r="R252" s="9" t="n"/>
+      <c r="S252" s="9" t="n"/>
     </row>
     <row r="253" ht="23" customHeight="1">
       <c r="A253" s="14" t="n"/>
@@ -9113,6 +9884,9 @@
         <f>IF(A253="","",IF(COUNTIF($A$2:$A$501,A253)&gt;1,"Duplicate lot ID",IF(OR(B253="",H253="",I253="",J253=""),"Complete required fields",IF(L253&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q253" s="14" t="n"/>
+      <c r="R253" s="14" t="n"/>
+      <c r="S253" s="14" t="n"/>
     </row>
     <row r="254" ht="23" customHeight="1">
       <c r="A254" s="9" t="n"/>
@@ -9146,6 +9920,9 @@
         <f>IF(A254="","",IF(COUNTIF($A$2:$A$501,A254)&gt;1,"Duplicate lot ID",IF(OR(B254="",H254="",I254="",J254=""),"Complete required fields",IF(L254&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q254" s="9" t="n"/>
+      <c r="R254" s="9" t="n"/>
+      <c r="S254" s="9" t="n"/>
     </row>
     <row r="255" ht="23" customHeight="1">
       <c r="A255" s="14" t="n"/>
@@ -9179,6 +9956,9 @@
         <f>IF(A255="","",IF(COUNTIF($A$2:$A$501,A255)&gt;1,"Duplicate lot ID",IF(OR(B255="",H255="",I255="",J255=""),"Complete required fields",IF(L255&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q255" s="14" t="n"/>
+      <c r="R255" s="14" t="n"/>
+      <c r="S255" s="14" t="n"/>
     </row>
     <row r="256" ht="23" customHeight="1">
       <c r="A256" s="9" t="n"/>
@@ -9212,6 +9992,9 @@
         <f>IF(A256="","",IF(COUNTIF($A$2:$A$501,A256)&gt;1,"Duplicate lot ID",IF(OR(B256="",H256="",I256="",J256=""),"Complete required fields",IF(L256&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q256" s="9" t="n"/>
+      <c r="R256" s="9" t="n"/>
+      <c r="S256" s="9" t="n"/>
     </row>
     <row r="257" ht="23" customHeight="1">
       <c r="A257" s="14" t="n"/>
@@ -9245,6 +10028,9 @@
         <f>IF(A257="","",IF(COUNTIF($A$2:$A$501,A257)&gt;1,"Duplicate lot ID",IF(OR(B257="",H257="",I257="",J257=""),"Complete required fields",IF(L257&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q257" s="14" t="n"/>
+      <c r="R257" s="14" t="n"/>
+      <c r="S257" s="14" t="n"/>
     </row>
     <row r="258" ht="23" customHeight="1">
       <c r="A258" s="9" t="n"/>
@@ -9278,6 +10064,9 @@
         <f>IF(A258="","",IF(COUNTIF($A$2:$A$501,A258)&gt;1,"Duplicate lot ID",IF(OR(B258="",H258="",I258="",J258=""),"Complete required fields",IF(L258&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q258" s="9" t="n"/>
+      <c r="R258" s="9" t="n"/>
+      <c r="S258" s="9" t="n"/>
     </row>
     <row r="259" ht="23" customHeight="1">
       <c r="A259" s="14" t="n"/>
@@ -9311,6 +10100,9 @@
         <f>IF(A259="","",IF(COUNTIF($A$2:$A$501,A259)&gt;1,"Duplicate lot ID",IF(OR(B259="",H259="",I259="",J259=""),"Complete required fields",IF(L259&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q259" s="14" t="n"/>
+      <c r="R259" s="14" t="n"/>
+      <c r="S259" s="14" t="n"/>
     </row>
     <row r="260" ht="23" customHeight="1">
       <c r="A260" s="9" t="n"/>
@@ -9344,6 +10136,9 @@
         <f>IF(A260="","",IF(COUNTIF($A$2:$A$501,A260)&gt;1,"Duplicate lot ID",IF(OR(B260="",H260="",I260="",J260=""),"Complete required fields",IF(L260&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q260" s="9" t="n"/>
+      <c r="R260" s="9" t="n"/>
+      <c r="S260" s="9" t="n"/>
     </row>
     <row r="261" ht="23" customHeight="1">
       <c r="A261" s="14" t="n"/>
@@ -9377,6 +10172,9 @@
         <f>IF(A261="","",IF(COUNTIF($A$2:$A$501,A261)&gt;1,"Duplicate lot ID",IF(OR(B261="",H261="",I261="",J261=""),"Complete required fields",IF(L261&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q261" s="14" t="n"/>
+      <c r="R261" s="14" t="n"/>
+      <c r="S261" s="14" t="n"/>
     </row>
     <row r="262" ht="23" customHeight="1">
       <c r="A262" s="9" t="n"/>
@@ -9410,6 +10208,9 @@
         <f>IF(A262="","",IF(COUNTIF($A$2:$A$501,A262)&gt;1,"Duplicate lot ID",IF(OR(B262="",H262="",I262="",J262=""),"Complete required fields",IF(L262&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q262" s="9" t="n"/>
+      <c r="R262" s="9" t="n"/>
+      <c r="S262" s="9" t="n"/>
     </row>
     <row r="263" ht="23" customHeight="1">
       <c r="A263" s="14" t="n"/>
@@ -9443,6 +10244,9 @@
         <f>IF(A263="","",IF(COUNTIF($A$2:$A$501,A263)&gt;1,"Duplicate lot ID",IF(OR(B263="",H263="",I263="",J263=""),"Complete required fields",IF(L263&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q263" s="14" t="n"/>
+      <c r="R263" s="14" t="n"/>
+      <c r="S263" s="14" t="n"/>
     </row>
     <row r="264" ht="23" customHeight="1">
       <c r="A264" s="9" t="n"/>
@@ -9476,6 +10280,9 @@
         <f>IF(A264="","",IF(COUNTIF($A$2:$A$501,A264)&gt;1,"Duplicate lot ID",IF(OR(B264="",H264="",I264="",J264=""),"Complete required fields",IF(L264&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q264" s="9" t="n"/>
+      <c r="R264" s="9" t="n"/>
+      <c r="S264" s="9" t="n"/>
     </row>
     <row r="265" ht="23" customHeight="1">
       <c r="A265" s="14" t="n"/>
@@ -9509,6 +10316,9 @@
         <f>IF(A265="","",IF(COUNTIF($A$2:$A$501,A265)&gt;1,"Duplicate lot ID",IF(OR(B265="",H265="",I265="",J265=""),"Complete required fields",IF(L265&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q265" s="14" t="n"/>
+      <c r="R265" s="14" t="n"/>
+      <c r="S265" s="14" t="n"/>
     </row>
     <row r="266" ht="23" customHeight="1">
       <c r="A266" s="9" t="n"/>
@@ -9542,6 +10352,9 @@
         <f>IF(A266="","",IF(COUNTIF($A$2:$A$501,A266)&gt;1,"Duplicate lot ID",IF(OR(B266="",H266="",I266="",J266=""),"Complete required fields",IF(L266&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q266" s="9" t="n"/>
+      <c r="R266" s="9" t="n"/>
+      <c r="S266" s="9" t="n"/>
     </row>
     <row r="267" ht="23" customHeight="1">
       <c r="A267" s="14" t="n"/>
@@ -9575,6 +10388,9 @@
         <f>IF(A267="","",IF(COUNTIF($A$2:$A$501,A267)&gt;1,"Duplicate lot ID",IF(OR(B267="",H267="",I267="",J267=""),"Complete required fields",IF(L267&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q267" s="14" t="n"/>
+      <c r="R267" s="14" t="n"/>
+      <c r="S267" s="14" t="n"/>
     </row>
     <row r="268" ht="23" customHeight="1">
       <c r="A268" s="9" t="n"/>
@@ -9608,6 +10424,9 @@
         <f>IF(A268="","",IF(COUNTIF($A$2:$A$501,A268)&gt;1,"Duplicate lot ID",IF(OR(B268="",H268="",I268="",J268=""),"Complete required fields",IF(L268&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q268" s="9" t="n"/>
+      <c r="R268" s="9" t="n"/>
+      <c r="S268" s="9" t="n"/>
     </row>
     <row r="269" ht="23" customHeight="1">
       <c r="A269" s="14" t="n"/>
@@ -9641,6 +10460,9 @@
         <f>IF(A269="","",IF(COUNTIF($A$2:$A$501,A269)&gt;1,"Duplicate lot ID",IF(OR(B269="",H269="",I269="",J269=""),"Complete required fields",IF(L269&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q269" s="14" t="n"/>
+      <c r="R269" s="14" t="n"/>
+      <c r="S269" s="14" t="n"/>
     </row>
     <row r="270" ht="23" customHeight="1">
       <c r="A270" s="9" t="n"/>
@@ -9674,6 +10496,9 @@
         <f>IF(A270="","",IF(COUNTIF($A$2:$A$501,A270)&gt;1,"Duplicate lot ID",IF(OR(B270="",H270="",I270="",J270=""),"Complete required fields",IF(L270&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q270" s="9" t="n"/>
+      <c r="R270" s="9" t="n"/>
+      <c r="S270" s="9" t="n"/>
     </row>
     <row r="271" ht="23" customHeight="1">
       <c r="A271" s="14" t="n"/>
@@ -9707,6 +10532,9 @@
         <f>IF(A271="","",IF(COUNTIF($A$2:$A$501,A271)&gt;1,"Duplicate lot ID",IF(OR(B271="",H271="",I271="",J271=""),"Complete required fields",IF(L271&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q271" s="14" t="n"/>
+      <c r="R271" s="14" t="n"/>
+      <c r="S271" s="14" t="n"/>
     </row>
     <row r="272" ht="23" customHeight="1">
       <c r="A272" s="9" t="n"/>
@@ -9740,6 +10568,9 @@
         <f>IF(A272="","",IF(COUNTIF($A$2:$A$501,A272)&gt;1,"Duplicate lot ID",IF(OR(B272="",H272="",I272="",J272=""),"Complete required fields",IF(L272&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q272" s="9" t="n"/>
+      <c r="R272" s="9" t="n"/>
+      <c r="S272" s="9" t="n"/>
     </row>
     <row r="273" ht="23" customHeight="1">
       <c r="A273" s="14" t="n"/>
@@ -9773,6 +10604,9 @@
         <f>IF(A273="","",IF(COUNTIF($A$2:$A$501,A273)&gt;1,"Duplicate lot ID",IF(OR(B273="",H273="",I273="",J273=""),"Complete required fields",IF(L273&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q273" s="14" t="n"/>
+      <c r="R273" s="14" t="n"/>
+      <c r="S273" s="14" t="n"/>
     </row>
     <row r="274" ht="23" customHeight="1">
       <c r="A274" s="9" t="n"/>
@@ -9806,6 +10640,9 @@
         <f>IF(A274="","",IF(COUNTIF($A$2:$A$501,A274)&gt;1,"Duplicate lot ID",IF(OR(B274="",H274="",I274="",J274=""),"Complete required fields",IF(L274&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q274" s="9" t="n"/>
+      <c r="R274" s="9" t="n"/>
+      <c r="S274" s="9" t="n"/>
     </row>
     <row r="275" ht="23" customHeight="1">
       <c r="A275" s="14" t="n"/>
@@ -9839,6 +10676,9 @@
         <f>IF(A275="","",IF(COUNTIF($A$2:$A$501,A275)&gt;1,"Duplicate lot ID",IF(OR(B275="",H275="",I275="",J275=""),"Complete required fields",IF(L275&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q275" s="14" t="n"/>
+      <c r="R275" s="14" t="n"/>
+      <c r="S275" s="14" t="n"/>
     </row>
     <row r="276" ht="23" customHeight="1">
       <c r="A276" s="9" t="n"/>
@@ -9872,6 +10712,9 @@
         <f>IF(A276="","",IF(COUNTIF($A$2:$A$501,A276)&gt;1,"Duplicate lot ID",IF(OR(B276="",H276="",I276="",J276=""),"Complete required fields",IF(L276&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q276" s="9" t="n"/>
+      <c r="R276" s="9" t="n"/>
+      <c r="S276" s="9" t="n"/>
     </row>
     <row r="277" ht="23" customHeight="1">
       <c r="A277" s="14" t="n"/>
@@ -9905,6 +10748,9 @@
         <f>IF(A277="","",IF(COUNTIF($A$2:$A$501,A277)&gt;1,"Duplicate lot ID",IF(OR(B277="",H277="",I277="",J277=""),"Complete required fields",IF(L277&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q277" s="14" t="n"/>
+      <c r="R277" s="14" t="n"/>
+      <c r="S277" s="14" t="n"/>
     </row>
     <row r="278" ht="23" customHeight="1">
       <c r="A278" s="9" t="n"/>
@@ -9938,6 +10784,9 @@
         <f>IF(A278="","",IF(COUNTIF($A$2:$A$501,A278)&gt;1,"Duplicate lot ID",IF(OR(B278="",H278="",I278="",J278=""),"Complete required fields",IF(L278&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q278" s="9" t="n"/>
+      <c r="R278" s="9" t="n"/>
+      <c r="S278" s="9" t="n"/>
     </row>
     <row r="279" ht="23" customHeight="1">
       <c r="A279" s="14" t="n"/>
@@ -9971,6 +10820,9 @@
         <f>IF(A279="","",IF(COUNTIF($A$2:$A$501,A279)&gt;1,"Duplicate lot ID",IF(OR(B279="",H279="",I279="",J279=""),"Complete required fields",IF(L279&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q279" s="14" t="n"/>
+      <c r="R279" s="14" t="n"/>
+      <c r="S279" s="14" t="n"/>
     </row>
     <row r="280" ht="23" customHeight="1">
       <c r="A280" s="9" t="n"/>
@@ -10004,6 +10856,9 @@
         <f>IF(A280="","",IF(COUNTIF($A$2:$A$501,A280)&gt;1,"Duplicate lot ID",IF(OR(B280="",H280="",I280="",J280=""),"Complete required fields",IF(L280&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q280" s="9" t="n"/>
+      <c r="R280" s="9" t="n"/>
+      <c r="S280" s="9" t="n"/>
     </row>
     <row r="281" ht="23" customHeight="1">
       <c r="A281" s="14" t="n"/>
@@ -10037,6 +10892,9 @@
         <f>IF(A281="","",IF(COUNTIF($A$2:$A$501,A281)&gt;1,"Duplicate lot ID",IF(OR(B281="",H281="",I281="",J281=""),"Complete required fields",IF(L281&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q281" s="14" t="n"/>
+      <c r="R281" s="14" t="n"/>
+      <c r="S281" s="14" t="n"/>
     </row>
     <row r="282" ht="23" customHeight="1">
       <c r="A282" s="9" t="n"/>
@@ -10070,6 +10928,9 @@
         <f>IF(A282="","",IF(COUNTIF($A$2:$A$501,A282)&gt;1,"Duplicate lot ID",IF(OR(B282="",H282="",I282="",J282=""),"Complete required fields",IF(L282&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q282" s="9" t="n"/>
+      <c r="R282" s="9" t="n"/>
+      <c r="S282" s="9" t="n"/>
     </row>
     <row r="283" ht="23" customHeight="1">
       <c r="A283" s="14" t="n"/>
@@ -10103,6 +10964,9 @@
         <f>IF(A283="","",IF(COUNTIF($A$2:$A$501,A283)&gt;1,"Duplicate lot ID",IF(OR(B283="",H283="",I283="",J283=""),"Complete required fields",IF(L283&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q283" s="14" t="n"/>
+      <c r="R283" s="14" t="n"/>
+      <c r="S283" s="14" t="n"/>
     </row>
     <row r="284" ht="23" customHeight="1">
       <c r="A284" s="9" t="n"/>
@@ -10136,6 +11000,9 @@
         <f>IF(A284="","",IF(COUNTIF($A$2:$A$501,A284)&gt;1,"Duplicate lot ID",IF(OR(B284="",H284="",I284="",J284=""),"Complete required fields",IF(L284&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q284" s="9" t="n"/>
+      <c r="R284" s="9" t="n"/>
+      <c r="S284" s="9" t="n"/>
     </row>
     <row r="285" ht="23" customHeight="1">
       <c r="A285" s="14" t="n"/>
@@ -10169,6 +11036,9 @@
         <f>IF(A285="","",IF(COUNTIF($A$2:$A$501,A285)&gt;1,"Duplicate lot ID",IF(OR(B285="",H285="",I285="",J285=""),"Complete required fields",IF(L285&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q285" s="14" t="n"/>
+      <c r="R285" s="14" t="n"/>
+      <c r="S285" s="14" t="n"/>
     </row>
     <row r="286" ht="23" customHeight="1">
       <c r="A286" s="9" t="n"/>
@@ -10202,6 +11072,9 @@
         <f>IF(A286="","",IF(COUNTIF($A$2:$A$501,A286)&gt;1,"Duplicate lot ID",IF(OR(B286="",H286="",I286="",J286=""),"Complete required fields",IF(L286&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q286" s="9" t="n"/>
+      <c r="R286" s="9" t="n"/>
+      <c r="S286" s="9" t="n"/>
     </row>
     <row r="287" ht="23" customHeight="1">
       <c r="A287" s="14" t="n"/>
@@ -10235,6 +11108,9 @@
         <f>IF(A287="","",IF(COUNTIF($A$2:$A$501,A287)&gt;1,"Duplicate lot ID",IF(OR(B287="",H287="",I287="",J287=""),"Complete required fields",IF(L287&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q287" s="14" t="n"/>
+      <c r="R287" s="14" t="n"/>
+      <c r="S287" s="14" t="n"/>
     </row>
     <row r="288" ht="23" customHeight="1">
       <c r="A288" s="9" t="n"/>
@@ -10268,6 +11144,9 @@
         <f>IF(A288="","",IF(COUNTIF($A$2:$A$501,A288)&gt;1,"Duplicate lot ID",IF(OR(B288="",H288="",I288="",J288=""),"Complete required fields",IF(L288&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q288" s="9" t="n"/>
+      <c r="R288" s="9" t="n"/>
+      <c r="S288" s="9" t="n"/>
     </row>
     <row r="289" ht="23" customHeight="1">
       <c r="A289" s="14" t="n"/>
@@ -10301,6 +11180,9 @@
         <f>IF(A289="","",IF(COUNTIF($A$2:$A$501,A289)&gt;1,"Duplicate lot ID",IF(OR(B289="",H289="",I289="",J289=""),"Complete required fields",IF(L289&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q289" s="14" t="n"/>
+      <c r="R289" s="14" t="n"/>
+      <c r="S289" s="14" t="n"/>
     </row>
     <row r="290" ht="23" customHeight="1">
       <c r="A290" s="9" t="n"/>
@@ -10334,6 +11216,9 @@
         <f>IF(A290="","",IF(COUNTIF($A$2:$A$501,A290)&gt;1,"Duplicate lot ID",IF(OR(B290="",H290="",I290="",J290=""),"Complete required fields",IF(L290&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q290" s="9" t="n"/>
+      <c r="R290" s="9" t="n"/>
+      <c r="S290" s="9" t="n"/>
     </row>
     <row r="291" ht="23" customHeight="1">
       <c r="A291" s="14" t="n"/>
@@ -10367,6 +11252,9 @@
         <f>IF(A291="","",IF(COUNTIF($A$2:$A$501,A291)&gt;1,"Duplicate lot ID",IF(OR(B291="",H291="",I291="",J291=""),"Complete required fields",IF(L291&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q291" s="14" t="n"/>
+      <c r="R291" s="14" t="n"/>
+      <c r="S291" s="14" t="n"/>
     </row>
     <row r="292" ht="23" customHeight="1">
       <c r="A292" s="9" t="n"/>
@@ -10400,6 +11288,9 @@
         <f>IF(A292="","",IF(COUNTIF($A$2:$A$501,A292)&gt;1,"Duplicate lot ID",IF(OR(B292="",H292="",I292="",J292=""),"Complete required fields",IF(L292&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q292" s="9" t="n"/>
+      <c r="R292" s="9" t="n"/>
+      <c r="S292" s="9" t="n"/>
     </row>
     <row r="293" ht="23" customHeight="1">
       <c r="A293" s="14" t="n"/>
@@ -10433,6 +11324,9 @@
         <f>IF(A293="","",IF(COUNTIF($A$2:$A$501,A293)&gt;1,"Duplicate lot ID",IF(OR(B293="",H293="",I293="",J293=""),"Complete required fields",IF(L293&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q293" s="14" t="n"/>
+      <c r="R293" s="14" t="n"/>
+      <c r="S293" s="14" t="n"/>
     </row>
     <row r="294" ht="23" customHeight="1">
       <c r="A294" s="9" t="n"/>
@@ -10466,6 +11360,9 @@
         <f>IF(A294="","",IF(COUNTIF($A$2:$A$501,A294)&gt;1,"Duplicate lot ID",IF(OR(B294="",H294="",I294="",J294=""),"Complete required fields",IF(L294&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q294" s="9" t="n"/>
+      <c r="R294" s="9" t="n"/>
+      <c r="S294" s="9" t="n"/>
     </row>
     <row r="295" ht="23" customHeight="1">
       <c r="A295" s="14" t="n"/>
@@ -10499,6 +11396,9 @@
         <f>IF(A295="","",IF(COUNTIF($A$2:$A$501,A295)&gt;1,"Duplicate lot ID",IF(OR(B295="",H295="",I295="",J295=""),"Complete required fields",IF(L295&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q295" s="14" t="n"/>
+      <c r="R295" s="14" t="n"/>
+      <c r="S295" s="14" t="n"/>
     </row>
     <row r="296" ht="23" customHeight="1">
       <c r="A296" s="9" t="n"/>
@@ -10532,6 +11432,9 @@
         <f>IF(A296="","",IF(COUNTIF($A$2:$A$501,A296)&gt;1,"Duplicate lot ID",IF(OR(B296="",H296="",I296="",J296=""),"Complete required fields",IF(L296&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q296" s="9" t="n"/>
+      <c r="R296" s="9" t="n"/>
+      <c r="S296" s="9" t="n"/>
     </row>
     <row r="297" ht="23" customHeight="1">
       <c r="A297" s="14" t="n"/>
@@ -10565,6 +11468,9 @@
         <f>IF(A297="","",IF(COUNTIF($A$2:$A$501,A297)&gt;1,"Duplicate lot ID",IF(OR(B297="",H297="",I297="",J297=""),"Complete required fields",IF(L297&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q297" s="14" t="n"/>
+      <c r="R297" s="14" t="n"/>
+      <c r="S297" s="14" t="n"/>
     </row>
     <row r="298" ht="23" customHeight="1">
       <c r="A298" s="9" t="n"/>
@@ -10598,6 +11504,9 @@
         <f>IF(A298="","",IF(COUNTIF($A$2:$A$501,A298)&gt;1,"Duplicate lot ID",IF(OR(B298="",H298="",I298="",J298=""),"Complete required fields",IF(L298&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q298" s="9" t="n"/>
+      <c r="R298" s="9" t="n"/>
+      <c r="S298" s="9" t="n"/>
     </row>
     <row r="299" ht="23" customHeight="1">
       <c r="A299" s="14" t="n"/>
@@ -10631,6 +11540,9 @@
         <f>IF(A299="","",IF(COUNTIF($A$2:$A$501,A299)&gt;1,"Duplicate lot ID",IF(OR(B299="",H299="",I299="",J299=""),"Complete required fields",IF(L299&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q299" s="14" t="n"/>
+      <c r="R299" s="14" t="n"/>
+      <c r="S299" s="14" t="n"/>
     </row>
     <row r="300" ht="23" customHeight="1">
       <c r="A300" s="9" t="n"/>
@@ -10664,6 +11576,9 @@
         <f>IF(A300="","",IF(COUNTIF($A$2:$A$501,A300)&gt;1,"Duplicate lot ID",IF(OR(B300="",H300="",I300="",J300=""),"Complete required fields",IF(L300&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q300" s="9" t="n"/>
+      <c r="R300" s="9" t="n"/>
+      <c r="S300" s="9" t="n"/>
     </row>
     <row r="301" ht="23" customHeight="1">
       <c r="A301" s="14" t="n"/>
@@ -10697,6 +11612,9 @@
         <f>IF(A301="","",IF(COUNTIF($A$2:$A$501,A301)&gt;1,"Duplicate lot ID",IF(OR(B301="",H301="",I301="",J301=""),"Complete required fields",IF(L301&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q301" s="14" t="n"/>
+      <c r="R301" s="14" t="n"/>
+      <c r="S301" s="14" t="n"/>
     </row>
     <row r="302" ht="23" customHeight="1">
       <c r="A302" s="9" t="n"/>
@@ -10730,6 +11648,9 @@
         <f>IF(A302="","",IF(COUNTIF($A$2:$A$501,A302)&gt;1,"Duplicate lot ID",IF(OR(B302="",H302="",I302="",J302=""),"Complete required fields",IF(L302&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q302" s="9" t="n"/>
+      <c r="R302" s="9" t="n"/>
+      <c r="S302" s="9" t="n"/>
     </row>
     <row r="303" ht="23" customHeight="1">
       <c r="A303" s="14" t="n"/>
@@ -10763,6 +11684,9 @@
         <f>IF(A303="","",IF(COUNTIF($A$2:$A$501,A303)&gt;1,"Duplicate lot ID",IF(OR(B303="",H303="",I303="",J303=""),"Complete required fields",IF(L303&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q303" s="14" t="n"/>
+      <c r="R303" s="14" t="n"/>
+      <c r="S303" s="14" t="n"/>
     </row>
     <row r="304" ht="23" customHeight="1">
       <c r="A304" s="9" t="n"/>
@@ -10796,6 +11720,9 @@
         <f>IF(A304="","",IF(COUNTIF($A$2:$A$501,A304)&gt;1,"Duplicate lot ID",IF(OR(B304="",H304="",I304="",J304=""),"Complete required fields",IF(L304&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q304" s="9" t="n"/>
+      <c r="R304" s="9" t="n"/>
+      <c r="S304" s="9" t="n"/>
     </row>
     <row r="305" ht="23" customHeight="1">
       <c r="A305" s="14" t="n"/>
@@ -10829,6 +11756,9 @@
         <f>IF(A305="","",IF(COUNTIF($A$2:$A$501,A305)&gt;1,"Duplicate lot ID",IF(OR(B305="",H305="",I305="",J305=""),"Complete required fields",IF(L305&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q305" s="14" t="n"/>
+      <c r="R305" s="14" t="n"/>
+      <c r="S305" s="14" t="n"/>
     </row>
     <row r="306" ht="23" customHeight="1">
       <c r="A306" s="9" t="n"/>
@@ -10862,6 +11792,9 @@
         <f>IF(A306="","",IF(COUNTIF($A$2:$A$501,A306)&gt;1,"Duplicate lot ID",IF(OR(B306="",H306="",I306="",J306=""),"Complete required fields",IF(L306&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q306" s="9" t="n"/>
+      <c r="R306" s="9" t="n"/>
+      <c r="S306" s="9" t="n"/>
     </row>
     <row r="307" ht="23" customHeight="1">
       <c r="A307" s="14" t="n"/>
@@ -10895,6 +11828,9 @@
         <f>IF(A307="","",IF(COUNTIF($A$2:$A$501,A307)&gt;1,"Duplicate lot ID",IF(OR(B307="",H307="",I307="",J307=""),"Complete required fields",IF(L307&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q307" s="14" t="n"/>
+      <c r="R307" s="14" t="n"/>
+      <c r="S307" s="14" t="n"/>
     </row>
     <row r="308" ht="23" customHeight="1">
       <c r="A308" s="9" t="n"/>
@@ -10928,6 +11864,9 @@
         <f>IF(A308="","",IF(COUNTIF($A$2:$A$501,A308)&gt;1,"Duplicate lot ID",IF(OR(B308="",H308="",I308="",J308=""),"Complete required fields",IF(L308&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q308" s="9" t="n"/>
+      <c r="R308" s="9" t="n"/>
+      <c r="S308" s="9" t="n"/>
     </row>
     <row r="309" ht="23" customHeight="1">
       <c r="A309" s="14" t="n"/>
@@ -10961,6 +11900,9 @@
         <f>IF(A309="","",IF(COUNTIF($A$2:$A$501,A309)&gt;1,"Duplicate lot ID",IF(OR(B309="",H309="",I309="",J309=""),"Complete required fields",IF(L309&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q309" s="14" t="n"/>
+      <c r="R309" s="14" t="n"/>
+      <c r="S309" s="14" t="n"/>
     </row>
     <row r="310" ht="23" customHeight="1">
       <c r="A310" s="9" t="n"/>
@@ -10994,6 +11936,9 @@
         <f>IF(A310="","",IF(COUNTIF($A$2:$A$501,A310)&gt;1,"Duplicate lot ID",IF(OR(B310="",H310="",I310="",J310=""),"Complete required fields",IF(L310&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q310" s="9" t="n"/>
+      <c r="R310" s="9" t="n"/>
+      <c r="S310" s="9" t="n"/>
     </row>
     <row r="311" ht="23" customHeight="1">
       <c r="A311" s="14" t="n"/>
@@ -11027,6 +11972,9 @@
         <f>IF(A311="","",IF(COUNTIF($A$2:$A$501,A311)&gt;1,"Duplicate lot ID",IF(OR(B311="",H311="",I311="",J311=""),"Complete required fields",IF(L311&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q311" s="14" t="n"/>
+      <c r="R311" s="14" t="n"/>
+      <c r="S311" s="14" t="n"/>
     </row>
     <row r="312" ht="23" customHeight="1">
       <c r="A312" s="9" t="n"/>
@@ -11060,6 +12008,9 @@
         <f>IF(A312="","",IF(COUNTIF($A$2:$A$501,A312)&gt;1,"Duplicate lot ID",IF(OR(B312="",H312="",I312="",J312=""),"Complete required fields",IF(L312&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q312" s="9" t="n"/>
+      <c r="R312" s="9" t="n"/>
+      <c r="S312" s="9" t="n"/>
     </row>
     <row r="313" ht="23" customHeight="1">
       <c r="A313" s="14" t="n"/>
@@ -11093,6 +12044,9 @@
         <f>IF(A313="","",IF(COUNTIF($A$2:$A$501,A313)&gt;1,"Duplicate lot ID",IF(OR(B313="",H313="",I313="",J313=""),"Complete required fields",IF(L313&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q313" s="14" t="n"/>
+      <c r="R313" s="14" t="n"/>
+      <c r="S313" s="14" t="n"/>
     </row>
     <row r="314" ht="23" customHeight="1">
       <c r="A314" s="9" t="n"/>
@@ -11126,6 +12080,9 @@
         <f>IF(A314="","",IF(COUNTIF($A$2:$A$501,A314)&gt;1,"Duplicate lot ID",IF(OR(B314="",H314="",I314="",J314=""),"Complete required fields",IF(L314&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q314" s="9" t="n"/>
+      <c r="R314" s="9" t="n"/>
+      <c r="S314" s="9" t="n"/>
     </row>
     <row r="315" ht="23" customHeight="1">
       <c r="A315" s="14" t="n"/>
@@ -11159,6 +12116,9 @@
         <f>IF(A315="","",IF(COUNTIF($A$2:$A$501,A315)&gt;1,"Duplicate lot ID",IF(OR(B315="",H315="",I315="",J315=""),"Complete required fields",IF(L315&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q315" s="14" t="n"/>
+      <c r="R315" s="14" t="n"/>
+      <c r="S315" s="14" t="n"/>
     </row>
     <row r="316" ht="23" customHeight="1">
       <c r="A316" s="9" t="n"/>
@@ -11192,6 +12152,9 @@
         <f>IF(A316="","",IF(COUNTIF($A$2:$A$501,A316)&gt;1,"Duplicate lot ID",IF(OR(B316="",H316="",I316="",J316=""),"Complete required fields",IF(L316&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q316" s="9" t="n"/>
+      <c r="R316" s="9" t="n"/>
+      <c r="S316" s="9" t="n"/>
     </row>
     <row r="317" ht="23" customHeight="1">
       <c r="A317" s="14" t="n"/>
@@ -11225,6 +12188,9 @@
         <f>IF(A317="","",IF(COUNTIF($A$2:$A$501,A317)&gt;1,"Duplicate lot ID",IF(OR(B317="",H317="",I317="",J317=""),"Complete required fields",IF(L317&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q317" s="14" t="n"/>
+      <c r="R317" s="14" t="n"/>
+      <c r="S317" s="14" t="n"/>
     </row>
     <row r="318" ht="23" customHeight="1">
       <c r="A318" s="9" t="n"/>
@@ -11258,6 +12224,9 @@
         <f>IF(A318="","",IF(COUNTIF($A$2:$A$501,A318)&gt;1,"Duplicate lot ID",IF(OR(B318="",H318="",I318="",J318=""),"Complete required fields",IF(L318&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q318" s="9" t="n"/>
+      <c r="R318" s="9" t="n"/>
+      <c r="S318" s="9" t="n"/>
     </row>
     <row r="319" ht="23" customHeight="1">
       <c r="A319" s="14" t="n"/>
@@ -11291,6 +12260,9 @@
         <f>IF(A319="","",IF(COUNTIF($A$2:$A$501,A319)&gt;1,"Duplicate lot ID",IF(OR(B319="",H319="",I319="",J319=""),"Complete required fields",IF(L319&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q319" s="14" t="n"/>
+      <c r="R319" s="14" t="n"/>
+      <c r="S319" s="14" t="n"/>
     </row>
     <row r="320" ht="23" customHeight="1">
       <c r="A320" s="9" t="n"/>
@@ -11324,6 +12296,9 @@
         <f>IF(A320="","",IF(COUNTIF($A$2:$A$501,A320)&gt;1,"Duplicate lot ID",IF(OR(B320="",H320="",I320="",J320=""),"Complete required fields",IF(L320&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q320" s="9" t="n"/>
+      <c r="R320" s="9" t="n"/>
+      <c r="S320" s="9" t="n"/>
     </row>
     <row r="321" ht="23" customHeight="1">
       <c r="A321" s="14" t="n"/>
@@ -11357,6 +12332,9 @@
         <f>IF(A321="","",IF(COUNTIF($A$2:$A$501,A321)&gt;1,"Duplicate lot ID",IF(OR(B321="",H321="",I321="",J321=""),"Complete required fields",IF(L321&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q321" s="14" t="n"/>
+      <c r="R321" s="14" t="n"/>
+      <c r="S321" s="14" t="n"/>
     </row>
     <row r="322" ht="23" customHeight="1">
       <c r="A322" s="9" t="n"/>
@@ -11390,6 +12368,9 @@
         <f>IF(A322="","",IF(COUNTIF($A$2:$A$501,A322)&gt;1,"Duplicate lot ID",IF(OR(B322="",H322="",I322="",J322=""),"Complete required fields",IF(L322&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q322" s="9" t="n"/>
+      <c r="R322" s="9" t="n"/>
+      <c r="S322" s="9" t="n"/>
     </row>
     <row r="323" ht="23" customHeight="1">
       <c r="A323" s="14" t="n"/>
@@ -11423,6 +12404,9 @@
         <f>IF(A323="","",IF(COUNTIF($A$2:$A$501,A323)&gt;1,"Duplicate lot ID",IF(OR(B323="",H323="",I323="",J323=""),"Complete required fields",IF(L323&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q323" s="14" t="n"/>
+      <c r="R323" s="14" t="n"/>
+      <c r="S323" s="14" t="n"/>
     </row>
     <row r="324" ht="23" customHeight="1">
       <c r="A324" s="9" t="n"/>
@@ -11456,6 +12440,9 @@
         <f>IF(A324="","",IF(COUNTIF($A$2:$A$501,A324)&gt;1,"Duplicate lot ID",IF(OR(B324="",H324="",I324="",J324=""),"Complete required fields",IF(L324&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q324" s="9" t="n"/>
+      <c r="R324" s="9" t="n"/>
+      <c r="S324" s="9" t="n"/>
     </row>
     <row r="325" ht="23" customHeight="1">
       <c r="A325" s="14" t="n"/>
@@ -11489,6 +12476,9 @@
         <f>IF(A325="","",IF(COUNTIF($A$2:$A$501,A325)&gt;1,"Duplicate lot ID",IF(OR(B325="",H325="",I325="",J325=""),"Complete required fields",IF(L325&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q325" s="14" t="n"/>
+      <c r="R325" s="14" t="n"/>
+      <c r="S325" s="14" t="n"/>
     </row>
     <row r="326" ht="23" customHeight="1">
       <c r="A326" s="9" t="n"/>
@@ -11522,6 +12512,9 @@
         <f>IF(A326="","",IF(COUNTIF($A$2:$A$501,A326)&gt;1,"Duplicate lot ID",IF(OR(B326="",H326="",I326="",J326=""),"Complete required fields",IF(L326&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q326" s="9" t="n"/>
+      <c r="R326" s="9" t="n"/>
+      <c r="S326" s="9" t="n"/>
     </row>
     <row r="327" ht="23" customHeight="1">
       <c r="A327" s="14" t="n"/>
@@ -11555,6 +12548,9 @@
         <f>IF(A327="","",IF(COUNTIF($A$2:$A$501,A327)&gt;1,"Duplicate lot ID",IF(OR(B327="",H327="",I327="",J327=""),"Complete required fields",IF(L327&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q327" s="14" t="n"/>
+      <c r="R327" s="14" t="n"/>
+      <c r="S327" s="14" t="n"/>
     </row>
     <row r="328" ht="23" customHeight="1">
       <c r="A328" s="9" t="n"/>
@@ -11588,6 +12584,9 @@
         <f>IF(A328="","",IF(COUNTIF($A$2:$A$501,A328)&gt;1,"Duplicate lot ID",IF(OR(B328="",H328="",I328="",J328=""),"Complete required fields",IF(L328&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q328" s="9" t="n"/>
+      <c r="R328" s="9" t="n"/>
+      <c r="S328" s="9" t="n"/>
     </row>
     <row r="329" ht="23" customHeight="1">
       <c r="A329" s="14" t="n"/>
@@ -11621,6 +12620,9 @@
         <f>IF(A329="","",IF(COUNTIF($A$2:$A$501,A329)&gt;1,"Duplicate lot ID",IF(OR(B329="",H329="",I329="",J329=""),"Complete required fields",IF(L329&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q329" s="14" t="n"/>
+      <c r="R329" s="14" t="n"/>
+      <c r="S329" s="14" t="n"/>
     </row>
     <row r="330" ht="23" customHeight="1">
       <c r="A330" s="9" t="n"/>
@@ -11654,6 +12656,9 @@
         <f>IF(A330="","",IF(COUNTIF($A$2:$A$501,A330)&gt;1,"Duplicate lot ID",IF(OR(B330="",H330="",I330="",J330=""),"Complete required fields",IF(L330&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q330" s="9" t="n"/>
+      <c r="R330" s="9" t="n"/>
+      <c r="S330" s="9" t="n"/>
     </row>
     <row r="331" ht="23" customHeight="1">
       <c r="A331" s="14" t="n"/>
@@ -11687,6 +12692,9 @@
         <f>IF(A331="","",IF(COUNTIF($A$2:$A$501,A331)&gt;1,"Duplicate lot ID",IF(OR(B331="",H331="",I331="",J331=""),"Complete required fields",IF(L331&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q331" s="14" t="n"/>
+      <c r="R331" s="14" t="n"/>
+      <c r="S331" s="14" t="n"/>
     </row>
     <row r="332" ht="23" customHeight="1">
       <c r="A332" s="9" t="n"/>
@@ -11720,6 +12728,9 @@
         <f>IF(A332="","",IF(COUNTIF($A$2:$A$501,A332)&gt;1,"Duplicate lot ID",IF(OR(B332="",H332="",I332="",J332=""),"Complete required fields",IF(L332&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q332" s="9" t="n"/>
+      <c r="R332" s="9" t="n"/>
+      <c r="S332" s="9" t="n"/>
     </row>
     <row r="333" ht="23" customHeight="1">
       <c r="A333" s="14" t="n"/>
@@ -11753,6 +12764,9 @@
         <f>IF(A333="","",IF(COUNTIF($A$2:$A$501,A333)&gt;1,"Duplicate lot ID",IF(OR(B333="",H333="",I333="",J333=""),"Complete required fields",IF(L333&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q333" s="14" t="n"/>
+      <c r="R333" s="14" t="n"/>
+      <c r="S333" s="14" t="n"/>
     </row>
     <row r="334" ht="23" customHeight="1">
       <c r="A334" s="9" t="n"/>
@@ -11786,6 +12800,9 @@
         <f>IF(A334="","",IF(COUNTIF($A$2:$A$501,A334)&gt;1,"Duplicate lot ID",IF(OR(B334="",H334="",I334="",J334=""),"Complete required fields",IF(L334&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q334" s="9" t="n"/>
+      <c r="R334" s="9" t="n"/>
+      <c r="S334" s="9" t="n"/>
     </row>
     <row r="335" ht="23" customHeight="1">
       <c r="A335" s="14" t="n"/>
@@ -11819,6 +12836,9 @@
         <f>IF(A335="","",IF(COUNTIF($A$2:$A$501,A335)&gt;1,"Duplicate lot ID",IF(OR(B335="",H335="",I335="",J335=""),"Complete required fields",IF(L335&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q335" s="14" t="n"/>
+      <c r="R335" s="14" t="n"/>
+      <c r="S335" s="14" t="n"/>
     </row>
     <row r="336" ht="23" customHeight="1">
       <c r="A336" s="9" t="n"/>
@@ -11852,6 +12872,9 @@
         <f>IF(A336="","",IF(COUNTIF($A$2:$A$501,A336)&gt;1,"Duplicate lot ID",IF(OR(B336="",H336="",I336="",J336=""),"Complete required fields",IF(L336&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q336" s="9" t="n"/>
+      <c r="R336" s="9" t="n"/>
+      <c r="S336" s="9" t="n"/>
     </row>
     <row r="337" ht="23" customHeight="1">
       <c r="A337" s="14" t="n"/>
@@ -11885,6 +12908,9 @@
         <f>IF(A337="","",IF(COUNTIF($A$2:$A$501,A337)&gt;1,"Duplicate lot ID",IF(OR(B337="",H337="",I337="",J337=""),"Complete required fields",IF(L337&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q337" s="14" t="n"/>
+      <c r="R337" s="14" t="n"/>
+      <c r="S337" s="14" t="n"/>
     </row>
     <row r="338" ht="23" customHeight="1">
       <c r="A338" s="9" t="n"/>
@@ -11918,6 +12944,9 @@
         <f>IF(A338="","",IF(COUNTIF($A$2:$A$501,A338)&gt;1,"Duplicate lot ID",IF(OR(B338="",H338="",I338="",J338=""),"Complete required fields",IF(L338&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q338" s="9" t="n"/>
+      <c r="R338" s="9" t="n"/>
+      <c r="S338" s="9" t="n"/>
     </row>
     <row r="339" ht="23" customHeight="1">
       <c r="A339" s="14" t="n"/>
@@ -11951,6 +12980,9 @@
         <f>IF(A339="","",IF(COUNTIF($A$2:$A$501,A339)&gt;1,"Duplicate lot ID",IF(OR(B339="",H339="",I339="",J339=""),"Complete required fields",IF(L339&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q339" s="14" t="n"/>
+      <c r="R339" s="14" t="n"/>
+      <c r="S339" s="14" t="n"/>
     </row>
     <row r="340" ht="23" customHeight="1">
       <c r="A340" s="9" t="n"/>
@@ -11984,6 +13016,9 @@
         <f>IF(A340="","",IF(COUNTIF($A$2:$A$501,A340)&gt;1,"Duplicate lot ID",IF(OR(B340="",H340="",I340="",J340=""),"Complete required fields",IF(L340&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q340" s="9" t="n"/>
+      <c r="R340" s="9" t="n"/>
+      <c r="S340" s="9" t="n"/>
     </row>
     <row r="341" ht="23" customHeight="1">
       <c r="A341" s="14" t="n"/>
@@ -12017,6 +13052,9 @@
         <f>IF(A341="","",IF(COUNTIF($A$2:$A$501,A341)&gt;1,"Duplicate lot ID",IF(OR(B341="",H341="",I341="",J341=""),"Complete required fields",IF(L341&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q341" s="14" t="n"/>
+      <c r="R341" s="14" t="n"/>
+      <c r="S341" s="14" t="n"/>
     </row>
     <row r="342" ht="23" customHeight="1">
       <c r="A342" s="9" t="n"/>
@@ -12050,6 +13088,9 @@
         <f>IF(A342="","",IF(COUNTIF($A$2:$A$501,A342)&gt;1,"Duplicate lot ID",IF(OR(B342="",H342="",I342="",J342=""),"Complete required fields",IF(L342&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q342" s="9" t="n"/>
+      <c r="R342" s="9" t="n"/>
+      <c r="S342" s="9" t="n"/>
     </row>
     <row r="343" ht="23" customHeight="1">
       <c r="A343" s="14" t="n"/>
@@ -12083,6 +13124,9 @@
         <f>IF(A343="","",IF(COUNTIF($A$2:$A$501,A343)&gt;1,"Duplicate lot ID",IF(OR(B343="",H343="",I343="",J343=""),"Complete required fields",IF(L343&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q343" s="14" t="n"/>
+      <c r="R343" s="14" t="n"/>
+      <c r="S343" s="14" t="n"/>
     </row>
     <row r="344" ht="23" customHeight="1">
       <c r="A344" s="9" t="n"/>
@@ -12116,6 +13160,9 @@
         <f>IF(A344="","",IF(COUNTIF($A$2:$A$501,A344)&gt;1,"Duplicate lot ID",IF(OR(B344="",H344="",I344="",J344=""),"Complete required fields",IF(L344&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q344" s="9" t="n"/>
+      <c r="R344" s="9" t="n"/>
+      <c r="S344" s="9" t="n"/>
     </row>
     <row r="345" ht="23" customHeight="1">
       <c r="A345" s="14" t="n"/>
@@ -12149,6 +13196,9 @@
         <f>IF(A345="","",IF(COUNTIF($A$2:$A$501,A345)&gt;1,"Duplicate lot ID",IF(OR(B345="",H345="",I345="",J345=""),"Complete required fields",IF(L345&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q345" s="14" t="n"/>
+      <c r="R345" s="14" t="n"/>
+      <c r="S345" s="14" t="n"/>
     </row>
     <row r="346" ht="23" customHeight="1">
       <c r="A346" s="9" t="n"/>
@@ -12182,6 +13232,9 @@
         <f>IF(A346="","",IF(COUNTIF($A$2:$A$501,A346)&gt;1,"Duplicate lot ID",IF(OR(B346="",H346="",I346="",J346=""),"Complete required fields",IF(L346&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q346" s="9" t="n"/>
+      <c r="R346" s="9" t="n"/>
+      <c r="S346" s="9" t="n"/>
     </row>
     <row r="347" ht="23" customHeight="1">
       <c r="A347" s="14" t="n"/>
@@ -12215,6 +13268,9 @@
         <f>IF(A347="","",IF(COUNTIF($A$2:$A$501,A347)&gt;1,"Duplicate lot ID",IF(OR(B347="",H347="",I347="",J347=""),"Complete required fields",IF(L347&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q347" s="14" t="n"/>
+      <c r="R347" s="14" t="n"/>
+      <c r="S347" s="14" t="n"/>
     </row>
     <row r="348" ht="23" customHeight="1">
       <c r="A348" s="9" t="n"/>
@@ -12248,6 +13304,9 @@
         <f>IF(A348="","",IF(COUNTIF($A$2:$A$501,A348)&gt;1,"Duplicate lot ID",IF(OR(B348="",H348="",I348="",J348=""),"Complete required fields",IF(L348&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q348" s="9" t="n"/>
+      <c r="R348" s="9" t="n"/>
+      <c r="S348" s="9" t="n"/>
     </row>
     <row r="349" ht="23" customHeight="1">
       <c r="A349" s="14" t="n"/>
@@ -12281,6 +13340,9 @@
         <f>IF(A349="","",IF(COUNTIF($A$2:$A$501,A349)&gt;1,"Duplicate lot ID",IF(OR(B349="",H349="",I349="",J349=""),"Complete required fields",IF(L349&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q349" s="14" t="n"/>
+      <c r="R349" s="14" t="n"/>
+      <c r="S349" s="14" t="n"/>
     </row>
     <row r="350" ht="23" customHeight="1">
       <c r="A350" s="9" t="n"/>
@@ -12314,6 +13376,9 @@
         <f>IF(A350="","",IF(COUNTIF($A$2:$A$501,A350)&gt;1,"Duplicate lot ID",IF(OR(B350="",H350="",I350="",J350=""),"Complete required fields",IF(L350&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q350" s="9" t="n"/>
+      <c r="R350" s="9" t="n"/>
+      <c r="S350" s="9" t="n"/>
     </row>
     <row r="351" ht="23" customHeight="1">
       <c r="A351" s="14" t="n"/>
@@ -12347,6 +13412,9 @@
         <f>IF(A351="","",IF(COUNTIF($A$2:$A$501,A351)&gt;1,"Duplicate lot ID",IF(OR(B351="",H351="",I351="",J351=""),"Complete required fields",IF(L351&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q351" s="14" t="n"/>
+      <c r="R351" s="14" t="n"/>
+      <c r="S351" s="14" t="n"/>
     </row>
     <row r="352" ht="23" customHeight="1">
       <c r="A352" s="9" t="n"/>
@@ -12380,6 +13448,9 @@
         <f>IF(A352="","",IF(COUNTIF($A$2:$A$501,A352)&gt;1,"Duplicate lot ID",IF(OR(B352="",H352="",I352="",J352=""),"Complete required fields",IF(L352&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q352" s="9" t="n"/>
+      <c r="R352" s="9" t="n"/>
+      <c r="S352" s="9" t="n"/>
     </row>
     <row r="353" ht="23" customHeight="1">
       <c r="A353" s="14" t="n"/>
@@ -12413,6 +13484,9 @@
         <f>IF(A353="","",IF(COUNTIF($A$2:$A$501,A353)&gt;1,"Duplicate lot ID",IF(OR(B353="",H353="",I353="",J353=""),"Complete required fields",IF(L353&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q353" s="14" t="n"/>
+      <c r="R353" s="14" t="n"/>
+      <c r="S353" s="14" t="n"/>
     </row>
     <row r="354" ht="23" customHeight="1">
       <c r="A354" s="9" t="n"/>
@@ -12446,6 +13520,9 @@
         <f>IF(A354="","",IF(COUNTIF($A$2:$A$501,A354)&gt;1,"Duplicate lot ID",IF(OR(B354="",H354="",I354="",J354=""),"Complete required fields",IF(L354&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q354" s="9" t="n"/>
+      <c r="R354" s="9" t="n"/>
+      <c r="S354" s="9" t="n"/>
     </row>
     <row r="355" ht="23" customHeight="1">
       <c r="A355" s="14" t="n"/>
@@ -12479,6 +13556,9 @@
         <f>IF(A355="","",IF(COUNTIF($A$2:$A$501,A355)&gt;1,"Duplicate lot ID",IF(OR(B355="",H355="",I355="",J355=""),"Complete required fields",IF(L355&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q355" s="14" t="n"/>
+      <c r="R355" s="14" t="n"/>
+      <c r="S355" s="14" t="n"/>
     </row>
     <row r="356" ht="23" customHeight="1">
       <c r="A356" s="9" t="n"/>
@@ -12512,6 +13592,9 @@
         <f>IF(A356="","",IF(COUNTIF($A$2:$A$501,A356)&gt;1,"Duplicate lot ID",IF(OR(B356="",H356="",I356="",J356=""),"Complete required fields",IF(L356&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q356" s="9" t="n"/>
+      <c r="R356" s="9" t="n"/>
+      <c r="S356" s="9" t="n"/>
     </row>
     <row r="357" ht="23" customHeight="1">
       <c r="A357" s="14" t="n"/>
@@ -12545,6 +13628,9 @@
         <f>IF(A357="","",IF(COUNTIF($A$2:$A$501,A357)&gt;1,"Duplicate lot ID",IF(OR(B357="",H357="",I357="",J357=""),"Complete required fields",IF(L357&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q357" s="14" t="n"/>
+      <c r="R357" s="14" t="n"/>
+      <c r="S357" s="14" t="n"/>
     </row>
     <row r="358" ht="23" customHeight="1">
       <c r="A358" s="9" t="n"/>
@@ -12578,6 +13664,9 @@
         <f>IF(A358="","",IF(COUNTIF($A$2:$A$501,A358)&gt;1,"Duplicate lot ID",IF(OR(B358="",H358="",I358="",J358=""),"Complete required fields",IF(L358&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q358" s="9" t="n"/>
+      <c r="R358" s="9" t="n"/>
+      <c r="S358" s="9" t="n"/>
     </row>
     <row r="359" ht="23" customHeight="1">
       <c r="A359" s="14" t="n"/>
@@ -12611,6 +13700,9 @@
         <f>IF(A359="","",IF(COUNTIF($A$2:$A$501,A359)&gt;1,"Duplicate lot ID",IF(OR(B359="",H359="",I359="",J359=""),"Complete required fields",IF(L359&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q359" s="14" t="n"/>
+      <c r="R359" s="14" t="n"/>
+      <c r="S359" s="14" t="n"/>
     </row>
     <row r="360" ht="23" customHeight="1">
       <c r="A360" s="9" t="n"/>
@@ -12644,6 +13736,9 @@
         <f>IF(A360="","",IF(COUNTIF($A$2:$A$501,A360)&gt;1,"Duplicate lot ID",IF(OR(B360="",H360="",I360="",J360=""),"Complete required fields",IF(L360&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q360" s="9" t="n"/>
+      <c r="R360" s="9" t="n"/>
+      <c r="S360" s="9" t="n"/>
     </row>
     <row r="361" ht="23" customHeight="1">
       <c r="A361" s="14" t="n"/>
@@ -12677,6 +13772,9 @@
         <f>IF(A361="","",IF(COUNTIF($A$2:$A$501,A361)&gt;1,"Duplicate lot ID",IF(OR(B361="",H361="",I361="",J361=""),"Complete required fields",IF(L361&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q361" s="14" t="n"/>
+      <c r="R361" s="14" t="n"/>
+      <c r="S361" s="14" t="n"/>
     </row>
     <row r="362" ht="23" customHeight="1">
       <c r="A362" s="9" t="n"/>
@@ -12710,6 +13808,9 @@
         <f>IF(A362="","",IF(COUNTIF($A$2:$A$501,A362)&gt;1,"Duplicate lot ID",IF(OR(B362="",H362="",I362="",J362=""),"Complete required fields",IF(L362&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q362" s="9" t="n"/>
+      <c r="R362" s="9" t="n"/>
+      <c r="S362" s="9" t="n"/>
     </row>
     <row r="363" ht="23" customHeight="1">
       <c r="A363" s="14" t="n"/>
@@ -12743,6 +13844,9 @@
         <f>IF(A363="","",IF(COUNTIF($A$2:$A$501,A363)&gt;1,"Duplicate lot ID",IF(OR(B363="",H363="",I363="",J363=""),"Complete required fields",IF(L363&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q363" s="14" t="n"/>
+      <c r="R363" s="14" t="n"/>
+      <c r="S363" s="14" t="n"/>
     </row>
     <row r="364" ht="23" customHeight="1">
       <c r="A364" s="9" t="n"/>
@@ -12776,6 +13880,9 @@
         <f>IF(A364="","",IF(COUNTIF($A$2:$A$501,A364)&gt;1,"Duplicate lot ID",IF(OR(B364="",H364="",I364="",J364=""),"Complete required fields",IF(L364&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q364" s="9" t="n"/>
+      <c r="R364" s="9" t="n"/>
+      <c r="S364" s="9" t="n"/>
     </row>
     <row r="365" ht="23" customHeight="1">
       <c r="A365" s="14" t="n"/>
@@ -12809,6 +13916,9 @@
         <f>IF(A365="","",IF(COUNTIF($A$2:$A$501,A365)&gt;1,"Duplicate lot ID",IF(OR(B365="",H365="",I365="",J365=""),"Complete required fields",IF(L365&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q365" s="14" t="n"/>
+      <c r="R365" s="14" t="n"/>
+      <c r="S365" s="14" t="n"/>
     </row>
     <row r="366" ht="23" customHeight="1">
       <c r="A366" s="9" t="n"/>
@@ -12842,6 +13952,9 @@
         <f>IF(A366="","",IF(COUNTIF($A$2:$A$501,A366)&gt;1,"Duplicate lot ID",IF(OR(B366="",H366="",I366="",J366=""),"Complete required fields",IF(L366&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q366" s="9" t="n"/>
+      <c r="R366" s="9" t="n"/>
+      <c r="S366" s="9" t="n"/>
     </row>
     <row r="367" ht="23" customHeight="1">
       <c r="A367" s="14" t="n"/>
@@ -12875,6 +13988,9 @@
         <f>IF(A367="","",IF(COUNTIF($A$2:$A$501,A367)&gt;1,"Duplicate lot ID",IF(OR(B367="",H367="",I367="",J367=""),"Complete required fields",IF(L367&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q367" s="14" t="n"/>
+      <c r="R367" s="14" t="n"/>
+      <c r="S367" s="14" t="n"/>
     </row>
     <row r="368" ht="23" customHeight="1">
       <c r="A368" s="9" t="n"/>
@@ -12908,6 +14024,9 @@
         <f>IF(A368="","",IF(COUNTIF($A$2:$A$501,A368)&gt;1,"Duplicate lot ID",IF(OR(B368="",H368="",I368="",J368=""),"Complete required fields",IF(L368&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q368" s="9" t="n"/>
+      <c r="R368" s="9" t="n"/>
+      <c r="S368" s="9" t="n"/>
     </row>
     <row r="369" ht="23" customHeight="1">
       <c r="A369" s="14" t="n"/>
@@ -12941,6 +14060,9 @@
         <f>IF(A369="","",IF(COUNTIF($A$2:$A$501,A369)&gt;1,"Duplicate lot ID",IF(OR(B369="",H369="",I369="",J369=""),"Complete required fields",IF(L369&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q369" s="14" t="n"/>
+      <c r="R369" s="14" t="n"/>
+      <c r="S369" s="14" t="n"/>
     </row>
     <row r="370" ht="23" customHeight="1">
       <c r="A370" s="9" t="n"/>
@@ -12974,6 +14096,9 @@
         <f>IF(A370="","",IF(COUNTIF($A$2:$A$501,A370)&gt;1,"Duplicate lot ID",IF(OR(B370="",H370="",I370="",J370=""),"Complete required fields",IF(L370&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q370" s="9" t="n"/>
+      <c r="R370" s="9" t="n"/>
+      <c r="S370" s="9" t="n"/>
     </row>
     <row r="371" ht="23" customHeight="1">
       <c r="A371" s="14" t="n"/>
@@ -13007,6 +14132,9 @@
         <f>IF(A371="","",IF(COUNTIF($A$2:$A$501,A371)&gt;1,"Duplicate lot ID",IF(OR(B371="",H371="",I371="",J371=""),"Complete required fields",IF(L371&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q371" s="14" t="n"/>
+      <c r="R371" s="14" t="n"/>
+      <c r="S371" s="14" t="n"/>
     </row>
     <row r="372" ht="23" customHeight="1">
       <c r="A372" s="9" t="n"/>
@@ -13040,6 +14168,9 @@
         <f>IF(A372="","",IF(COUNTIF($A$2:$A$501,A372)&gt;1,"Duplicate lot ID",IF(OR(B372="",H372="",I372="",J372=""),"Complete required fields",IF(L372&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q372" s="9" t="n"/>
+      <c r="R372" s="9" t="n"/>
+      <c r="S372" s="9" t="n"/>
     </row>
     <row r="373" ht="23" customHeight="1">
       <c r="A373" s="14" t="n"/>
@@ -13073,6 +14204,9 @@
         <f>IF(A373="","",IF(COUNTIF($A$2:$A$501,A373)&gt;1,"Duplicate lot ID",IF(OR(B373="",H373="",I373="",J373=""),"Complete required fields",IF(L373&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q373" s="14" t="n"/>
+      <c r="R373" s="14" t="n"/>
+      <c r="S373" s="14" t="n"/>
     </row>
     <row r="374" ht="23" customHeight="1">
       <c r="A374" s="9" t="n"/>
@@ -13106,6 +14240,9 @@
         <f>IF(A374="","",IF(COUNTIF($A$2:$A$501,A374)&gt;1,"Duplicate lot ID",IF(OR(B374="",H374="",I374="",J374=""),"Complete required fields",IF(L374&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q374" s="9" t="n"/>
+      <c r="R374" s="9" t="n"/>
+      <c r="S374" s="9" t="n"/>
     </row>
     <row r="375" ht="23" customHeight="1">
       <c r="A375" s="14" t="n"/>
@@ -13139,6 +14276,9 @@
         <f>IF(A375="","",IF(COUNTIF($A$2:$A$501,A375)&gt;1,"Duplicate lot ID",IF(OR(B375="",H375="",I375="",J375=""),"Complete required fields",IF(L375&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q375" s="14" t="n"/>
+      <c r="R375" s="14" t="n"/>
+      <c r="S375" s="14" t="n"/>
     </row>
     <row r="376" ht="23" customHeight="1">
       <c r="A376" s="9" t="n"/>
@@ -13172,6 +14312,9 @@
         <f>IF(A376="","",IF(COUNTIF($A$2:$A$501,A376)&gt;1,"Duplicate lot ID",IF(OR(B376="",H376="",I376="",J376=""),"Complete required fields",IF(L376&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q376" s="9" t="n"/>
+      <c r="R376" s="9" t="n"/>
+      <c r="S376" s="9" t="n"/>
     </row>
     <row r="377" ht="23" customHeight="1">
       <c r="A377" s="14" t="n"/>
@@ -13205,6 +14348,9 @@
         <f>IF(A377="","",IF(COUNTIF($A$2:$A$501,A377)&gt;1,"Duplicate lot ID",IF(OR(B377="",H377="",I377="",J377=""),"Complete required fields",IF(L377&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q377" s="14" t="n"/>
+      <c r="R377" s="14" t="n"/>
+      <c r="S377" s="14" t="n"/>
     </row>
     <row r="378" ht="23" customHeight="1">
       <c r="A378" s="9" t="n"/>
@@ -13238,6 +14384,9 @@
         <f>IF(A378="","",IF(COUNTIF($A$2:$A$501,A378)&gt;1,"Duplicate lot ID",IF(OR(B378="",H378="",I378="",J378=""),"Complete required fields",IF(L378&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q378" s="9" t="n"/>
+      <c r="R378" s="9" t="n"/>
+      <c r="S378" s="9" t="n"/>
     </row>
     <row r="379" ht="23" customHeight="1">
       <c r="A379" s="14" t="n"/>
@@ -13271,6 +14420,9 @@
         <f>IF(A379="","",IF(COUNTIF($A$2:$A$501,A379)&gt;1,"Duplicate lot ID",IF(OR(B379="",H379="",I379="",J379=""),"Complete required fields",IF(L379&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q379" s="14" t="n"/>
+      <c r="R379" s="14" t="n"/>
+      <c r="S379" s="14" t="n"/>
     </row>
     <row r="380" ht="23" customHeight="1">
       <c r="A380" s="9" t="n"/>
@@ -13304,6 +14456,9 @@
         <f>IF(A380="","",IF(COUNTIF($A$2:$A$501,A380)&gt;1,"Duplicate lot ID",IF(OR(B380="",H380="",I380="",J380=""),"Complete required fields",IF(L380&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q380" s="9" t="n"/>
+      <c r="R380" s="9" t="n"/>
+      <c r="S380" s="9" t="n"/>
     </row>
     <row r="381" ht="23" customHeight="1">
       <c r="A381" s="14" t="n"/>
@@ -13337,6 +14492,9 @@
         <f>IF(A381="","",IF(COUNTIF($A$2:$A$501,A381)&gt;1,"Duplicate lot ID",IF(OR(B381="",H381="",I381="",J381=""),"Complete required fields",IF(L381&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q381" s="14" t="n"/>
+      <c r="R381" s="14" t="n"/>
+      <c r="S381" s="14" t="n"/>
     </row>
     <row r="382" ht="23" customHeight="1">
       <c r="A382" s="9" t="n"/>
@@ -13370,6 +14528,9 @@
         <f>IF(A382="","",IF(COUNTIF($A$2:$A$501,A382)&gt;1,"Duplicate lot ID",IF(OR(B382="",H382="",I382="",J382=""),"Complete required fields",IF(L382&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q382" s="9" t="n"/>
+      <c r="R382" s="9" t="n"/>
+      <c r="S382" s="9" t="n"/>
     </row>
     <row r="383" ht="23" customHeight="1">
       <c r="A383" s="14" t="n"/>
@@ -13403,6 +14564,9 @@
         <f>IF(A383="","",IF(COUNTIF($A$2:$A$501,A383)&gt;1,"Duplicate lot ID",IF(OR(B383="",H383="",I383="",J383=""),"Complete required fields",IF(L383&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q383" s="14" t="n"/>
+      <c r="R383" s="14" t="n"/>
+      <c r="S383" s="14" t="n"/>
     </row>
     <row r="384" ht="23" customHeight="1">
       <c r="A384" s="9" t="n"/>
@@ -13436,6 +14600,9 @@
         <f>IF(A384="","",IF(COUNTIF($A$2:$A$501,A384)&gt;1,"Duplicate lot ID",IF(OR(B384="",H384="",I384="",J384=""),"Complete required fields",IF(L384&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q384" s="9" t="n"/>
+      <c r="R384" s="9" t="n"/>
+      <c r="S384" s="9" t="n"/>
     </row>
     <row r="385" ht="23" customHeight="1">
       <c r="A385" s="14" t="n"/>
@@ -13469,6 +14636,9 @@
         <f>IF(A385="","",IF(COUNTIF($A$2:$A$501,A385)&gt;1,"Duplicate lot ID",IF(OR(B385="",H385="",I385="",J385=""),"Complete required fields",IF(L385&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q385" s="14" t="n"/>
+      <c r="R385" s="14" t="n"/>
+      <c r="S385" s="14" t="n"/>
     </row>
     <row r="386" ht="23" customHeight="1">
       <c r="A386" s="9" t="n"/>
@@ -13502,6 +14672,9 @@
         <f>IF(A386="","",IF(COUNTIF($A$2:$A$501,A386)&gt;1,"Duplicate lot ID",IF(OR(B386="",H386="",I386="",J386=""),"Complete required fields",IF(L386&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q386" s="9" t="n"/>
+      <c r="R386" s="9" t="n"/>
+      <c r="S386" s="9" t="n"/>
     </row>
     <row r="387" ht="23" customHeight="1">
       <c r="A387" s="14" t="n"/>
@@ -13535,6 +14708,9 @@
         <f>IF(A387="","",IF(COUNTIF($A$2:$A$501,A387)&gt;1,"Duplicate lot ID",IF(OR(B387="",H387="",I387="",J387=""),"Complete required fields",IF(L387&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q387" s="14" t="n"/>
+      <c r="R387" s="14" t="n"/>
+      <c r="S387" s="14" t="n"/>
     </row>
     <row r="388" ht="23" customHeight="1">
       <c r="A388" s="9" t="n"/>
@@ -13568,6 +14744,9 @@
         <f>IF(A388="","",IF(COUNTIF($A$2:$A$501,A388)&gt;1,"Duplicate lot ID",IF(OR(B388="",H388="",I388="",J388=""),"Complete required fields",IF(L388&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q388" s="9" t="n"/>
+      <c r="R388" s="9" t="n"/>
+      <c r="S388" s="9" t="n"/>
     </row>
     <row r="389" ht="23" customHeight="1">
       <c r="A389" s="14" t="n"/>
@@ -13601,6 +14780,9 @@
         <f>IF(A389="","",IF(COUNTIF($A$2:$A$501,A389)&gt;1,"Duplicate lot ID",IF(OR(B389="",H389="",I389="",J389=""),"Complete required fields",IF(L389&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q389" s="14" t="n"/>
+      <c r="R389" s="14" t="n"/>
+      <c r="S389" s="14" t="n"/>
     </row>
     <row r="390" ht="23" customHeight="1">
       <c r="A390" s="9" t="n"/>
@@ -13634,6 +14816,9 @@
         <f>IF(A390="","",IF(COUNTIF($A$2:$A$501,A390)&gt;1,"Duplicate lot ID",IF(OR(B390="",H390="",I390="",J390=""),"Complete required fields",IF(L390&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q390" s="9" t="n"/>
+      <c r="R390" s="9" t="n"/>
+      <c r="S390" s="9" t="n"/>
     </row>
     <row r="391" ht="23" customHeight="1">
       <c r="A391" s="14" t="n"/>
@@ -13667,6 +14852,9 @@
         <f>IF(A391="","",IF(COUNTIF($A$2:$A$501,A391)&gt;1,"Duplicate lot ID",IF(OR(B391="",H391="",I391="",J391=""),"Complete required fields",IF(L391&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q391" s="14" t="n"/>
+      <c r="R391" s="14" t="n"/>
+      <c r="S391" s="14" t="n"/>
     </row>
     <row r="392" ht="23" customHeight="1">
       <c r="A392" s="9" t="n"/>
@@ -13700,6 +14888,9 @@
         <f>IF(A392="","",IF(COUNTIF($A$2:$A$501,A392)&gt;1,"Duplicate lot ID",IF(OR(B392="",H392="",I392="",J392=""),"Complete required fields",IF(L392&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q392" s="9" t="n"/>
+      <c r="R392" s="9" t="n"/>
+      <c r="S392" s="9" t="n"/>
     </row>
     <row r="393" ht="23" customHeight="1">
       <c r="A393" s="14" t="n"/>
@@ -13733,6 +14924,9 @@
         <f>IF(A393="","",IF(COUNTIF($A$2:$A$501,A393)&gt;1,"Duplicate lot ID",IF(OR(B393="",H393="",I393="",J393=""),"Complete required fields",IF(L393&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q393" s="14" t="n"/>
+      <c r="R393" s="14" t="n"/>
+      <c r="S393" s="14" t="n"/>
     </row>
     <row r="394" ht="23" customHeight="1">
       <c r="A394" s="9" t="n"/>
@@ -13766,6 +14960,9 @@
         <f>IF(A394="","",IF(COUNTIF($A$2:$A$501,A394)&gt;1,"Duplicate lot ID",IF(OR(B394="",H394="",I394="",J394=""),"Complete required fields",IF(L394&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q394" s="9" t="n"/>
+      <c r="R394" s="9" t="n"/>
+      <c r="S394" s="9" t="n"/>
     </row>
     <row r="395" ht="23" customHeight="1">
       <c r="A395" s="14" t="n"/>
@@ -13799,6 +14996,9 @@
         <f>IF(A395="","",IF(COUNTIF($A$2:$A$501,A395)&gt;1,"Duplicate lot ID",IF(OR(B395="",H395="",I395="",J395=""),"Complete required fields",IF(L395&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q395" s="14" t="n"/>
+      <c r="R395" s="14" t="n"/>
+      <c r="S395" s="14" t="n"/>
     </row>
     <row r="396" ht="23" customHeight="1">
       <c r="A396" s="9" t="n"/>
@@ -13832,6 +15032,9 @@
         <f>IF(A396="","",IF(COUNTIF($A$2:$A$501,A396)&gt;1,"Duplicate lot ID",IF(OR(B396="",H396="",I396="",J396=""),"Complete required fields",IF(L396&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q396" s="9" t="n"/>
+      <c r="R396" s="9" t="n"/>
+      <c r="S396" s="9" t="n"/>
     </row>
     <row r="397" ht="23" customHeight="1">
       <c r="A397" s="14" t="n"/>
@@ -13865,6 +15068,9 @@
         <f>IF(A397="","",IF(COUNTIF($A$2:$A$501,A397)&gt;1,"Duplicate lot ID",IF(OR(B397="",H397="",I397="",J397=""),"Complete required fields",IF(L397&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q397" s="14" t="n"/>
+      <c r="R397" s="14" t="n"/>
+      <c r="S397" s="14" t="n"/>
     </row>
     <row r="398" ht="23" customHeight="1">
       <c r="A398" s="9" t="n"/>
@@ -13898,6 +15104,9 @@
         <f>IF(A398="","",IF(COUNTIF($A$2:$A$501,A398)&gt;1,"Duplicate lot ID",IF(OR(B398="",H398="",I398="",J398=""),"Complete required fields",IF(L398&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q398" s="9" t="n"/>
+      <c r="R398" s="9" t="n"/>
+      <c r="S398" s="9" t="n"/>
     </row>
     <row r="399" ht="23" customHeight="1">
       <c r="A399" s="14" t="n"/>
@@ -13931,6 +15140,9 @@
         <f>IF(A399="","",IF(COUNTIF($A$2:$A$501,A399)&gt;1,"Duplicate lot ID",IF(OR(B399="",H399="",I399="",J399=""),"Complete required fields",IF(L399&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q399" s="14" t="n"/>
+      <c r="R399" s="14" t="n"/>
+      <c r="S399" s="14" t="n"/>
     </row>
     <row r="400" ht="23" customHeight="1">
       <c r="A400" s="9" t="n"/>
@@ -13964,6 +15176,9 @@
         <f>IF(A400="","",IF(COUNTIF($A$2:$A$501,A400)&gt;1,"Duplicate lot ID",IF(OR(B400="",H400="",I400="",J400=""),"Complete required fields",IF(L400&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q400" s="9" t="n"/>
+      <c r="R400" s="9" t="n"/>
+      <c r="S400" s="9" t="n"/>
     </row>
     <row r="401" ht="23" customHeight="1">
       <c r="A401" s="14" t="n"/>
@@ -13997,6 +15212,9 @@
         <f>IF(A401="","",IF(COUNTIF($A$2:$A$501,A401)&gt;1,"Duplicate lot ID",IF(OR(B401="",H401="",I401="",J401=""),"Complete required fields",IF(L401&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q401" s="14" t="n"/>
+      <c r="R401" s="14" t="n"/>
+      <c r="S401" s="14" t="n"/>
     </row>
     <row r="402" ht="23" customHeight="1">
       <c r="A402" s="9" t="n"/>
@@ -14030,6 +15248,9 @@
         <f>IF(A402="","",IF(COUNTIF($A$2:$A$501,A402)&gt;1,"Duplicate lot ID",IF(OR(B402="",H402="",I402="",J402=""),"Complete required fields",IF(L402&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q402" s="9" t="n"/>
+      <c r="R402" s="9" t="n"/>
+      <c r="S402" s="9" t="n"/>
     </row>
     <row r="403" ht="23" customHeight="1">
       <c r="A403" s="14" t="n"/>
@@ -14063,6 +15284,9 @@
         <f>IF(A403="","",IF(COUNTIF($A$2:$A$501,A403)&gt;1,"Duplicate lot ID",IF(OR(B403="",H403="",I403="",J403=""),"Complete required fields",IF(L403&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q403" s="14" t="n"/>
+      <c r="R403" s="14" t="n"/>
+      <c r="S403" s="14" t="n"/>
     </row>
     <row r="404" ht="23" customHeight="1">
       <c r="A404" s="9" t="n"/>
@@ -14096,6 +15320,9 @@
         <f>IF(A404="","",IF(COUNTIF($A$2:$A$501,A404)&gt;1,"Duplicate lot ID",IF(OR(B404="",H404="",I404="",J404=""),"Complete required fields",IF(L404&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q404" s="9" t="n"/>
+      <c r="R404" s="9" t="n"/>
+      <c r="S404" s="9" t="n"/>
     </row>
     <row r="405" ht="23" customHeight="1">
       <c r="A405" s="14" t="n"/>
@@ -14129,6 +15356,9 @@
         <f>IF(A405="","",IF(COUNTIF($A$2:$A$501,A405)&gt;1,"Duplicate lot ID",IF(OR(B405="",H405="",I405="",J405=""),"Complete required fields",IF(L405&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q405" s="14" t="n"/>
+      <c r="R405" s="14" t="n"/>
+      <c r="S405" s="14" t="n"/>
     </row>
     <row r="406" ht="23" customHeight="1">
       <c r="A406" s="9" t="n"/>
@@ -14162,6 +15392,9 @@
         <f>IF(A406="","",IF(COUNTIF($A$2:$A$501,A406)&gt;1,"Duplicate lot ID",IF(OR(B406="",H406="",I406="",J406=""),"Complete required fields",IF(L406&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q406" s="9" t="n"/>
+      <c r="R406" s="9" t="n"/>
+      <c r="S406" s="9" t="n"/>
     </row>
     <row r="407" ht="23" customHeight="1">
       <c r="A407" s="14" t="n"/>
@@ -14195,6 +15428,9 @@
         <f>IF(A407="","",IF(COUNTIF($A$2:$A$501,A407)&gt;1,"Duplicate lot ID",IF(OR(B407="",H407="",I407="",J407=""),"Complete required fields",IF(L407&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q407" s="14" t="n"/>
+      <c r="R407" s="14" t="n"/>
+      <c r="S407" s="14" t="n"/>
     </row>
     <row r="408" ht="23" customHeight="1">
       <c r="A408" s="9" t="n"/>
@@ -14228,6 +15464,9 @@
         <f>IF(A408="","",IF(COUNTIF($A$2:$A$501,A408)&gt;1,"Duplicate lot ID",IF(OR(B408="",H408="",I408="",J408=""),"Complete required fields",IF(L408&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q408" s="9" t="n"/>
+      <c r="R408" s="9" t="n"/>
+      <c r="S408" s="9" t="n"/>
     </row>
     <row r="409" ht="23" customHeight="1">
       <c r="A409" s="14" t="n"/>
@@ -14261,6 +15500,9 @@
         <f>IF(A409="","",IF(COUNTIF($A$2:$A$501,A409)&gt;1,"Duplicate lot ID",IF(OR(B409="",H409="",I409="",J409=""),"Complete required fields",IF(L409&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q409" s="14" t="n"/>
+      <c r="R409" s="14" t="n"/>
+      <c r="S409" s="14" t="n"/>
     </row>
     <row r="410" ht="23" customHeight="1">
       <c r="A410" s="9" t="n"/>
@@ -14294,6 +15536,9 @@
         <f>IF(A410="","",IF(COUNTIF($A$2:$A$501,A410)&gt;1,"Duplicate lot ID",IF(OR(B410="",H410="",I410="",J410=""),"Complete required fields",IF(L410&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q410" s="9" t="n"/>
+      <c r="R410" s="9" t="n"/>
+      <c r="S410" s="9" t="n"/>
     </row>
     <row r="411" ht="23" customHeight="1">
       <c r="A411" s="14" t="n"/>
@@ -14327,6 +15572,9 @@
         <f>IF(A411="","",IF(COUNTIF($A$2:$A$501,A411)&gt;1,"Duplicate lot ID",IF(OR(B411="",H411="",I411="",J411=""),"Complete required fields",IF(L411&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q411" s="14" t="n"/>
+      <c r="R411" s="14" t="n"/>
+      <c r="S411" s="14" t="n"/>
     </row>
     <row r="412" ht="23" customHeight="1">
       <c r="A412" s="9" t="n"/>
@@ -14360,6 +15608,9 @@
         <f>IF(A412="","",IF(COUNTIF($A$2:$A$501,A412)&gt;1,"Duplicate lot ID",IF(OR(B412="",H412="",I412="",J412=""),"Complete required fields",IF(L412&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q412" s="9" t="n"/>
+      <c r="R412" s="9" t="n"/>
+      <c r="S412" s="9" t="n"/>
     </row>
     <row r="413" ht="23" customHeight="1">
       <c r="A413" s="14" t="n"/>
@@ -14393,6 +15644,9 @@
         <f>IF(A413="","",IF(COUNTIF($A$2:$A$501,A413)&gt;1,"Duplicate lot ID",IF(OR(B413="",H413="",I413="",J413=""),"Complete required fields",IF(L413&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q413" s="14" t="n"/>
+      <c r="R413" s="14" t="n"/>
+      <c r="S413" s="14" t="n"/>
     </row>
     <row r="414" ht="23" customHeight="1">
       <c r="A414" s="9" t="n"/>
@@ -14426,6 +15680,9 @@
         <f>IF(A414="","",IF(COUNTIF($A$2:$A$501,A414)&gt;1,"Duplicate lot ID",IF(OR(B414="",H414="",I414="",J414=""),"Complete required fields",IF(L414&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q414" s="9" t="n"/>
+      <c r="R414" s="9" t="n"/>
+      <c r="S414" s="9" t="n"/>
     </row>
     <row r="415" ht="23" customHeight="1">
       <c r="A415" s="14" t="n"/>
@@ -14459,6 +15716,9 @@
         <f>IF(A415="","",IF(COUNTIF($A$2:$A$501,A415)&gt;1,"Duplicate lot ID",IF(OR(B415="",H415="",I415="",J415=""),"Complete required fields",IF(L415&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q415" s="14" t="n"/>
+      <c r="R415" s="14" t="n"/>
+      <c r="S415" s="14" t="n"/>
     </row>
     <row r="416" ht="23" customHeight="1">
       <c r="A416" s="9" t="n"/>
@@ -14492,6 +15752,9 @@
         <f>IF(A416="","",IF(COUNTIF($A$2:$A$501,A416)&gt;1,"Duplicate lot ID",IF(OR(B416="",H416="",I416="",J416=""),"Complete required fields",IF(L416&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q416" s="9" t="n"/>
+      <c r="R416" s="9" t="n"/>
+      <c r="S416" s="9" t="n"/>
     </row>
     <row r="417" ht="23" customHeight="1">
       <c r="A417" s="14" t="n"/>
@@ -14525,6 +15788,9 @@
         <f>IF(A417="","",IF(COUNTIF($A$2:$A$501,A417)&gt;1,"Duplicate lot ID",IF(OR(B417="",H417="",I417="",J417=""),"Complete required fields",IF(L417&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q417" s="14" t="n"/>
+      <c r="R417" s="14" t="n"/>
+      <c r="S417" s="14" t="n"/>
     </row>
     <row r="418" ht="23" customHeight="1">
       <c r="A418" s="9" t="n"/>
@@ -14558,6 +15824,9 @@
         <f>IF(A418="","",IF(COUNTIF($A$2:$A$501,A418)&gt;1,"Duplicate lot ID",IF(OR(B418="",H418="",I418="",J418=""),"Complete required fields",IF(L418&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q418" s="9" t="n"/>
+      <c r="R418" s="9" t="n"/>
+      <c r="S418" s="9" t="n"/>
     </row>
     <row r="419" ht="23" customHeight="1">
       <c r="A419" s="14" t="n"/>
@@ -14591,6 +15860,9 @@
         <f>IF(A419="","",IF(COUNTIF($A$2:$A$501,A419)&gt;1,"Duplicate lot ID",IF(OR(B419="",H419="",I419="",J419=""),"Complete required fields",IF(L419&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q419" s="14" t="n"/>
+      <c r="R419" s="14" t="n"/>
+      <c r="S419" s="14" t="n"/>
     </row>
     <row r="420" ht="23" customHeight="1">
       <c r="A420" s="9" t="n"/>
@@ -14624,6 +15896,9 @@
         <f>IF(A420="","",IF(COUNTIF($A$2:$A$501,A420)&gt;1,"Duplicate lot ID",IF(OR(B420="",H420="",I420="",J420=""),"Complete required fields",IF(L420&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q420" s="9" t="n"/>
+      <c r="R420" s="9" t="n"/>
+      <c r="S420" s="9" t="n"/>
     </row>
     <row r="421" ht="23" customHeight="1">
       <c r="A421" s="14" t="n"/>
@@ -14657,6 +15932,9 @@
         <f>IF(A421="","",IF(COUNTIF($A$2:$A$501,A421)&gt;1,"Duplicate lot ID",IF(OR(B421="",H421="",I421="",J421=""),"Complete required fields",IF(L421&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q421" s="14" t="n"/>
+      <c r="R421" s="14" t="n"/>
+      <c r="S421" s="14" t="n"/>
     </row>
     <row r="422" ht="23" customHeight="1">
       <c r="A422" s="9" t="n"/>
@@ -14690,6 +15968,9 @@
         <f>IF(A422="","",IF(COUNTIF($A$2:$A$501,A422)&gt;1,"Duplicate lot ID",IF(OR(B422="",H422="",I422="",J422=""),"Complete required fields",IF(L422&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q422" s="9" t="n"/>
+      <c r="R422" s="9" t="n"/>
+      <c r="S422" s="9" t="n"/>
     </row>
     <row r="423" ht="23" customHeight="1">
       <c r="A423" s="14" t="n"/>
@@ -14723,6 +16004,9 @@
         <f>IF(A423="","",IF(COUNTIF($A$2:$A$501,A423)&gt;1,"Duplicate lot ID",IF(OR(B423="",H423="",I423="",J423=""),"Complete required fields",IF(L423&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q423" s="14" t="n"/>
+      <c r="R423" s="14" t="n"/>
+      <c r="S423" s="14" t="n"/>
     </row>
     <row r="424" ht="23" customHeight="1">
       <c r="A424" s="9" t="n"/>
@@ -14756,6 +16040,9 @@
         <f>IF(A424="","",IF(COUNTIF($A$2:$A$501,A424)&gt;1,"Duplicate lot ID",IF(OR(B424="",H424="",I424="",J424=""),"Complete required fields",IF(L424&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q424" s="9" t="n"/>
+      <c r="R424" s="9" t="n"/>
+      <c r="S424" s="9" t="n"/>
     </row>
     <row r="425" ht="23" customHeight="1">
       <c r="A425" s="14" t="n"/>
@@ -14789,6 +16076,9 @@
         <f>IF(A425="","",IF(COUNTIF($A$2:$A$501,A425)&gt;1,"Duplicate lot ID",IF(OR(B425="",H425="",I425="",J425=""),"Complete required fields",IF(L425&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q425" s="14" t="n"/>
+      <c r="R425" s="14" t="n"/>
+      <c r="S425" s="14" t="n"/>
     </row>
     <row r="426" ht="23" customHeight="1">
       <c r="A426" s="9" t="n"/>
@@ -14822,6 +16112,9 @@
         <f>IF(A426="","",IF(COUNTIF($A$2:$A$501,A426)&gt;1,"Duplicate lot ID",IF(OR(B426="",H426="",I426="",J426=""),"Complete required fields",IF(L426&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q426" s="9" t="n"/>
+      <c r="R426" s="9" t="n"/>
+      <c r="S426" s="9" t="n"/>
     </row>
     <row r="427" ht="23" customHeight="1">
       <c r="A427" s="14" t="n"/>
@@ -14855,6 +16148,9 @@
         <f>IF(A427="","",IF(COUNTIF($A$2:$A$501,A427)&gt;1,"Duplicate lot ID",IF(OR(B427="",H427="",I427="",J427=""),"Complete required fields",IF(L427&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q427" s="14" t="n"/>
+      <c r="R427" s="14" t="n"/>
+      <c r="S427" s="14" t="n"/>
     </row>
     <row r="428" ht="23" customHeight="1">
       <c r="A428" s="9" t="n"/>
@@ -14888,6 +16184,9 @@
         <f>IF(A428="","",IF(COUNTIF($A$2:$A$501,A428)&gt;1,"Duplicate lot ID",IF(OR(B428="",H428="",I428="",J428=""),"Complete required fields",IF(L428&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q428" s="9" t="n"/>
+      <c r="R428" s="9" t="n"/>
+      <c r="S428" s="9" t="n"/>
     </row>
     <row r="429" ht="23" customHeight="1">
       <c r="A429" s="14" t="n"/>
@@ -14921,6 +16220,9 @@
         <f>IF(A429="","",IF(COUNTIF($A$2:$A$501,A429)&gt;1,"Duplicate lot ID",IF(OR(B429="",H429="",I429="",J429=""),"Complete required fields",IF(L429&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q429" s="14" t="n"/>
+      <c r="R429" s="14" t="n"/>
+      <c r="S429" s="14" t="n"/>
     </row>
     <row r="430" ht="23" customHeight="1">
       <c r="A430" s="9" t="n"/>
@@ -14954,6 +16256,9 @@
         <f>IF(A430="","",IF(COUNTIF($A$2:$A$501,A430)&gt;1,"Duplicate lot ID",IF(OR(B430="",H430="",I430="",J430=""),"Complete required fields",IF(L430&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q430" s="9" t="n"/>
+      <c r="R430" s="9" t="n"/>
+      <c r="S430" s="9" t="n"/>
     </row>
     <row r="431" ht="23" customHeight="1">
       <c r="A431" s="14" t="n"/>
@@ -14987,6 +16292,9 @@
         <f>IF(A431="","",IF(COUNTIF($A$2:$A$501,A431)&gt;1,"Duplicate lot ID",IF(OR(B431="",H431="",I431="",J431=""),"Complete required fields",IF(L431&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q431" s="14" t="n"/>
+      <c r="R431" s="14" t="n"/>
+      <c r="S431" s="14" t="n"/>
     </row>
     <row r="432" ht="23" customHeight="1">
       <c r="A432" s="9" t="n"/>
@@ -15020,6 +16328,9 @@
         <f>IF(A432="","",IF(COUNTIF($A$2:$A$501,A432)&gt;1,"Duplicate lot ID",IF(OR(B432="",H432="",I432="",J432=""),"Complete required fields",IF(L432&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q432" s="9" t="n"/>
+      <c r="R432" s="9" t="n"/>
+      <c r="S432" s="9" t="n"/>
     </row>
     <row r="433" ht="23" customHeight="1">
       <c r="A433" s="14" t="n"/>
@@ -15053,6 +16364,9 @@
         <f>IF(A433="","",IF(COUNTIF($A$2:$A$501,A433)&gt;1,"Duplicate lot ID",IF(OR(B433="",H433="",I433="",J433=""),"Complete required fields",IF(L433&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q433" s="14" t="n"/>
+      <c r="R433" s="14" t="n"/>
+      <c r="S433" s="14" t="n"/>
     </row>
     <row r="434" ht="23" customHeight="1">
       <c r="A434" s="9" t="n"/>
@@ -15086,6 +16400,9 @@
         <f>IF(A434="","",IF(COUNTIF($A$2:$A$501,A434)&gt;1,"Duplicate lot ID",IF(OR(B434="",H434="",I434="",J434=""),"Complete required fields",IF(L434&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q434" s="9" t="n"/>
+      <c r="R434" s="9" t="n"/>
+      <c r="S434" s="9" t="n"/>
     </row>
     <row r="435" ht="23" customHeight="1">
       <c r="A435" s="14" t="n"/>
@@ -15119,6 +16436,9 @@
         <f>IF(A435="","",IF(COUNTIF($A$2:$A$501,A435)&gt;1,"Duplicate lot ID",IF(OR(B435="",H435="",I435="",J435=""),"Complete required fields",IF(L435&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q435" s="14" t="n"/>
+      <c r="R435" s="14" t="n"/>
+      <c r="S435" s="14" t="n"/>
     </row>
     <row r="436" ht="23" customHeight="1">
       <c r="A436" s="9" t="n"/>
@@ -15152,6 +16472,9 @@
         <f>IF(A436="","",IF(COUNTIF($A$2:$A$501,A436)&gt;1,"Duplicate lot ID",IF(OR(B436="",H436="",I436="",J436=""),"Complete required fields",IF(L436&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q436" s="9" t="n"/>
+      <c r="R436" s="9" t="n"/>
+      <c r="S436" s="9" t="n"/>
     </row>
     <row r="437" ht="23" customHeight="1">
       <c r="A437" s="14" t="n"/>
@@ -15185,6 +16508,9 @@
         <f>IF(A437="","",IF(COUNTIF($A$2:$A$501,A437)&gt;1,"Duplicate lot ID",IF(OR(B437="",H437="",I437="",J437=""),"Complete required fields",IF(L437&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q437" s="14" t="n"/>
+      <c r="R437" s="14" t="n"/>
+      <c r="S437" s="14" t="n"/>
     </row>
     <row r="438" ht="23" customHeight="1">
       <c r="A438" s="9" t="n"/>
@@ -15218,6 +16544,9 @@
         <f>IF(A438="","",IF(COUNTIF($A$2:$A$501,A438)&gt;1,"Duplicate lot ID",IF(OR(B438="",H438="",I438="",J438=""),"Complete required fields",IF(L438&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q438" s="9" t="n"/>
+      <c r="R438" s="9" t="n"/>
+      <c r="S438" s="9" t="n"/>
     </row>
     <row r="439" ht="23" customHeight="1">
       <c r="A439" s="14" t="n"/>
@@ -15251,6 +16580,9 @@
         <f>IF(A439="","",IF(COUNTIF($A$2:$A$501,A439)&gt;1,"Duplicate lot ID",IF(OR(B439="",H439="",I439="",J439=""),"Complete required fields",IF(L439&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q439" s="14" t="n"/>
+      <c r="R439" s="14" t="n"/>
+      <c r="S439" s="14" t="n"/>
     </row>
     <row r="440" ht="23" customHeight="1">
       <c r="A440" s="9" t="n"/>
@@ -15284,6 +16616,9 @@
         <f>IF(A440="","",IF(COUNTIF($A$2:$A$501,A440)&gt;1,"Duplicate lot ID",IF(OR(B440="",H440="",I440="",J440=""),"Complete required fields",IF(L440&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q440" s="9" t="n"/>
+      <c r="R440" s="9" t="n"/>
+      <c r="S440" s="9" t="n"/>
     </row>
     <row r="441" ht="23" customHeight="1">
       <c r="A441" s="14" t="n"/>
@@ -15317,6 +16652,9 @@
         <f>IF(A441="","",IF(COUNTIF($A$2:$A$501,A441)&gt;1,"Duplicate lot ID",IF(OR(B441="",H441="",I441="",J441=""),"Complete required fields",IF(L441&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q441" s="14" t="n"/>
+      <c r="R441" s="14" t="n"/>
+      <c r="S441" s="14" t="n"/>
     </row>
     <row r="442" ht="23" customHeight="1">
       <c r="A442" s="9" t="n"/>
@@ -15350,6 +16688,9 @@
         <f>IF(A442="","",IF(COUNTIF($A$2:$A$501,A442)&gt;1,"Duplicate lot ID",IF(OR(B442="",H442="",I442="",J442=""),"Complete required fields",IF(L442&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q442" s="9" t="n"/>
+      <c r="R442" s="9" t="n"/>
+      <c r="S442" s="9" t="n"/>
     </row>
     <row r="443" ht="23" customHeight="1">
       <c r="A443" s="14" t="n"/>
@@ -15383,6 +16724,9 @@
         <f>IF(A443="","",IF(COUNTIF($A$2:$A$501,A443)&gt;1,"Duplicate lot ID",IF(OR(B443="",H443="",I443="",J443=""),"Complete required fields",IF(L443&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q443" s="14" t="n"/>
+      <c r="R443" s="14" t="n"/>
+      <c r="S443" s="14" t="n"/>
     </row>
     <row r="444" ht="23" customHeight="1">
       <c r="A444" s="9" t="n"/>
@@ -15416,6 +16760,9 @@
         <f>IF(A444="","",IF(COUNTIF($A$2:$A$501,A444)&gt;1,"Duplicate lot ID",IF(OR(B444="",H444="",I444="",J444=""),"Complete required fields",IF(L444&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q444" s="9" t="n"/>
+      <c r="R444" s="9" t="n"/>
+      <c r="S444" s="9" t="n"/>
     </row>
     <row r="445" ht="23" customHeight="1">
       <c r="A445" s="14" t="n"/>
@@ -15449,6 +16796,9 @@
         <f>IF(A445="","",IF(COUNTIF($A$2:$A$501,A445)&gt;1,"Duplicate lot ID",IF(OR(B445="",H445="",I445="",J445=""),"Complete required fields",IF(L445&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q445" s="14" t="n"/>
+      <c r="R445" s="14" t="n"/>
+      <c r="S445" s="14" t="n"/>
     </row>
     <row r="446" ht="23" customHeight="1">
       <c r="A446" s="9" t="n"/>
@@ -15482,6 +16832,9 @@
         <f>IF(A446="","",IF(COUNTIF($A$2:$A$501,A446)&gt;1,"Duplicate lot ID",IF(OR(B446="",H446="",I446="",J446=""),"Complete required fields",IF(L446&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q446" s="9" t="n"/>
+      <c r="R446" s="9" t="n"/>
+      <c r="S446" s="9" t="n"/>
     </row>
     <row r="447" ht="23" customHeight="1">
       <c r="A447" s="14" t="n"/>
@@ -15515,6 +16868,9 @@
         <f>IF(A447="","",IF(COUNTIF($A$2:$A$501,A447)&gt;1,"Duplicate lot ID",IF(OR(B447="",H447="",I447="",J447=""),"Complete required fields",IF(L447&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q447" s="14" t="n"/>
+      <c r="R447" s="14" t="n"/>
+      <c r="S447" s="14" t="n"/>
     </row>
     <row r="448" ht="23" customHeight="1">
       <c r="A448" s="9" t="n"/>
@@ -15548,6 +16904,9 @@
         <f>IF(A448="","",IF(COUNTIF($A$2:$A$501,A448)&gt;1,"Duplicate lot ID",IF(OR(B448="",H448="",I448="",J448=""),"Complete required fields",IF(L448&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q448" s="9" t="n"/>
+      <c r="R448" s="9" t="n"/>
+      <c r="S448" s="9" t="n"/>
     </row>
     <row r="449" ht="23" customHeight="1">
       <c r="A449" s="14" t="n"/>
@@ -15581,6 +16940,9 @@
         <f>IF(A449="","",IF(COUNTIF($A$2:$A$501,A449)&gt;1,"Duplicate lot ID",IF(OR(B449="",H449="",I449="",J449=""),"Complete required fields",IF(L449&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q449" s="14" t="n"/>
+      <c r="R449" s="14" t="n"/>
+      <c r="S449" s="14" t="n"/>
     </row>
     <row r="450" ht="23" customHeight="1">
       <c r="A450" s="9" t="n"/>
@@ -15614,6 +16976,9 @@
         <f>IF(A450="","",IF(COUNTIF($A$2:$A$501,A450)&gt;1,"Duplicate lot ID",IF(OR(B450="",H450="",I450="",J450=""),"Complete required fields",IF(L450&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q450" s="9" t="n"/>
+      <c r="R450" s="9" t="n"/>
+      <c r="S450" s="9" t="n"/>
     </row>
     <row r="451" ht="23" customHeight="1">
       <c r="A451" s="14" t="n"/>
@@ -15647,6 +17012,9 @@
         <f>IF(A451="","",IF(COUNTIF($A$2:$A$501,A451)&gt;1,"Duplicate lot ID",IF(OR(B451="",H451="",I451="",J451=""),"Complete required fields",IF(L451&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q451" s="14" t="n"/>
+      <c r="R451" s="14" t="n"/>
+      <c r="S451" s="14" t="n"/>
     </row>
     <row r="452" ht="23" customHeight="1">
       <c r="A452" s="9" t="n"/>
@@ -15680,6 +17048,9 @@
         <f>IF(A452="","",IF(COUNTIF($A$2:$A$501,A452)&gt;1,"Duplicate lot ID",IF(OR(B452="",H452="",I452="",J452=""),"Complete required fields",IF(L452&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q452" s="9" t="n"/>
+      <c r="R452" s="9" t="n"/>
+      <c r="S452" s="9" t="n"/>
     </row>
     <row r="453" ht="23" customHeight="1">
       <c r="A453" s="14" t="n"/>
@@ -15713,6 +17084,9 @@
         <f>IF(A453="","",IF(COUNTIF($A$2:$A$501,A453)&gt;1,"Duplicate lot ID",IF(OR(B453="",H453="",I453="",J453=""),"Complete required fields",IF(L453&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q453" s="14" t="n"/>
+      <c r="R453" s="14" t="n"/>
+      <c r="S453" s="14" t="n"/>
     </row>
     <row r="454" ht="23" customHeight="1">
       <c r="A454" s="9" t="n"/>
@@ -15746,6 +17120,9 @@
         <f>IF(A454="","",IF(COUNTIF($A$2:$A$501,A454)&gt;1,"Duplicate lot ID",IF(OR(B454="",H454="",I454="",J454=""),"Complete required fields",IF(L454&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q454" s="9" t="n"/>
+      <c r="R454" s="9" t="n"/>
+      <c r="S454" s="9" t="n"/>
     </row>
     <row r="455" ht="23" customHeight="1">
       <c r="A455" s="14" t="n"/>
@@ -15779,6 +17156,9 @@
         <f>IF(A455="","",IF(COUNTIF($A$2:$A$501,A455)&gt;1,"Duplicate lot ID",IF(OR(B455="",H455="",I455="",J455=""),"Complete required fields",IF(L455&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q455" s="14" t="n"/>
+      <c r="R455" s="14" t="n"/>
+      <c r="S455" s="14" t="n"/>
     </row>
     <row r="456" ht="23" customHeight="1">
       <c r="A456" s="9" t="n"/>
@@ -15812,6 +17192,9 @@
         <f>IF(A456="","",IF(COUNTIF($A$2:$A$501,A456)&gt;1,"Duplicate lot ID",IF(OR(B456="",H456="",I456="",J456=""),"Complete required fields",IF(L456&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q456" s="9" t="n"/>
+      <c r="R456" s="9" t="n"/>
+      <c r="S456" s="9" t="n"/>
     </row>
     <row r="457" ht="23" customHeight="1">
       <c r="A457" s="14" t="n"/>
@@ -15845,6 +17228,9 @@
         <f>IF(A457="","",IF(COUNTIF($A$2:$A$501,A457)&gt;1,"Duplicate lot ID",IF(OR(B457="",H457="",I457="",J457=""),"Complete required fields",IF(L457&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q457" s="14" t="n"/>
+      <c r="R457" s="14" t="n"/>
+      <c r="S457" s="14" t="n"/>
     </row>
     <row r="458" ht="23" customHeight="1">
       <c r="A458" s="9" t="n"/>
@@ -15878,6 +17264,9 @@
         <f>IF(A458="","",IF(COUNTIF($A$2:$A$501,A458)&gt;1,"Duplicate lot ID",IF(OR(B458="",H458="",I458="",J458=""),"Complete required fields",IF(L458&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q458" s="9" t="n"/>
+      <c r="R458" s="9" t="n"/>
+      <c r="S458" s="9" t="n"/>
     </row>
     <row r="459" ht="23" customHeight="1">
       <c r="A459" s="14" t="n"/>
@@ -15911,6 +17300,9 @@
         <f>IF(A459="","",IF(COUNTIF($A$2:$A$501,A459)&gt;1,"Duplicate lot ID",IF(OR(B459="",H459="",I459="",J459=""),"Complete required fields",IF(L459&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q459" s="14" t="n"/>
+      <c r="R459" s="14" t="n"/>
+      <c r="S459" s="14" t="n"/>
     </row>
     <row r="460" ht="23" customHeight="1">
       <c r="A460" s="9" t="n"/>
@@ -15944,6 +17336,9 @@
         <f>IF(A460="","",IF(COUNTIF($A$2:$A$501,A460)&gt;1,"Duplicate lot ID",IF(OR(B460="",H460="",I460="",J460=""),"Complete required fields",IF(L460&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q460" s="9" t="n"/>
+      <c r="R460" s="9" t="n"/>
+      <c r="S460" s="9" t="n"/>
     </row>
     <row r="461" ht="23" customHeight="1">
       <c r="A461" s="14" t="n"/>
@@ -15977,6 +17372,9 @@
         <f>IF(A461="","",IF(COUNTIF($A$2:$A$501,A461)&gt;1,"Duplicate lot ID",IF(OR(B461="",H461="",I461="",J461=""),"Complete required fields",IF(L461&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q461" s="14" t="n"/>
+      <c r="R461" s="14" t="n"/>
+      <c r="S461" s="14" t="n"/>
     </row>
     <row r="462" ht="23" customHeight="1">
       <c r="A462" s="9" t="n"/>
@@ -16010,6 +17408,9 @@
         <f>IF(A462="","",IF(COUNTIF($A$2:$A$501,A462)&gt;1,"Duplicate lot ID",IF(OR(B462="",H462="",I462="",J462=""),"Complete required fields",IF(L462&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q462" s="9" t="n"/>
+      <c r="R462" s="9" t="n"/>
+      <c r="S462" s="9" t="n"/>
     </row>
     <row r="463" ht="23" customHeight="1">
       <c r="A463" s="14" t="n"/>
@@ -16043,6 +17444,9 @@
         <f>IF(A463="","",IF(COUNTIF($A$2:$A$501,A463)&gt;1,"Duplicate lot ID",IF(OR(B463="",H463="",I463="",J463=""),"Complete required fields",IF(L463&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q463" s="14" t="n"/>
+      <c r="R463" s="14" t="n"/>
+      <c r="S463" s="14" t="n"/>
     </row>
     <row r="464" ht="23" customHeight="1">
       <c r="A464" s="9" t="n"/>
@@ -16076,6 +17480,9 @@
         <f>IF(A464="","",IF(COUNTIF($A$2:$A$501,A464)&gt;1,"Duplicate lot ID",IF(OR(B464="",H464="",I464="",J464=""),"Complete required fields",IF(L464&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q464" s="9" t="n"/>
+      <c r="R464" s="9" t="n"/>
+      <c r="S464" s="9" t="n"/>
     </row>
     <row r="465" ht="23" customHeight="1">
       <c r="A465" s="14" t="n"/>
@@ -16109,6 +17516,9 @@
         <f>IF(A465="","",IF(COUNTIF($A$2:$A$501,A465)&gt;1,"Duplicate lot ID",IF(OR(B465="",H465="",I465="",J465=""),"Complete required fields",IF(L465&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q465" s="14" t="n"/>
+      <c r="R465" s="14" t="n"/>
+      <c r="S465" s="14" t="n"/>
     </row>
     <row r="466" ht="23" customHeight="1">
       <c r="A466" s="9" t="n"/>
@@ -16142,6 +17552,9 @@
         <f>IF(A466="","",IF(COUNTIF($A$2:$A$501,A466)&gt;1,"Duplicate lot ID",IF(OR(B466="",H466="",I466="",J466=""),"Complete required fields",IF(L466&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q466" s="9" t="n"/>
+      <c r="R466" s="9" t="n"/>
+      <c r="S466" s="9" t="n"/>
     </row>
     <row r="467" ht="23" customHeight="1">
       <c r="A467" s="14" t="n"/>
@@ -16175,6 +17588,9 @@
         <f>IF(A467="","",IF(COUNTIF($A$2:$A$501,A467)&gt;1,"Duplicate lot ID",IF(OR(B467="",H467="",I467="",J467=""),"Complete required fields",IF(L467&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q467" s="14" t="n"/>
+      <c r="R467" s="14" t="n"/>
+      <c r="S467" s="14" t="n"/>
     </row>
     <row r="468" ht="23" customHeight="1">
       <c r="A468" s="9" t="n"/>
@@ -16208,6 +17624,9 @@
         <f>IF(A468="","",IF(COUNTIF($A$2:$A$501,A468)&gt;1,"Duplicate lot ID",IF(OR(B468="",H468="",I468="",J468=""),"Complete required fields",IF(L468&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q468" s="9" t="n"/>
+      <c r="R468" s="9" t="n"/>
+      <c r="S468" s="9" t="n"/>
     </row>
     <row r="469" ht="23" customHeight="1">
       <c r="A469" s="14" t="n"/>
@@ -16241,6 +17660,9 @@
         <f>IF(A469="","",IF(COUNTIF($A$2:$A$501,A469)&gt;1,"Duplicate lot ID",IF(OR(B469="",H469="",I469="",J469=""),"Complete required fields",IF(L469&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q469" s="14" t="n"/>
+      <c r="R469" s="14" t="n"/>
+      <c r="S469" s="14" t="n"/>
     </row>
     <row r="470" ht="23" customHeight="1">
       <c r="A470" s="9" t="n"/>
@@ -16274,6 +17696,9 @@
         <f>IF(A470="","",IF(COUNTIF($A$2:$A$501,A470)&gt;1,"Duplicate lot ID",IF(OR(B470="",H470="",I470="",J470=""),"Complete required fields",IF(L470&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q470" s="9" t="n"/>
+      <c r="R470" s="9" t="n"/>
+      <c r="S470" s="9" t="n"/>
     </row>
     <row r="471" ht="23" customHeight="1">
       <c r="A471" s="14" t="n"/>
@@ -16307,6 +17732,9 @@
         <f>IF(A471="","",IF(COUNTIF($A$2:$A$501,A471)&gt;1,"Duplicate lot ID",IF(OR(B471="",H471="",I471="",J471=""),"Complete required fields",IF(L471&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q471" s="14" t="n"/>
+      <c r="R471" s="14" t="n"/>
+      <c r="S471" s="14" t="n"/>
     </row>
     <row r="472" ht="23" customHeight="1">
       <c r="A472" s="9" t="n"/>
@@ -16340,6 +17768,9 @@
         <f>IF(A472="","",IF(COUNTIF($A$2:$A$501,A472)&gt;1,"Duplicate lot ID",IF(OR(B472="",H472="",I472="",J472=""),"Complete required fields",IF(L472&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q472" s="9" t="n"/>
+      <c r="R472" s="9" t="n"/>
+      <c r="S472" s="9" t="n"/>
     </row>
     <row r="473" ht="23" customHeight="1">
       <c r="A473" s="14" t="n"/>
@@ -16373,6 +17804,9 @@
         <f>IF(A473="","",IF(COUNTIF($A$2:$A$501,A473)&gt;1,"Duplicate lot ID",IF(OR(B473="",H473="",I473="",J473=""),"Complete required fields",IF(L473&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q473" s="14" t="n"/>
+      <c r="R473" s="14" t="n"/>
+      <c r="S473" s="14" t="n"/>
     </row>
     <row r="474" ht="23" customHeight="1">
       <c r="A474" s="9" t="n"/>
@@ -16406,6 +17840,9 @@
         <f>IF(A474="","",IF(COUNTIF($A$2:$A$501,A474)&gt;1,"Duplicate lot ID",IF(OR(B474="",H474="",I474="",J474=""),"Complete required fields",IF(L474&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q474" s="9" t="n"/>
+      <c r="R474" s="9" t="n"/>
+      <c r="S474" s="9" t="n"/>
     </row>
     <row r="475" ht="23" customHeight="1">
       <c r="A475" s="14" t="n"/>
@@ -16439,6 +17876,9 @@
         <f>IF(A475="","",IF(COUNTIF($A$2:$A$501,A475)&gt;1,"Duplicate lot ID",IF(OR(B475="",H475="",I475="",J475=""),"Complete required fields",IF(L475&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q475" s="14" t="n"/>
+      <c r="R475" s="14" t="n"/>
+      <c r="S475" s="14" t="n"/>
     </row>
     <row r="476" ht="23" customHeight="1">
       <c r="A476" s="9" t="n"/>
@@ -16472,6 +17912,9 @@
         <f>IF(A476="","",IF(COUNTIF($A$2:$A$501,A476)&gt;1,"Duplicate lot ID",IF(OR(B476="",H476="",I476="",J476=""),"Complete required fields",IF(L476&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q476" s="9" t="n"/>
+      <c r="R476" s="9" t="n"/>
+      <c r="S476" s="9" t="n"/>
     </row>
     <row r="477" ht="23" customHeight="1">
       <c r="A477" s="14" t="n"/>
@@ -16505,6 +17948,9 @@
         <f>IF(A477="","",IF(COUNTIF($A$2:$A$501,A477)&gt;1,"Duplicate lot ID",IF(OR(B477="",H477="",I477="",J477=""),"Complete required fields",IF(L477&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q477" s="14" t="n"/>
+      <c r="R477" s="14" t="n"/>
+      <c r="S477" s="14" t="n"/>
     </row>
     <row r="478" ht="23" customHeight="1">
       <c r="A478" s="9" t="n"/>
@@ -16538,6 +17984,9 @@
         <f>IF(A478="","",IF(COUNTIF($A$2:$A$501,A478)&gt;1,"Duplicate lot ID",IF(OR(B478="",H478="",I478="",J478=""),"Complete required fields",IF(L478&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q478" s="9" t="n"/>
+      <c r="R478" s="9" t="n"/>
+      <c r="S478" s="9" t="n"/>
     </row>
     <row r="479" ht="23" customHeight="1">
       <c r="A479" s="14" t="n"/>
@@ -16571,6 +18020,9 @@
         <f>IF(A479="","",IF(COUNTIF($A$2:$A$501,A479)&gt;1,"Duplicate lot ID",IF(OR(B479="",H479="",I479="",J479=""),"Complete required fields",IF(L479&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q479" s="14" t="n"/>
+      <c r="R479" s="14" t="n"/>
+      <c r="S479" s="14" t="n"/>
     </row>
     <row r="480" ht="23" customHeight="1">
       <c r="A480" s="9" t="n"/>
@@ -16604,6 +18056,9 @@
         <f>IF(A480="","",IF(COUNTIF($A$2:$A$501,A480)&gt;1,"Duplicate lot ID",IF(OR(B480="",H480="",I480="",J480=""),"Complete required fields",IF(L480&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q480" s="9" t="n"/>
+      <c r="R480" s="9" t="n"/>
+      <c r="S480" s="9" t="n"/>
     </row>
     <row r="481" ht="23" customHeight="1">
       <c r="A481" s="14" t="n"/>
@@ -16637,6 +18092,9 @@
         <f>IF(A481="","",IF(COUNTIF($A$2:$A$501,A481)&gt;1,"Duplicate lot ID",IF(OR(B481="",H481="",I481="",J481=""),"Complete required fields",IF(L481&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q481" s="14" t="n"/>
+      <c r="R481" s="14" t="n"/>
+      <c r="S481" s="14" t="n"/>
     </row>
     <row r="482" ht="23" customHeight="1">
       <c r="A482" s="9" t="n"/>
@@ -16670,6 +18128,9 @@
         <f>IF(A482="","",IF(COUNTIF($A$2:$A$501,A482)&gt;1,"Duplicate lot ID",IF(OR(B482="",H482="",I482="",J482=""),"Complete required fields",IF(L482&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q482" s="9" t="n"/>
+      <c r="R482" s="9" t="n"/>
+      <c r="S482" s="9" t="n"/>
     </row>
     <row r="483" ht="23" customHeight="1">
       <c r="A483" s="14" t="n"/>
@@ -16703,6 +18164,9 @@
         <f>IF(A483="","",IF(COUNTIF($A$2:$A$501,A483)&gt;1,"Duplicate lot ID",IF(OR(B483="",H483="",I483="",J483=""),"Complete required fields",IF(L483&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q483" s="14" t="n"/>
+      <c r="R483" s="14" t="n"/>
+      <c r="S483" s="14" t="n"/>
     </row>
     <row r="484" ht="23" customHeight="1">
       <c r="A484" s="9" t="n"/>
@@ -16736,6 +18200,9 @@
         <f>IF(A484="","",IF(COUNTIF($A$2:$A$501,A484)&gt;1,"Duplicate lot ID",IF(OR(B484="",H484="",I484="",J484=""),"Complete required fields",IF(L484&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q484" s="9" t="n"/>
+      <c r="R484" s="9" t="n"/>
+      <c r="S484" s="9" t="n"/>
     </row>
     <row r="485" ht="23" customHeight="1">
       <c r="A485" s="14" t="n"/>
@@ -16769,6 +18236,9 @@
         <f>IF(A485="","",IF(COUNTIF($A$2:$A$501,A485)&gt;1,"Duplicate lot ID",IF(OR(B485="",H485="",I485="",J485=""),"Complete required fields",IF(L485&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q485" s="14" t="n"/>
+      <c r="R485" s="14" t="n"/>
+      <c r="S485" s="14" t="n"/>
     </row>
     <row r="486" ht="23" customHeight="1">
       <c r="A486" s="9" t="n"/>
@@ -16802,6 +18272,9 @@
         <f>IF(A486="","",IF(COUNTIF($A$2:$A$501,A486)&gt;1,"Duplicate lot ID",IF(OR(B486="",H486="",I486="",J486=""),"Complete required fields",IF(L486&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q486" s="9" t="n"/>
+      <c r="R486" s="9" t="n"/>
+      <c r="S486" s="9" t="n"/>
     </row>
     <row r="487" ht="23" customHeight="1">
       <c r="A487" s="14" t="n"/>
@@ -16835,6 +18308,9 @@
         <f>IF(A487="","",IF(COUNTIF($A$2:$A$501,A487)&gt;1,"Duplicate lot ID",IF(OR(B487="",H487="",I487="",J487=""),"Complete required fields",IF(L487&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q487" s="14" t="n"/>
+      <c r="R487" s="14" t="n"/>
+      <c r="S487" s="14" t="n"/>
     </row>
     <row r="488" ht="23" customHeight="1">
       <c r="A488" s="9" t="n"/>
@@ -16868,6 +18344,9 @@
         <f>IF(A488="","",IF(COUNTIF($A$2:$A$501,A488)&gt;1,"Duplicate lot ID",IF(OR(B488="",H488="",I488="",J488=""),"Complete required fields",IF(L488&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q488" s="9" t="n"/>
+      <c r="R488" s="9" t="n"/>
+      <c r="S488" s="9" t="n"/>
     </row>
     <row r="489" ht="23" customHeight="1">
       <c r="A489" s="14" t="n"/>
@@ -16901,6 +18380,9 @@
         <f>IF(A489="","",IF(COUNTIF($A$2:$A$501,A489)&gt;1,"Duplicate lot ID",IF(OR(B489="",H489="",I489="",J489=""),"Complete required fields",IF(L489&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q489" s="14" t="n"/>
+      <c r="R489" s="14" t="n"/>
+      <c r="S489" s="14" t="n"/>
     </row>
     <row r="490" ht="23" customHeight="1">
       <c r="A490" s="9" t="n"/>
@@ -16934,6 +18416,9 @@
         <f>IF(A490="","",IF(COUNTIF($A$2:$A$501,A490)&gt;1,"Duplicate lot ID",IF(OR(B490="",H490="",I490="",J490=""),"Complete required fields",IF(L490&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q490" s="9" t="n"/>
+      <c r="R490" s="9" t="n"/>
+      <c r="S490" s="9" t="n"/>
     </row>
     <row r="491" ht="23" customHeight="1">
       <c r="A491" s="14" t="n"/>
@@ -16967,6 +18452,9 @@
         <f>IF(A491="","",IF(COUNTIF($A$2:$A$501,A491)&gt;1,"Duplicate lot ID",IF(OR(B491="",H491="",I491="",J491=""),"Complete required fields",IF(L491&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q491" s="14" t="n"/>
+      <c r="R491" s="14" t="n"/>
+      <c r="S491" s="14" t="n"/>
     </row>
     <row r="492" ht="23" customHeight="1">
       <c r="A492" s="9" t="n"/>
@@ -17000,6 +18488,9 @@
         <f>IF(A492="","",IF(COUNTIF($A$2:$A$501,A492)&gt;1,"Duplicate lot ID",IF(OR(B492="",H492="",I492="",J492=""),"Complete required fields",IF(L492&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q492" s="9" t="n"/>
+      <c r="R492" s="9" t="n"/>
+      <c r="S492" s="9" t="n"/>
     </row>
     <row r="493" ht="23" customHeight="1">
       <c r="A493" s="14" t="n"/>
@@ -17033,6 +18524,9 @@
         <f>IF(A493="","",IF(COUNTIF($A$2:$A$501,A493)&gt;1,"Duplicate lot ID",IF(OR(B493="",H493="",I493="",J493=""),"Complete required fields",IF(L493&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q493" s="14" t="n"/>
+      <c r="R493" s="14" t="n"/>
+      <c r="S493" s="14" t="n"/>
     </row>
     <row r="494" ht="23" customHeight="1">
       <c r="A494" s="9" t="n"/>
@@ -17066,6 +18560,9 @@
         <f>IF(A494="","",IF(COUNTIF($A$2:$A$501,A494)&gt;1,"Duplicate lot ID",IF(OR(B494="",H494="",I494="",J494=""),"Complete required fields",IF(L494&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q494" s="9" t="n"/>
+      <c r="R494" s="9" t="n"/>
+      <c r="S494" s="9" t="n"/>
     </row>
     <row r="495" ht="23" customHeight="1">
       <c r="A495" s="14" t="n"/>
@@ -17099,6 +18596,9 @@
         <f>IF(A495="","",IF(COUNTIF($A$2:$A$501,A495)&gt;1,"Duplicate lot ID",IF(OR(B495="",H495="",I495="",J495=""),"Complete required fields",IF(L495&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q495" s="14" t="n"/>
+      <c r="R495" s="14" t="n"/>
+      <c r="S495" s="14" t="n"/>
     </row>
     <row r="496" ht="23" customHeight="1">
       <c r="A496" s="9" t="n"/>
@@ -17132,6 +18632,9 @@
         <f>IF(A496="","",IF(COUNTIF($A$2:$A$501,A496)&gt;1,"Duplicate lot ID",IF(OR(B496="",H496="",I496="",J496=""),"Complete required fields",IF(L496&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q496" s="9" t="n"/>
+      <c r="R496" s="9" t="n"/>
+      <c r="S496" s="9" t="n"/>
     </row>
     <row r="497" ht="23" customHeight="1">
       <c r="A497" s="14" t="n"/>
@@ -17165,6 +18668,9 @@
         <f>IF(A497="","",IF(COUNTIF($A$2:$A$501,A497)&gt;1,"Duplicate lot ID",IF(OR(B497="",H497="",I497="",J497=""),"Complete required fields",IF(L497&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q497" s="14" t="n"/>
+      <c r="R497" s="14" t="n"/>
+      <c r="S497" s="14" t="n"/>
     </row>
     <row r="498" ht="23" customHeight="1">
       <c r="A498" s="9" t="n"/>
@@ -17198,6 +18704,9 @@
         <f>IF(A498="","",IF(COUNTIF($A$2:$A$501,A498)&gt;1,"Duplicate lot ID",IF(OR(B498="",H498="",I498="",J498=""),"Complete required fields",IF(L498&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q498" s="9" t="n"/>
+      <c r="R498" s="9" t="n"/>
+      <c r="S498" s="9" t="n"/>
     </row>
     <row r="499" ht="23" customHeight="1">
       <c r="A499" s="14" t="n"/>
@@ -17231,6 +18740,9 @@
         <f>IF(A499="","",IF(COUNTIF($A$2:$A$501,A499)&gt;1,"Duplicate lot ID",IF(OR(B499="",H499="",I499="",J499=""),"Complete required fields",IF(L499&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q499" s="14" t="n"/>
+      <c r="R499" s="14" t="n"/>
+      <c r="S499" s="14" t="n"/>
     </row>
     <row r="500" ht="23" customHeight="1">
       <c r="A500" s="9" t="n"/>
@@ -17264,6 +18776,9 @@
         <f>IF(A500="","",IF(COUNTIF($A$2:$A$501,A500)&gt;1,"Duplicate lot ID",IF(OR(B500="",H500="",I500="",J500=""),"Complete required fields",IF(L500&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q500" s="9" t="n"/>
+      <c r="R500" s="9" t="n"/>
+      <c r="S500" s="9" t="n"/>
     </row>
     <row r="501" ht="23" customHeight="1">
       <c r="A501" s="14" t="n"/>
@@ -17297,9 +18812,12 @@
         <f>IF(A501="","",IF(COUNTIF($A$2:$A$501,A501)&gt;1,"Duplicate lot ID",IF(OR(B501="",H501="",I501="",J501=""),"Complete required fields",IF(L501&lt;0,"OVER SOLD","OK"))))</f>
         <v/>
       </c>
+      <c r="Q501" s="14" t="n"/>
+      <c r="R501" s="14" t="n"/>
+      <c r="S501" s="14" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P501"/>
+  <autoFilter ref="A1:S501"/>
   <conditionalFormatting sqref="L2:L501">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
@@ -47049,7 +48567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -47177,6 +48695,13 @@
     </row>
     <row r="19" ht="45" customHeight="1">
       <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>17. Inventory Q is Subset / parallel, R is card serial number (e.g. 025/199), and S is grading certificate number. Grade remains in column G. Keep separate serialized or certified cards in separate rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>16. In Google Sheets, if the brand dropdown does not convert, select Inventory E2:E501 → Data → Data validation → Dropdown from a range → Brands &amp; Makes!A2:A1001. Use a warning rather than rejecting custom brands.</t>
         </is>
